--- a/試跑/試跑資料_排課需求收集表.xlsx
+++ b/試跑/試跑資料_排課需求收集表.xlsx
@@ -16687,7 +16687,7 @@
       </c>
       <c r="E5" s="44" t="inlineStr">
         <is>
-          <t>英語乙</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F5" s="44" t="inlineStr">
@@ -16695,26 +16695,22 @@
           <t>原班教室</t>
         </is>
       </c>
-      <c r="G5" s="44" t="inlineStr">
-        <is>
-          <t>（試跑）科任兼本土語</t>
-        </is>
-      </c>
+      <c r="G5" s="44" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="36">
       <c r="A6" s="52" t="inlineStr">
         <is>
-          <t>1年2班</t>
+          <t>2年1班</t>
         </is>
       </c>
       <c r="B6" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C6" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D6" s="52" t="inlineStr">
@@ -16724,7 +16720,7 @@
       </c>
       <c r="E6" s="44" t="inlineStr">
         <is>
-          <t>英語乙</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F6" s="44" t="inlineStr">
@@ -16737,17 +16733,17 @@
     <row r="7" ht="15" customHeight="1" s="36">
       <c r="A7" s="52" t="inlineStr">
         <is>
-          <t>1年3班</t>
+          <t>3年1班</t>
         </is>
       </c>
       <c r="B7" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C7" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D7" s="52" t="inlineStr">
@@ -16757,7 +16753,7 @@
       </c>
       <c r="E7" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F7" s="44" t="inlineStr">
@@ -16770,7 +16766,7 @@
     <row r="8" ht="15" customHeight="1" s="36">
       <c r="A8" s="52" t="inlineStr">
         <is>
-          <t>1年4班</t>
+          <t>4年1班</t>
         </is>
       </c>
       <c r="B8" s="52" t="inlineStr">
@@ -16780,17 +16776,17 @@
       </c>
       <c r="C8" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D8" s="52" t="inlineStr">
         <is>
-          <t>新住民語</t>
+          <t>閩南語</t>
         </is>
       </c>
       <c r="E8" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F8" s="44" t="inlineStr">
@@ -16803,17 +16799,17 @@
     <row r="9" ht="15" customHeight="1" s="36">
       <c r="A9" s="52" t="inlineStr">
         <is>
-          <t>1年5班</t>
+          <t>5年1班</t>
         </is>
       </c>
       <c r="B9" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C9" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D9" s="52" t="inlineStr">
@@ -16823,7 +16819,7 @@
       </c>
       <c r="E9" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F9" s="44" t="inlineStr">
@@ -16836,7 +16832,7 @@
     <row r="10" ht="15" customHeight="1" s="36">
       <c r="A10" s="52" t="inlineStr">
         <is>
-          <t>1年6班</t>
+          <t>6年1班</t>
         </is>
       </c>
       <c r="B10" s="52" t="inlineStr">
@@ -16846,7 +16842,7 @@
       </c>
       <c r="C10" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D10" s="52" t="inlineStr">
@@ -16856,7 +16852,7 @@
       </c>
       <c r="E10" s="44" t="inlineStr">
         <is>
-          <t>本土語乙</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F10" s="44" t="inlineStr">
@@ -16869,12 +16865,12 @@
     <row r="11" ht="15" customHeight="1" s="36">
       <c r="A11" s="52" t="inlineStr">
         <is>
-          <t>1年7班</t>
+          <t>1年2班</t>
         </is>
       </c>
       <c r="B11" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C11" s="52" t="inlineStr">
@@ -16889,7 +16885,7 @@
       </c>
       <c r="E11" s="44" t="inlineStr">
         <is>
-          <t>本土語乙</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F11" s="44" t="inlineStr">
@@ -16902,17 +16898,17 @@
     <row r="12" ht="15" customHeight="1" s="36">
       <c r="A12" s="52" t="inlineStr">
         <is>
-          <t>1年8班</t>
+          <t>2年2班</t>
         </is>
       </c>
       <c r="B12" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C12" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D12" s="52" t="inlineStr">
@@ -16922,7 +16918,7 @@
       </c>
       <c r="E12" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F12" s="44" t="inlineStr">
@@ -16935,12 +16931,12 @@
     <row r="13" ht="15" customHeight="1" s="36">
       <c r="A13" s="52" t="inlineStr">
         <is>
-          <t>1年9班</t>
+          <t>3年2班</t>
         </is>
       </c>
       <c r="B13" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C13" s="52" t="inlineStr">
@@ -16950,12 +16946,12 @@
       </c>
       <c r="D13" s="52" t="inlineStr">
         <is>
-          <t>新住民語</t>
+          <t>閩南語</t>
         </is>
       </c>
       <c r="E13" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F13" s="44" t="inlineStr">
@@ -16968,17 +16964,17 @@
     <row r="14" ht="15" customHeight="1" s="36">
       <c r="A14" s="52" t="inlineStr">
         <is>
-          <t>1年10班</t>
+          <t>4年2班</t>
         </is>
       </c>
       <c r="B14" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C14" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D14" s="52" t="inlineStr">
@@ -16988,7 +16984,7 @@
       </c>
       <c r="E14" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F14" s="44" t="inlineStr">
@@ -17001,27 +16997,27 @@
     <row r="15" ht="15" customHeight="1" s="36">
       <c r="A15" s="52" t="inlineStr">
         <is>
-          <t>1年11班</t>
+          <t>5年2班</t>
         </is>
       </c>
       <c r="B15" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C15" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D15" s="52" t="inlineStr">
         <is>
-          <t>新住民語</t>
+          <t>閩南語</t>
         </is>
       </c>
       <c r="E15" s="44" t="inlineStr">
         <is>
-          <t>本土語乙</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F15" s="44" t="inlineStr">
@@ -17034,27 +17030,27 @@
     <row r="16" ht="15" customHeight="1" s="36">
       <c r="A16" s="52" t="inlineStr">
         <is>
-          <t>1年12班</t>
+          <t>6年2班</t>
         </is>
       </c>
       <c r="B16" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C16" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="52" t="inlineStr">
         <is>
-          <t>客語</t>
+          <t>閩南語</t>
         </is>
       </c>
       <c r="E16" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F16" s="44" t="inlineStr">
@@ -17067,12 +17063,12 @@
     <row r="17" ht="15" customHeight="1" s="36">
       <c r="A17" s="52" t="inlineStr">
         <is>
-          <t>2年1班</t>
+          <t>1年3班</t>
         </is>
       </c>
       <c r="B17" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C17" s="52" t="inlineStr">
@@ -17087,7 +17083,7 @@
       </c>
       <c r="E17" s="44" t="inlineStr">
         <is>
-          <t>本土語乙</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F17" s="44" t="inlineStr">
@@ -17100,12 +17096,12 @@
     <row r="18" ht="15" customHeight="1" s="36">
       <c r="A18" s="52" t="inlineStr">
         <is>
-          <t>2年2班</t>
+          <t>2年3班</t>
         </is>
       </c>
       <c r="B18" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C18" s="52" t="inlineStr">
@@ -17120,7 +17116,7 @@
       </c>
       <c r="E18" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F18" s="44" t="inlineStr">
@@ -17133,7 +17129,7 @@
     <row r="19" ht="15" customHeight="1" s="36">
       <c r="A19" s="52" t="inlineStr">
         <is>
-          <t>2年3班</t>
+          <t>3年3班</t>
         </is>
       </c>
       <c r="B19" s="52" t="inlineStr">
@@ -17143,7 +17139,7 @@
       </c>
       <c r="C19" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="52" t="inlineStr">
@@ -17153,7 +17149,7 @@
       </c>
       <c r="E19" s="44" t="inlineStr">
         <is>
-          <t>本土語乙</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F19" s="44" t="inlineStr">
@@ -17166,17 +17162,17 @@
     <row r="20" ht="15" customHeight="1" s="36">
       <c r="A20" s="52" t="inlineStr">
         <is>
-          <t>2年4班</t>
+          <t>4年3班</t>
         </is>
       </c>
       <c r="B20" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C20" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D20" s="52" t="inlineStr">
@@ -17186,7 +17182,7 @@
       </c>
       <c r="E20" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F20" s="44" t="inlineStr">
@@ -17199,17 +17195,17 @@
     <row r="21" ht="15" customHeight="1" s="36">
       <c r="A21" s="52" t="inlineStr">
         <is>
-          <t>2年5班</t>
+          <t>5年3班</t>
         </is>
       </c>
       <c r="B21" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C21" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D21" s="52" t="inlineStr">
@@ -17219,7 +17215,7 @@
       </c>
       <c r="E21" s="44" t="inlineStr">
         <is>
-          <t>本土語丙</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F21" s="44" t="inlineStr">
@@ -17232,27 +17228,27 @@
     <row r="22" ht="15" customHeight="1" s="36">
       <c r="A22" s="52" t="inlineStr">
         <is>
-          <t>2年6班</t>
+          <t>6年3班</t>
         </is>
       </c>
       <c r="B22" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C22" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D22" s="52" t="inlineStr">
         <is>
-          <t>族語</t>
+          <t>閩南語</t>
         </is>
       </c>
       <c r="E22" s="44" t="inlineStr">
         <is>
-          <t>本土語乙</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F22" s="44" t="inlineStr">
@@ -17265,27 +17261,27 @@
     <row r="23" ht="15" customHeight="1" s="36">
       <c r="A23" s="52" t="inlineStr">
         <is>
-          <t>2年7班</t>
+          <t>1年4班</t>
         </is>
       </c>
       <c r="B23" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C23" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D23" s="52" t="inlineStr">
         <is>
-          <t>新住民語</t>
+          <t>閩南語</t>
         </is>
       </c>
       <c r="E23" s="44" t="inlineStr">
         <is>
-          <t>本土語乙</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F23" s="44" t="inlineStr">
@@ -17298,12 +17294,12 @@
     <row r="24" ht="15" customHeight="1" s="36">
       <c r="A24" s="52" t="inlineStr">
         <is>
-          <t>2年8班</t>
+          <t>2年4班</t>
         </is>
       </c>
       <c r="B24" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C24" s="52" t="inlineStr">
@@ -17318,7 +17314,7 @@
       </c>
       <c r="E24" s="44" t="inlineStr">
         <is>
-          <t>本土語丙</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F24" s="44" t="inlineStr">
@@ -17331,17 +17327,17 @@
     <row r="25" ht="15" customHeight="1" s="36">
       <c r="A25" s="52" t="inlineStr">
         <is>
-          <t>2年9班</t>
+          <t>3年4班</t>
         </is>
       </c>
       <c r="B25" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C25" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D25" s="52" t="inlineStr">
@@ -17351,7 +17347,7 @@
       </c>
       <c r="E25" s="44" t="inlineStr">
         <is>
-          <t>本土語丙</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F25" s="44" t="inlineStr">
@@ -17364,7 +17360,7 @@
     <row r="26" ht="15" customHeight="1" s="36">
       <c r="A26" s="52" t="inlineStr">
         <is>
-          <t>2年10班</t>
+          <t>4年4班</t>
         </is>
       </c>
       <c r="B26" s="52" t="inlineStr">
@@ -17374,17 +17370,17 @@
       </c>
       <c r="C26" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D26" s="52" t="inlineStr">
         <is>
-          <t>新住民語</t>
+          <t>閩南語</t>
         </is>
       </c>
       <c r="E26" s="44" t="inlineStr">
         <is>
-          <t>本土語丙</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F26" s="44" t="inlineStr">
@@ -17397,17 +17393,17 @@
     <row r="27" ht="15" customHeight="1" s="36">
       <c r="A27" s="52" t="inlineStr">
         <is>
-          <t>2年11班</t>
+          <t>5年4班</t>
         </is>
       </c>
       <c r="B27" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C27" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D27" s="52" t="inlineStr">
@@ -17417,7 +17413,7 @@
       </c>
       <c r="E27" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語甲</t>
         </is>
       </c>
       <c r="F27" s="44" t="inlineStr">
@@ -17430,12 +17426,12 @@
     <row r="28" ht="15" customHeight="1" s="36">
       <c r="A28" s="52" t="inlineStr">
         <is>
-          <t>3年1班</t>
+          <t>6年4班</t>
         </is>
       </c>
       <c r="B28" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C28" s="52" t="inlineStr">
@@ -17450,7 +17446,7 @@
       </c>
       <c r="E28" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語乙</t>
         </is>
       </c>
       <c r="F28" s="44" t="inlineStr">
@@ -17463,17 +17459,17 @@
     <row r="29" ht="15" customHeight="1" s="36">
       <c r="A29" s="52" t="inlineStr">
         <is>
-          <t>3年2班</t>
+          <t>1年5班</t>
         </is>
       </c>
       <c r="B29" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C29" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D29" s="52" t="inlineStr">
@@ -17483,7 +17479,7 @@
       </c>
       <c r="E29" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語乙</t>
         </is>
       </c>
       <c r="F29" s="44" t="inlineStr">
@@ -17496,7 +17492,7 @@
     <row r="30" ht="15" customHeight="1" s="36">
       <c r="A30" s="52" t="inlineStr">
         <is>
-          <t>3年3班</t>
+          <t>2年5班</t>
         </is>
       </c>
       <c r="B30" s="52" t="inlineStr">
@@ -17506,7 +17502,7 @@
       </c>
       <c r="C30" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D30" s="52" t="inlineStr">
@@ -17516,7 +17512,7 @@
       </c>
       <c r="E30" s="44" t="inlineStr">
         <is>
-          <t>本土語乙</t>
+          <t>閩南語乙</t>
         </is>
       </c>
       <c r="F30" s="44" t="inlineStr">
@@ -17529,7 +17525,7 @@
     <row r="31" ht="15" customHeight="1" s="36">
       <c r="A31" s="52" t="inlineStr">
         <is>
-          <t>3年4班</t>
+          <t>3年5班</t>
         </is>
       </c>
       <c r="B31" s="52" t="inlineStr">
@@ -17539,7 +17535,7 @@
       </c>
       <c r="C31" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D31" s="52" t="inlineStr">
@@ -17549,7 +17545,7 @@
       </c>
       <c r="E31" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語乙</t>
         </is>
       </c>
       <c r="F31" s="44" t="inlineStr">
@@ -17562,17 +17558,17 @@
     <row r="32" ht="15" customHeight="1" s="36">
       <c r="A32" s="52" t="inlineStr">
         <is>
-          <t>3年5班</t>
+          <t>4年5班</t>
         </is>
       </c>
       <c r="B32" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C32" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D32" s="52" t="inlineStr">
@@ -17582,7 +17578,7 @@
       </c>
       <c r="E32" s="44" t="inlineStr">
         <is>
-          <t>本土語丙</t>
+          <t>閩南語乙</t>
         </is>
       </c>
       <c r="F32" s="44" t="inlineStr">
@@ -17595,12 +17591,12 @@
     <row r="33" ht="15" customHeight="1" s="36">
       <c r="A33" s="52" t="inlineStr">
         <is>
-          <t>3年6班</t>
+          <t>5年5班</t>
         </is>
       </c>
       <c r="B33" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C33" s="52" t="inlineStr">
@@ -17615,7 +17611,7 @@
       </c>
       <c r="E33" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語乙</t>
         </is>
       </c>
       <c r="F33" s="44" t="inlineStr">
@@ -17628,17 +17624,17 @@
     <row r="34" ht="15" customHeight="1" s="36">
       <c r="A34" s="52" t="inlineStr">
         <is>
-          <t>3年7班</t>
+          <t>6年5班</t>
         </is>
       </c>
       <c r="B34" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C34" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D34" s="52" t="inlineStr">
@@ -17648,7 +17644,7 @@
       </c>
       <c r="E34" s="44" t="inlineStr">
         <is>
-          <t>本土語乙</t>
+          <t>閩南語乙</t>
         </is>
       </c>
       <c r="F34" s="44" t="inlineStr">
@@ -17661,7 +17657,7 @@
     <row r="35" ht="15" customHeight="1" s="36">
       <c r="A35" s="52" t="inlineStr">
         <is>
-          <t>3年8班</t>
+          <t>1年6班</t>
         </is>
       </c>
       <c r="B35" s="52" t="inlineStr">
@@ -17671,7 +17667,7 @@
       </c>
       <c r="C35" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D35" s="52" t="inlineStr">
@@ -17681,7 +17677,7 @@
       </c>
       <c r="E35" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語乙</t>
         </is>
       </c>
       <c r="F35" s="44" t="inlineStr">
@@ -17694,17 +17690,17 @@
     <row r="36" ht="15" customHeight="1" s="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
-          <t>3年9班</t>
+          <t>2年6班</t>
         </is>
       </c>
       <c r="B36" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C36" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D36" s="52" t="inlineStr">
@@ -17714,7 +17710,7 @@
       </c>
       <c r="E36" s="44" t="inlineStr">
         <is>
-          <t>本土語丙</t>
+          <t>閩南語乙</t>
         </is>
       </c>
       <c r="F36" s="44" t="inlineStr">
@@ -17727,17 +17723,17 @@
     <row r="37" ht="15" customHeight="1" s="36">
       <c r="A37" s="52" t="inlineStr">
         <is>
-          <t>3年10班</t>
+          <t>3年6班</t>
         </is>
       </c>
       <c r="B37" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C37" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D37" s="52" t="inlineStr">
@@ -17747,7 +17743,7 @@
       </c>
       <c r="E37" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語乙</t>
         </is>
       </c>
       <c r="F37" s="44" t="inlineStr">
@@ -17760,27 +17756,27 @@
     <row r="38" ht="15" customHeight="1" s="36">
       <c r="A38" s="52" t="inlineStr">
         <is>
-          <t>3年11班</t>
+          <t>4年6班</t>
         </is>
       </c>
       <c r="B38" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C38" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D38" s="52" t="inlineStr">
         <is>
-          <t>新住民語</t>
+          <t>閩南語</t>
         </is>
       </c>
       <c r="E38" s="44" t="inlineStr">
         <is>
-          <t>本土語乙</t>
+          <t>閩南語乙</t>
         </is>
       </c>
       <c r="F38" s="44" t="inlineStr">
@@ -17793,17 +17789,17 @@
     <row r="39" ht="15" customHeight="1" s="36">
       <c r="A39" s="52" t="inlineStr">
         <is>
-          <t>3年12班</t>
+          <t>5年6班</t>
         </is>
       </c>
       <c r="B39" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C39" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D39" s="52" t="inlineStr">
@@ -17813,7 +17809,7 @@
       </c>
       <c r="E39" s="44" t="inlineStr">
         <is>
-          <t>本土語丙</t>
+          <t>閩南語乙</t>
         </is>
       </c>
       <c r="F39" s="44" t="inlineStr">
@@ -17826,17 +17822,17 @@
     <row r="40" ht="15" customHeight="1" s="36">
       <c r="A40" s="52" t="inlineStr">
         <is>
-          <t>4年1班</t>
+          <t>6年6班</t>
         </is>
       </c>
       <c r="B40" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C40" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D40" s="52" t="inlineStr">
@@ -17846,7 +17842,7 @@
       </c>
       <c r="E40" s="44" t="inlineStr">
         <is>
-          <t>本土語丁</t>
+          <t>閩南語乙</t>
         </is>
       </c>
       <c r="F40" s="44" t="inlineStr">
@@ -17859,17 +17855,17 @@
     <row r="41" ht="15" customHeight="1" s="36">
       <c r="A41" s="52" t="inlineStr">
         <is>
-          <t>4年2班</t>
+          <t>1年7班</t>
         </is>
       </c>
       <c r="B41" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C41" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D41" s="52" t="inlineStr">
@@ -17879,7 +17875,7 @@
       </c>
       <c r="E41" s="44" t="inlineStr">
         <is>
-          <t>本土語丁</t>
+          <t>閩南語乙</t>
         </is>
       </c>
       <c r="F41" s="44" t="inlineStr">
@@ -17892,17 +17888,17 @@
     <row r="42" ht="15" customHeight="1" s="36">
       <c r="A42" s="52" t="inlineStr">
         <is>
-          <t>4年3班</t>
+          <t>2年7班</t>
         </is>
       </c>
       <c r="B42" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C42" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D42" s="52" t="inlineStr">
@@ -17912,7 +17908,7 @@
       </c>
       <c r="E42" s="44" t="inlineStr">
         <is>
-          <t>本土語丁</t>
+          <t>閩南語乙</t>
         </is>
       </c>
       <c r="F42" s="44" t="inlineStr">
@@ -17925,12 +17921,12 @@
     <row r="43" ht="15" customHeight="1" s="36">
       <c r="A43" s="52" t="inlineStr">
         <is>
-          <t>4年4班</t>
+          <t>3年7班</t>
         </is>
       </c>
       <c r="B43" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C43" s="52" t="inlineStr">
@@ -17945,7 +17941,7 @@
       </c>
       <c r="E43" s="44" t="inlineStr">
         <is>
-          <t>本土語丙</t>
+          <t>閩南語乙</t>
         </is>
       </c>
       <c r="F43" s="44" t="inlineStr">
@@ -17958,12 +17954,12 @@
     <row r="44" ht="15" customHeight="1" s="36">
       <c r="A44" s="52" t="inlineStr">
         <is>
-          <t>4年5班</t>
+          <t>4年7班</t>
         </is>
       </c>
       <c r="B44" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C44" s="52" t="inlineStr">
@@ -17978,7 +17974,7 @@
       </c>
       <c r="E44" s="44" t="inlineStr">
         <is>
-          <t>本土語乙</t>
+          <t>閩南語乙</t>
         </is>
       </c>
       <c r="F44" s="44" t="inlineStr">
@@ -17991,17 +17987,17 @@
     <row r="45" ht="15" customHeight="1" s="36">
       <c r="A45" s="52" t="inlineStr">
         <is>
-          <t>4年6班</t>
+          <t>5年7班</t>
         </is>
       </c>
       <c r="B45" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C45" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D45" s="52" t="inlineStr">
@@ -18011,7 +18007,7 @@
       </c>
       <c r="E45" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語乙</t>
         </is>
       </c>
       <c r="F45" s="44" t="inlineStr">
@@ -18024,17 +18020,17 @@
     <row r="46" ht="15" customHeight="1" s="36">
       <c r="A46" s="52" t="inlineStr">
         <is>
-          <t>4年7班</t>
+          <t>6年7班</t>
         </is>
       </c>
       <c r="B46" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C46" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D46" s="52" t="inlineStr">
@@ -18044,7 +18040,7 @@
       </c>
       <c r="E46" s="44" t="inlineStr">
         <is>
-          <t>本土語乙</t>
+          <t>閩南語乙</t>
         </is>
       </c>
       <c r="F46" s="44" t="inlineStr">
@@ -18057,17 +18053,17 @@
     <row r="47" ht="15" customHeight="1" s="36">
       <c r="A47" s="52" t="inlineStr">
         <is>
-          <t>4年8班</t>
+          <t>1年8班</t>
         </is>
       </c>
       <c r="B47" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C47" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D47" s="52" t="inlineStr">
@@ -18077,7 +18073,7 @@
       </c>
       <c r="E47" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語乙</t>
         </is>
       </c>
       <c r="F47" s="44" t="inlineStr">
@@ -18090,17 +18086,17 @@
     <row r="48" ht="15" customHeight="1" s="36">
       <c r="A48" s="52" t="inlineStr">
         <is>
-          <t>4年9班</t>
+          <t>2年8班</t>
         </is>
       </c>
       <c r="B48" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C48" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D48" s="52" t="inlineStr">
@@ -18110,7 +18106,7 @@
       </c>
       <c r="E48" s="44" t="inlineStr">
         <is>
-          <t>本土語乙</t>
+          <t>閩南語乙</t>
         </is>
       </c>
       <c r="F48" s="44" t="inlineStr">
@@ -18123,17 +18119,17 @@
     <row r="49" ht="15" customHeight="1" s="36">
       <c r="A49" s="52" t="inlineStr">
         <is>
-          <t>4年10班</t>
+          <t>3年8班</t>
         </is>
       </c>
       <c r="B49" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C49" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D49" s="52" t="inlineStr">
@@ -18143,7 +18139,7 @@
       </c>
       <c r="E49" s="44" t="inlineStr">
         <is>
-          <t>本土語丙</t>
+          <t>閩南語乙</t>
         </is>
       </c>
       <c r="F49" s="44" t="inlineStr">
@@ -18156,7 +18152,7 @@
     <row r="50" ht="15" customHeight="1" s="36">
       <c r="A50" s="52" t="inlineStr">
         <is>
-          <t>4年11班</t>
+          <t>4年8班</t>
         </is>
       </c>
       <c r="B50" s="52" t="inlineStr">
@@ -18166,17 +18162,17 @@
       </c>
       <c r="C50" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D50" s="52" t="inlineStr">
         <is>
-          <t>新住民語</t>
+          <t>閩南語</t>
         </is>
       </c>
       <c r="E50" s="44" t="inlineStr">
         <is>
-          <t>本土語乙</t>
+          <t>閩南語丙</t>
         </is>
       </c>
       <c r="F50" s="44" t="inlineStr">
@@ -18189,17 +18185,17 @@
     <row r="51" ht="15" customHeight="1" s="36">
       <c r="A51" s="52" t="inlineStr">
         <is>
-          <t>4年12班</t>
+          <t>5年8班</t>
         </is>
       </c>
       <c r="B51" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C51" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D51" s="52" t="inlineStr">
@@ -18209,7 +18205,7 @@
       </c>
       <c r="E51" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語丙</t>
         </is>
       </c>
       <c r="F51" s="44" t="inlineStr">
@@ -18222,7 +18218,7 @@
     <row r="52" ht="15" customHeight="1" s="36">
       <c r="A52" s="52" t="inlineStr">
         <is>
-          <t>5年1班</t>
+          <t>6年8班</t>
         </is>
       </c>
       <c r="B52" s="52" t="inlineStr">
@@ -18232,7 +18228,7 @@
       </c>
       <c r="C52" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D52" s="52" t="inlineStr">
@@ -18242,7 +18238,7 @@
       </c>
       <c r="E52" s="44" t="inlineStr">
         <is>
-          <t>本土語丙</t>
+          <t>閩南語丙</t>
         </is>
       </c>
       <c r="F52" s="44" t="inlineStr">
@@ -18255,17 +18251,17 @@
     <row r="53" ht="15" customHeight="1" s="36">
       <c r="A53" s="52" t="inlineStr">
         <is>
-          <t>5年2班</t>
+          <t>1年9班</t>
         </is>
       </c>
       <c r="B53" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C53" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D53" s="52" t="inlineStr">
@@ -18275,7 +18271,7 @@
       </c>
       <c r="E53" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語丙</t>
         </is>
       </c>
       <c r="F53" s="44" t="inlineStr">
@@ -18288,12 +18284,12 @@
     <row r="54" ht="15" customHeight="1" s="36">
       <c r="A54" s="52" t="inlineStr">
         <is>
-          <t>5年3班</t>
+          <t>2年9班</t>
         </is>
       </c>
       <c r="B54" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C54" s="52" t="inlineStr">
@@ -18308,7 +18304,7 @@
       </c>
       <c r="E54" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語丙</t>
         </is>
       </c>
       <c r="F54" s="44" t="inlineStr">
@@ -18321,27 +18317,27 @@
     <row r="55" ht="15" customHeight="1" s="36">
       <c r="A55" s="52" t="inlineStr">
         <is>
-          <t>5年4班</t>
+          <t>3年9班</t>
         </is>
       </c>
       <c r="B55" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C55" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D55" s="52" t="inlineStr">
         <is>
-          <t>客語</t>
+          <t>閩南語</t>
         </is>
       </c>
       <c r="E55" s="44" t="inlineStr">
         <is>
-          <t>本土語乙</t>
+          <t>閩南語丙</t>
         </is>
       </c>
       <c r="F55" s="44" t="inlineStr">
@@ -18354,17 +18350,17 @@
     <row r="56" ht="15" customHeight="1" s="36">
       <c r="A56" s="52" t="inlineStr">
         <is>
-          <t>5年5班</t>
+          <t>4年9班</t>
         </is>
       </c>
       <c r="B56" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C56" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D56" s="52" t="inlineStr">
@@ -18374,7 +18370,7 @@
       </c>
       <c r="E56" s="44" t="inlineStr">
         <is>
-          <t>本土語丁</t>
+          <t>閩南語丙</t>
         </is>
       </c>
       <c r="F56" s="44" t="inlineStr">
@@ -18387,27 +18383,27 @@
     <row r="57" ht="15" customHeight="1" s="36">
       <c r="A57" s="52" t="inlineStr">
         <is>
-          <t>5年6班</t>
+          <t>5年9班</t>
         </is>
       </c>
       <c r="B57" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C57" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D57" s="52" t="inlineStr">
         <is>
-          <t>客語</t>
+          <t>閩南語</t>
         </is>
       </c>
       <c r="E57" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語丙</t>
         </is>
       </c>
       <c r="F57" s="44" t="inlineStr">
@@ -18420,17 +18416,17 @@
     <row r="58" ht="15" customHeight="1" s="36">
       <c r="A58" s="52" t="inlineStr">
         <is>
-          <t>5年7班</t>
+          <t>6年9班</t>
         </is>
       </c>
       <c r="B58" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C58" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D58" s="52" t="inlineStr">
@@ -18440,7 +18436,7 @@
       </c>
       <c r="E58" s="44" t="inlineStr">
         <is>
-          <t>本土語丙</t>
+          <t>閩南語丙</t>
         </is>
       </c>
       <c r="F58" s="44" t="inlineStr">
@@ -18453,17 +18449,17 @@
     <row r="59" ht="15" customHeight="1" s="36">
       <c r="A59" s="52" t="inlineStr">
         <is>
-          <t>5年8班</t>
+          <t>1年10班</t>
         </is>
       </c>
       <c r="B59" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C59" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D59" s="52" t="inlineStr">
@@ -18473,7 +18469,7 @@
       </c>
       <c r="E59" s="44" t="inlineStr">
         <is>
-          <t>本土語戊</t>
+          <t>閩南語丙</t>
         </is>
       </c>
       <c r="F59" s="44" t="inlineStr">
@@ -18486,17 +18482,17 @@
     <row r="60" ht="15" customHeight="1" s="36">
       <c r="A60" s="52" t="inlineStr">
         <is>
-          <t>5年9班</t>
+          <t>2年10班</t>
         </is>
       </c>
       <c r="B60" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C60" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D60" s="52" t="inlineStr">
@@ -18506,7 +18502,7 @@
       </c>
       <c r="E60" s="44" t="inlineStr">
         <is>
-          <t>本土語乙</t>
+          <t>閩南語丙</t>
         </is>
       </c>
       <c r="F60" s="44" t="inlineStr">
@@ -18519,17 +18515,17 @@
     <row r="61" ht="15" customHeight="1" s="36">
       <c r="A61" s="52" t="inlineStr">
         <is>
-          <t>5年10班</t>
+          <t>3年10班</t>
         </is>
       </c>
       <c r="B61" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C61" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D61" s="52" t="inlineStr">
@@ -18539,7 +18535,7 @@
       </c>
       <c r="E61" s="44" t="inlineStr">
         <is>
-          <t>本土語丁</t>
+          <t>閩南語丙</t>
         </is>
       </c>
       <c r="F61" s="44" t="inlineStr">
@@ -18552,27 +18548,27 @@
     <row r="62" ht="15" customHeight="1" s="36">
       <c r="A62" s="52" t="inlineStr">
         <is>
-          <t>5年11班</t>
+          <t>4年10班</t>
         </is>
       </c>
       <c r="B62" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C62" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D62" s="52" t="inlineStr">
         <is>
-          <t>客語</t>
+          <t>閩南語</t>
         </is>
       </c>
       <c r="E62" s="44" t="inlineStr">
         <is>
-          <t>本土語乙</t>
+          <t>閩南語丙</t>
         </is>
       </c>
       <c r="F62" s="44" t="inlineStr">
@@ -18585,17 +18581,17 @@
     <row r="63" ht="15" customHeight="1" s="36">
       <c r="A63" s="52" t="inlineStr">
         <is>
-          <t>5年12班</t>
+          <t>5年10班</t>
         </is>
       </c>
       <c r="B63" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C63" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D63" s="52" t="inlineStr">
@@ -18605,7 +18601,7 @@
       </c>
       <c r="E63" s="44" t="inlineStr">
         <is>
-          <t>本土語甲</t>
+          <t>閩南語丙</t>
         </is>
       </c>
       <c r="F63" s="44" t="inlineStr">
@@ -18618,12 +18614,12 @@
     <row r="64" ht="15" customHeight="1" s="36">
       <c r="A64" s="52" t="inlineStr">
         <is>
-          <t>6年1班</t>
+          <t>6年10班</t>
         </is>
       </c>
       <c r="B64" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C64" s="52" t="inlineStr">
@@ -18638,7 +18634,7 @@
       </c>
       <c r="E64" s="44" t="inlineStr">
         <is>
-          <t>本土語戊</t>
+          <t>閩南語丙</t>
         </is>
       </c>
       <c r="F64" s="44" t="inlineStr">
@@ -18651,17 +18647,17 @@
     <row r="65" ht="15" customHeight="1" s="36">
       <c r="A65" s="52" t="inlineStr">
         <is>
-          <t>6年2班</t>
+          <t>1年11班</t>
         </is>
       </c>
       <c r="B65" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C65" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D65" s="52" t="inlineStr">
@@ -18671,7 +18667,7 @@
       </c>
       <c r="E65" s="44" t="inlineStr">
         <is>
-          <t>本土語丙</t>
+          <t>閩南語丙</t>
         </is>
       </c>
       <c r="F65" s="44" t="inlineStr">
@@ -18684,17 +18680,17 @@
     <row r="66" ht="15" customHeight="1" s="36">
       <c r="A66" s="52" t="inlineStr">
         <is>
-          <t>6年3班</t>
+          <t>2年11班</t>
         </is>
       </c>
       <c r="B66" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C66" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D66" s="52" t="inlineStr">
@@ -18704,7 +18700,7 @@
       </c>
       <c r="E66" s="44" t="inlineStr">
         <is>
-          <t>本土語丁</t>
+          <t>閩南語丙</t>
         </is>
       </c>
       <c r="F66" s="44" t="inlineStr">
@@ -18717,17 +18713,17 @@
     <row r="67" ht="15" customHeight="1" s="36">
       <c r="A67" s="52" t="inlineStr">
         <is>
-          <t>6年4班</t>
+          <t>3年11班</t>
         </is>
       </c>
       <c r="B67" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C67" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D67" s="52" t="inlineStr">
@@ -18737,7 +18733,7 @@
       </c>
       <c r="E67" s="44" t="inlineStr">
         <is>
-          <t>本土語丁</t>
+          <t>閩南語丙</t>
         </is>
       </c>
       <c r="F67" s="44" t="inlineStr">
@@ -18750,17 +18746,17 @@
     <row r="68" ht="15" customHeight="1" s="36">
       <c r="A68" s="52" t="inlineStr">
         <is>
-          <t>6年5班</t>
+          <t>4年11班</t>
         </is>
       </c>
       <c r="B68" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C68" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D68" s="52" t="inlineStr">
@@ -18770,7 +18766,7 @@
       </c>
       <c r="E68" s="44" t="inlineStr">
         <is>
-          <t>本土語乙</t>
+          <t>閩南語丙</t>
         </is>
       </c>
       <c r="F68" s="44" t="inlineStr">
@@ -18783,7 +18779,7 @@
     <row r="69" ht="15" customHeight="1" s="36">
       <c r="A69" s="52" t="inlineStr">
         <is>
-          <t>6年6班</t>
+          <t>5年11班</t>
         </is>
       </c>
       <c r="B69" s="52" t="inlineStr">
@@ -18793,7 +18789,7 @@
       </c>
       <c r="C69" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D69" s="52" t="inlineStr">
@@ -18803,7 +18799,7 @@
       </c>
       <c r="E69" s="44" t="inlineStr">
         <is>
-          <t>本土語丙</t>
+          <t>閩南語丙</t>
         </is>
       </c>
       <c r="F69" s="44" t="inlineStr">
@@ -18816,7 +18812,7 @@
     <row r="70" ht="15" customHeight="1" s="36">
       <c r="A70" s="52" t="inlineStr">
         <is>
-          <t>6年7班</t>
+          <t>6年11班</t>
         </is>
       </c>
       <c r="B70" s="52" t="inlineStr">
@@ -18826,7 +18822,7 @@
       </c>
       <c r="C70" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D70" s="52" t="inlineStr">
@@ -18836,7 +18832,7 @@
       </c>
       <c r="E70" s="44" t="inlineStr">
         <is>
-          <t>本土語丙</t>
+          <t>閩南語丙</t>
         </is>
       </c>
       <c r="F70" s="44" t="inlineStr">
@@ -18849,12 +18845,12 @@
     <row r="71" ht="15" customHeight="1" s="36">
       <c r="A71" s="52" t="inlineStr">
         <is>
-          <t>6年8班</t>
+          <t>1年12班</t>
         </is>
       </c>
       <c r="B71" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C71" s="52" t="inlineStr">
@@ -18869,7 +18865,7 @@
       </c>
       <c r="E71" s="44" t="inlineStr">
         <is>
-          <t>本土語丁</t>
+          <t>閩南語丁</t>
         </is>
       </c>
       <c r="F71" s="44" t="inlineStr">
@@ -18882,27 +18878,27 @@
     <row r="72" ht="15" customHeight="1" s="36">
       <c r="A72" s="52" t="inlineStr">
         <is>
-          <t>6年9班</t>
+          <t>3年12班</t>
         </is>
       </c>
       <c r="B72" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C72" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D72" s="52" t="inlineStr">
         <is>
-          <t>客語</t>
+          <t>閩南語</t>
         </is>
       </c>
       <c r="E72" s="44" t="inlineStr">
         <is>
-          <t>本土語乙</t>
+          <t>閩南語丁</t>
         </is>
       </c>
       <c r="F72" s="44" t="inlineStr">
@@ -18915,17 +18911,17 @@
     <row r="73" ht="15" customHeight="1" s="36">
       <c r="A73" s="52" t="inlineStr">
         <is>
-          <t>6年10班</t>
+          <t>4年12班</t>
         </is>
       </c>
       <c r="B73" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C73" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D73" s="52" t="inlineStr">
@@ -18935,7 +18931,7 @@
       </c>
       <c r="E73" s="44" t="inlineStr">
         <is>
-          <t>本土語丙</t>
+          <t>閩南語丁</t>
         </is>
       </c>
       <c r="F73" s="44" t="inlineStr">
@@ -18948,27 +18944,27 @@
     <row r="74" ht="15" customHeight="1" s="36">
       <c r="A74" s="52" t="inlineStr">
         <is>
-          <t>6年11班</t>
+          <t>5年12班</t>
         </is>
       </c>
       <c r="B74" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C74" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D74" s="52" t="inlineStr">
         <is>
-          <t>客語</t>
+          <t>閩南語</t>
         </is>
       </c>
       <c r="E74" s="44" t="inlineStr">
         <is>
-          <t>本土語戊</t>
+          <t>英語乙</t>
         </is>
       </c>
       <c r="F74" s="44" t="inlineStr">
@@ -18976,7 +18972,11 @@
           <t>原班教室</t>
         </is>
       </c>
-      <c r="G74" s="44" t="n"/>
+      <c r="G74" s="44" t="inlineStr">
+        <is>
+          <t>（試跑）科任兼本土語</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="36">
       <c r="A75" s="52" t="inlineStr">
@@ -18986,120 +18986,404 @@
       </c>
       <c r="B75" s="52" t="inlineStr">
         <is>
+          <t>一</t>
+        </is>
+      </c>
+      <c r="C75" s="52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D75" s="52" t="inlineStr">
+        <is>
+          <t>閩南語</t>
+        </is>
+      </c>
+      <c r="E75" s="44" t="inlineStr">
+        <is>
+          <t>英語乙</t>
+        </is>
+      </c>
+      <c r="F75" s="44" t="inlineStr">
+        <is>
+          <t>原班教室</t>
+        </is>
+      </c>
+      <c r="G75" s="44" t="inlineStr">
+        <is>
+          <t>（試跑）科任兼本土語</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1" s="36">
+      <c r="A76" s="52" t="inlineStr">
+        <is>
+          <t>6年3班</t>
+        </is>
+      </c>
+      <c r="B76" s="52" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="C76" s="52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D76" s="52" t="inlineStr">
+        <is>
+          <t>新住民語</t>
+        </is>
+      </c>
+      <c r="E76" s="44" t="inlineStr">
+        <is>
+          <t>新住民語甲</t>
+        </is>
+      </c>
+      <c r="F76" s="44" t="inlineStr">
+        <is>
+          <t>本土語教室</t>
+        </is>
+      </c>
+      <c r="G76" s="44" t="inlineStr">
+        <is>
+          <t>分組上課</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1" s="36">
+      <c r="A77" s="52" t="inlineStr">
+        <is>
+          <t>1年2班</t>
+        </is>
+      </c>
+      <c r="B77" s="52" t="inlineStr">
+        <is>
+          <t>四</t>
+        </is>
+      </c>
+      <c r="C77" s="52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D77" s="52" t="inlineStr">
+        <is>
+          <t>客語</t>
+        </is>
+      </c>
+      <c r="E77" s="44" t="inlineStr">
+        <is>
+          <t>客語甲</t>
+        </is>
+      </c>
+      <c r="F77" s="44" t="inlineStr">
+        <is>
+          <t>本土語教室</t>
+        </is>
+      </c>
+      <c r="G77" s="44" t="inlineStr">
+        <is>
+          <t>分組上課</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1" s="36">
+      <c r="A78" s="52" t="inlineStr">
+        <is>
+          <t>6年11班</t>
+        </is>
+      </c>
+      <c r="B78" s="52" t="inlineStr">
+        <is>
+          <t>一</t>
+        </is>
+      </c>
+      <c r="C78" s="52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D78" s="52" t="inlineStr">
+        <is>
+          <t>客語</t>
+        </is>
+      </c>
+      <c r="E78" s="44" t="inlineStr">
+        <is>
+          <t>客語甲</t>
+        </is>
+      </c>
+      <c r="F78" s="44" t="inlineStr">
+        <is>
+          <t>本土語教室</t>
+        </is>
+      </c>
+      <c r="G78" s="44" t="inlineStr">
+        <is>
+          <t>分組上課</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1" s="36">
+      <c r="A79" s="52" t="inlineStr">
+        <is>
+          <t>2年7班</t>
+        </is>
+      </c>
+      <c r="B79" s="52" t="inlineStr">
+        <is>
           <t>二</t>
         </is>
       </c>
-      <c r="C75" s="52" t="inlineStr">
+      <c r="C79" s="52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D79" s="52" t="inlineStr">
+        <is>
+          <t>客語</t>
+        </is>
+      </c>
+      <c r="E79" s="44" t="inlineStr">
+        <is>
+          <t>客語甲</t>
+        </is>
+      </c>
+      <c r="F79" s="44" t="inlineStr">
+        <is>
+          <t>本土語教室</t>
+        </is>
+      </c>
+      <c r="G79" s="44" t="inlineStr">
+        <is>
+          <t>分組上課</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1" s="36">
+      <c r="A80" s="52" t="inlineStr">
+        <is>
+          <t>6年9班</t>
+        </is>
+      </c>
+      <c r="B80" s="52" t="inlineStr">
+        <is>
+          <t>二</t>
+        </is>
+      </c>
+      <c r="C80" s="52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D80" s="52" t="inlineStr">
+        <is>
+          <t>客語</t>
+        </is>
+      </c>
+      <c r="E80" s="44" t="inlineStr">
+        <is>
+          <t>客語甲</t>
+        </is>
+      </c>
+      <c r="F80" s="44" t="inlineStr">
+        <is>
+          <t>本土語教室</t>
+        </is>
+      </c>
+      <c r="G80" s="44" t="inlineStr">
+        <is>
+          <t>分組上課</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="15" customHeight="1" s="36">
+      <c r="A81" s="52" t="inlineStr">
+        <is>
+          <t>1年9班</t>
+        </is>
+      </c>
+      <c r="B81" s="52" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="C81" s="52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D81" s="52" t="inlineStr">
+        <is>
+          <t>客語</t>
+        </is>
+      </c>
+      <c r="E81" s="44" t="inlineStr">
+        <is>
+          <t>客語甲</t>
+        </is>
+      </c>
+      <c r="F81" s="44" t="inlineStr">
+        <is>
+          <t>本土語教室</t>
+        </is>
+      </c>
+      <c r="G81" s="44" t="inlineStr">
+        <is>
+          <t>分組上課</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="15" customHeight="1" s="36">
+      <c r="A82" s="52" t="inlineStr">
+        <is>
+          <t>6年6班</t>
+        </is>
+      </c>
+      <c r="B82" s="52" t="inlineStr">
+        <is>
+          <t>二</t>
+        </is>
+      </c>
+      <c r="C82" s="52" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D75" s="52" t="inlineStr">
-        <is>
-          <t>閩南語</t>
-        </is>
-      </c>
-      <c r="E75" s="44" t="inlineStr">
-        <is>
-          <t>本土語丁</t>
-        </is>
-      </c>
-      <c r="F75" s="44" t="inlineStr">
-        <is>
-          <t>原班教室</t>
-        </is>
-      </c>
-      <c r="G75" s="44" t="n"/>
-    </row>
-    <row r="76" ht="15" customHeight="1" s="36">
-      <c r="A76" s="52" t="n"/>
-      <c r="B76" s="52" t="n"/>
-      <c r="C76" s="52" t="n"/>
-      <c r="D76" s="52" t="n"/>
-      <c r="E76" s="44" t="n"/>
-      <c r="F76" s="44" t="n"/>
-      <c r="G76" s="44" t="n"/>
-    </row>
-    <row r="77" ht="15" customHeight="1" s="36">
-      <c r="A77" s="52" t="n"/>
-      <c r="B77" s="52" t="n"/>
-      <c r="C77" s="52" t="n"/>
-      <c r="D77" s="52" t="n"/>
-      <c r="E77" s="44" t="n"/>
-      <c r="F77" s="44" t="n"/>
-      <c r="G77" s="44" t="n"/>
-    </row>
-    <row r="78" ht="15" customHeight="1" s="36">
-      <c r="A78" s="52" t="n"/>
-      <c r="B78" s="52" t="n"/>
-      <c r="C78" s="52" t="n"/>
-      <c r="D78" s="52" t="n"/>
-      <c r="E78" s="44" t="n"/>
-      <c r="F78" s="44" t="n"/>
-      <c r="G78" s="44" t="n"/>
-    </row>
-    <row r="79" ht="15" customHeight="1" s="36">
-      <c r="A79" s="52" t="n"/>
-      <c r="B79" s="52" t="n"/>
-      <c r="C79" s="52" t="n"/>
-      <c r="D79" s="52" t="n"/>
-      <c r="E79" s="44" t="n"/>
-      <c r="F79" s="44" t="n"/>
-      <c r="G79" s="44" t="n"/>
-    </row>
-    <row r="80" ht="15" customHeight="1" s="36">
-      <c r="A80" s="52" t="n"/>
-      <c r="B80" s="52" t="n"/>
-      <c r="C80" s="52" t="n"/>
-      <c r="D80" s="52" t="n"/>
-      <c r="E80" s="44" t="n"/>
-      <c r="F80" s="44" t="n"/>
-      <c r="G80" s="44" t="n"/>
-    </row>
-    <row r="81" ht="15" customHeight="1" s="36">
-      <c r="A81" s="52" t="n"/>
-      <c r="B81" s="52" t="n"/>
-      <c r="C81" s="52" t="n"/>
-      <c r="D81" s="52" t="n"/>
-      <c r="E81" s="44" t="n"/>
-      <c r="F81" s="44" t="n"/>
-      <c r="G81" s="44" t="n"/>
-    </row>
-    <row r="82" ht="15" customHeight="1" s="36">
-      <c r="A82" s="52" t="n"/>
-      <c r="B82" s="52" t="n"/>
-      <c r="C82" s="52" t="n"/>
-      <c r="D82" s="52" t="n"/>
-      <c r="E82" s="44" t="n"/>
-      <c r="F82" s="44" t="n"/>
-      <c r="G82" s="44" t="n"/>
+      <c r="D82" s="52" t="inlineStr">
+        <is>
+          <t>族語</t>
+        </is>
+      </c>
+      <c r="E82" s="44" t="inlineStr">
+        <is>
+          <t>族語甲</t>
+        </is>
+      </c>
+      <c r="F82" s="44" t="inlineStr">
+        <is>
+          <t>本土語教室</t>
+        </is>
+      </c>
+      <c r="G82" s="44" t="inlineStr">
+        <is>
+          <t>分組上課</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="36">
-      <c r="A83" s="52" t="n"/>
-      <c r="B83" s="52" t="n"/>
-      <c r="C83" s="52" t="n"/>
-      <c r="D83" s="52" t="n"/>
-      <c r="E83" s="44" t="n"/>
-      <c r="F83" s="44" t="n"/>
-      <c r="G83" s="44" t="n"/>
+      <c r="A83" s="52" t="inlineStr">
+        <is>
+          <t>3年12班</t>
+        </is>
+      </c>
+      <c r="B83" s="52" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C83" s="52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D83" s="52" t="inlineStr">
+        <is>
+          <t>客語</t>
+        </is>
+      </c>
+      <c r="E83" s="44" t="inlineStr">
+        <is>
+          <t>客語甲</t>
+        </is>
+      </c>
+      <c r="F83" s="44" t="inlineStr">
+        <is>
+          <t>本土語教室</t>
+        </is>
+      </c>
+      <c r="G83" s="44" t="inlineStr">
+        <is>
+          <t>分組上課</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="36">
-      <c r="A84" s="52" t="n"/>
-      <c r="B84" s="52" t="n"/>
-      <c r="C84" s="52" t="n"/>
-      <c r="D84" s="52" t="n"/>
-      <c r="E84" s="44" t="n"/>
-      <c r="F84" s="44" t="n"/>
-      <c r="G84" s="44" t="n"/>
+      <c r="A84" s="52" t="inlineStr">
+        <is>
+          <t>6年4班</t>
+        </is>
+      </c>
+      <c r="B84" s="52" t="inlineStr">
+        <is>
+          <t>一</t>
+        </is>
+      </c>
+      <c r="C84" s="52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D84" s="52" t="inlineStr">
+        <is>
+          <t>族語</t>
+        </is>
+      </c>
+      <c r="E84" s="44" t="inlineStr">
+        <is>
+          <t>族語甲</t>
+        </is>
+      </c>
+      <c r="F84" s="44" t="inlineStr">
+        <is>
+          <t>本土語教室</t>
+        </is>
+      </c>
+      <c r="G84" s="44" t="inlineStr">
+        <is>
+          <t>分組上課</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="36">
-      <c r="A85" s="52" t="n"/>
-      <c r="B85" s="52" t="n"/>
-      <c r="C85" s="52" t="n"/>
-      <c r="D85" s="52" t="n"/>
-      <c r="E85" s="44" t="n"/>
-      <c r="F85" s="44" t="n"/>
-      <c r="G85" s="44" t="n"/>
+      <c r="A85" s="52" t="inlineStr">
+        <is>
+          <t>1年11班</t>
+        </is>
+      </c>
+      <c r="B85" s="52" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C85" s="52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D85" s="52" t="inlineStr">
+        <is>
+          <t>族語</t>
+        </is>
+      </c>
+      <c r="E85" s="44" t="inlineStr">
+        <is>
+          <t>族語甲</t>
+        </is>
+      </c>
+      <c r="F85" s="44" t="inlineStr">
+        <is>
+          <t>本土語教室</t>
+        </is>
+      </c>
+      <c r="G85" s="44" t="inlineStr">
+        <is>
+          <t>分組上課</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="36">
       <c r="A86" s="52" t="n"/>
@@ -19872,22 +20156,22 @@
       </c>
       <c r="B5" s="52" t="inlineStr">
         <is>
-          <t>6年1班</t>
+          <t>4年10班</t>
         </is>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>國語</t>
+          <t>數學</t>
         </is>
       </c>
       <c r="D5" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>二</t>
         </is>
       </c>
       <c r="E5" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F5" s="44" t="inlineStr">
@@ -19908,12 +20192,12 @@
       </c>
       <c r="B6" s="52" t="inlineStr">
         <is>
-          <t>5年5班</t>
+          <t>6年3班</t>
         </is>
       </c>
       <c r="C6" s="44" t="inlineStr">
         <is>
-          <t>國語</t>
+          <t>數學</t>
         </is>
       </c>
       <c r="D6" s="52" t="inlineStr">
@@ -19923,7 +20207,7 @@
       </c>
       <c r="E6" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F6" s="44" t="inlineStr">
@@ -19932,7 +20216,7 @@
         </is>
       </c>
       <c r="G6" s="44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" s="44" t="n"/>
     </row>
@@ -19944,12 +20228,12 @@
       </c>
       <c r="B7" s="52" t="inlineStr">
         <is>
-          <t>2年6班</t>
+          <t>4年11班</t>
         </is>
       </c>
       <c r="C7" s="44" t="inlineStr">
         <is>
-          <t>數學</t>
+          <t>國語</t>
         </is>
       </c>
       <c r="D7" s="52" t="inlineStr">
@@ -19968,7 +20252,7 @@
         </is>
       </c>
       <c r="G7" s="44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H7" s="44" t="n"/>
     </row>
@@ -19980,22 +20264,22 @@
       </c>
       <c r="B8" s="52" t="inlineStr">
         <is>
-          <t>3年10班</t>
+          <t>3年1班</t>
         </is>
       </c>
       <c r="C8" s="44" t="inlineStr">
         <is>
-          <t>數學</t>
+          <t>國語</t>
         </is>
       </c>
       <c r="D8" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>一</t>
         </is>
       </c>
       <c r="E8" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F8" s="44" t="inlineStr">
@@ -20004,7 +20288,7 @@
         </is>
       </c>
       <c r="G8" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="44" t="n"/>
     </row>
@@ -20016,7 +20300,7 @@
       </c>
       <c r="B9" s="52" t="inlineStr">
         <is>
-          <t>5年4班</t>
+          <t>3年7班</t>
         </is>
       </c>
       <c r="C9" s="44" t="inlineStr">
@@ -20026,12 +20310,12 @@
       </c>
       <c r="D9" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>五</t>
         </is>
       </c>
       <c r="E9" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F9" s="44" t="inlineStr">
@@ -20052,7 +20336,7 @@
       </c>
       <c r="B10" s="52" t="inlineStr">
         <is>
-          <t>4年1班</t>
+          <t>4年5班</t>
         </is>
       </c>
       <c r="C10" s="44" t="inlineStr">
@@ -20062,7 +20346,7 @@
       </c>
       <c r="D10" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>五</t>
         </is>
       </c>
       <c r="E10" s="52" t="inlineStr">
@@ -20076,7 +20360,7 @@
         </is>
       </c>
       <c r="G10" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" s="44" t="n"/>
     </row>
@@ -20088,7 +20372,7 @@
       </c>
       <c r="B11" s="52" t="inlineStr">
         <is>
-          <t>4年8班</t>
+          <t>4年12班</t>
         </is>
       </c>
       <c r="C11" s="44" t="inlineStr">
@@ -20098,12 +20382,12 @@
       </c>
       <c r="D11" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>一</t>
         </is>
       </c>
       <c r="E11" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F11" s="44" t="inlineStr">
@@ -20112,7 +20396,7 @@
         </is>
       </c>
       <c r="G11" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="44" t="n"/>
     </row>
@@ -20124,7 +20408,7 @@
       </c>
       <c r="B12" s="52" t="inlineStr">
         <is>
-          <t>6年7班</t>
+          <t>5年3班</t>
         </is>
       </c>
       <c r="C12" s="44" t="inlineStr">
@@ -20134,12 +20418,12 @@
       </c>
       <c r="D12" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>二</t>
         </is>
       </c>
       <c r="E12" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F12" s="44" t="inlineStr">
@@ -20148,7 +20432,7 @@
         </is>
       </c>
       <c r="G12" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="44" t="n"/>
     </row>
@@ -20160,22 +20444,22 @@
       </c>
       <c r="B13" s="52" t="inlineStr">
         <is>
-          <t>4年5班</t>
+          <t>6年6班</t>
         </is>
       </c>
       <c r="C13" s="44" t="inlineStr">
         <is>
-          <t>數學</t>
+          <t>國語</t>
         </is>
       </c>
       <c r="D13" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>四</t>
         </is>
       </c>
       <c r="E13" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F13" s="44" t="inlineStr">
@@ -20196,12 +20480,12 @@
       </c>
       <c r="B14" s="52" t="inlineStr">
         <is>
-          <t>2年1班</t>
+          <t>4年9班</t>
         </is>
       </c>
       <c r="C14" s="44" t="inlineStr">
         <is>
-          <t>數學</t>
+          <t>國語</t>
         </is>
       </c>
       <c r="D14" s="52" t="inlineStr">
@@ -20211,7 +20495,7 @@
       </c>
       <c r="E14" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F14" s="44" t="inlineStr">
@@ -20220,7 +20504,7 @@
         </is>
       </c>
       <c r="G14" s="44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" s="44" t="n"/>
     </row>
@@ -24086,27 +24370,27 @@
     <row r="5" ht="15" customHeight="1" s="36">
       <c r="A5" s="44" t="inlineStr">
         <is>
-          <t>英語丁</t>
+          <t>體育甲</t>
         </is>
       </c>
       <c r="B5" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C5" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="D5" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>希望</t>
         </is>
       </c>
       <c r="E5" s="44" t="inlineStr">
         <is>
-          <t>兼任行政會議</t>
+          <t>接送小孩</t>
         </is>
       </c>
       <c r="F5" s="56">
@@ -24117,7 +24401,7 @@
     <row r="6" ht="15" customHeight="1" s="36">
       <c r="A6" s="44" t="inlineStr">
         <is>
-          <t>英語丁</t>
+          <t>體育甲</t>
         </is>
       </c>
       <c r="B6" s="52" t="inlineStr">
@@ -24127,19 +24411,15 @@
       </c>
       <c r="C6" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E6" s="44" t="inlineStr">
-        <is>
-          <t>接送小孩</t>
-        </is>
-      </c>
+          <t>希望</t>
+        </is>
+      </c>
+      <c r="E6" s="44" t="n"/>
       <c r="F6" s="56">
         <f>IF(A6="","",COUNTIFS($A$5:$A$304,A6,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24148,17 +24428,17 @@
     <row r="7" ht="15" customHeight="1" s="36">
       <c r="A7" s="44" t="inlineStr">
         <is>
-          <t>英語丁</t>
+          <t>自然戊</t>
         </is>
       </c>
       <c r="B7" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C7" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D7" s="52" t="inlineStr">
@@ -24168,7 +24448,7 @@
       </c>
       <c r="E7" s="44" t="inlineStr">
         <is>
-          <t>接送小孩</t>
+          <t>身體因素</t>
         </is>
       </c>
       <c r="F7" s="56">
@@ -24179,29 +24459,25 @@
     <row r="8" ht="15" customHeight="1" s="36">
       <c r="A8" s="44" t="inlineStr">
         <is>
-          <t>資訊甲</t>
+          <t>自然戊</t>
         </is>
       </c>
       <c r="B8" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C8" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E8" s="44" t="inlineStr">
-        <is>
-          <t>身體因素</t>
-        </is>
-      </c>
+          <t>希望</t>
+        </is>
+      </c>
+      <c r="E8" s="44" t="n"/>
       <c r="F8" s="56">
         <f>IF(A8="","",COUNTIFS($A$5:$A$304,A8,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24210,17 +24486,17 @@
     <row r="9" ht="15" customHeight="1" s="36">
       <c r="A9" s="44" t="inlineStr">
         <is>
-          <t>資訊甲</t>
+          <t>社會乙</t>
         </is>
       </c>
       <c r="B9" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C9" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="D9" s="52" t="inlineStr">
@@ -24228,7 +24504,11 @@
           <t>希望</t>
         </is>
       </c>
-      <c r="E9" s="44" t="n"/>
+      <c r="E9" s="44" t="inlineStr">
+        <is>
+          <t>接送小孩</t>
+        </is>
+      </c>
       <c r="F9" s="56">
         <f>IF(A9="","",COUNTIFS($A$5:$A$304,A9,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24237,22 +24517,22 @@
     <row r="10" ht="15" customHeight="1" s="36">
       <c r="A10" s="44" t="inlineStr">
         <is>
-          <t>體育甲</t>
+          <t>社會乙</t>
         </is>
       </c>
       <c r="B10" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C10" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>希望</t>
         </is>
       </c>
       <c r="E10" s="44" t="n"/>
@@ -24264,12 +24544,12 @@
     <row r="11" ht="15" customHeight="1" s="36">
       <c r="A11" s="44" t="inlineStr">
         <is>
-          <t>體育甲</t>
+          <t>音樂戊</t>
         </is>
       </c>
       <c r="B11" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C11" s="52" t="inlineStr">
@@ -24284,7 +24564,7 @@
       </c>
       <c r="E11" s="44" t="inlineStr">
         <is>
-          <t>兼任行政會議</t>
+          <t>接送小孩</t>
         </is>
       </c>
       <c r="F11" s="56">
@@ -24295,27 +24575,27 @@
     <row r="12" ht="15" customHeight="1" s="36">
       <c r="A12" s="44" t="inlineStr">
         <is>
-          <t>體育甲</t>
+          <t>音樂戊</t>
         </is>
       </c>
       <c r="B12" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C12" s="52" t="inlineStr">
         <is>
-          <t>下午</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="52" t="inlineStr">
         <is>
-          <t>希望</t>
+          <t>必須</t>
         </is>
       </c>
       <c r="E12" s="44" t="inlineStr">
         <is>
-          <t>接送小孩</t>
+          <t>進修</t>
         </is>
       </c>
       <c r="F12" s="56">
@@ -24326,25 +24606,29 @@
     <row r="13" ht="15" customHeight="1" s="36">
       <c r="A13" s="44" t="inlineStr">
         <is>
-          <t>體育甲</t>
+          <t>體育乙</t>
         </is>
       </c>
       <c r="B13" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C13" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D13" s="52" t="inlineStr">
         <is>
-          <t>希望</t>
-        </is>
-      </c>
-      <c r="E13" s="44" t="n"/>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E13" s="44" t="inlineStr">
+        <is>
+          <t>兼任行政會議</t>
+        </is>
+      </c>
       <c r="F13" s="56">
         <f>IF(A13="","",COUNTIFS($A$5:$A$304,A13,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24353,27 +24637,27 @@
     <row r="14" ht="15" customHeight="1" s="36">
       <c r="A14" s="44" t="inlineStr">
         <is>
-          <t>英語甲</t>
+          <t>體育乙</t>
         </is>
       </c>
       <c r="B14" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C14" s="52" t="inlineStr">
         <is>
-          <t>下午</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" s="52" t="inlineStr">
         <is>
-          <t>希望</t>
+          <t>必須</t>
         </is>
       </c>
       <c r="E14" s="44" t="inlineStr">
         <is>
-          <t>接送小孩</t>
+          <t>兼任行政會議</t>
         </is>
       </c>
       <c r="F14" s="56">
@@ -24384,17 +24668,17 @@
     <row r="15" ht="15" customHeight="1" s="36">
       <c r="A15" s="44" t="inlineStr">
         <is>
-          <t>資訊乙</t>
+          <t>體育乙</t>
         </is>
       </c>
       <c r="B15" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C15" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D15" s="52" t="inlineStr">
@@ -24402,11 +24686,7 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="E15" s="44" t="inlineStr">
-        <is>
-          <t>接送小孩</t>
-        </is>
-      </c>
+      <c r="E15" s="44" t="n"/>
       <c r="F15" s="56">
         <f>IF(A15="","",COUNTIFS($A$5:$A$304,A15,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24415,7 +24695,7 @@
     <row r="16" ht="15" customHeight="1" s="36">
       <c r="A16" s="44" t="inlineStr">
         <is>
-          <t>資訊乙</t>
+          <t>體育乙</t>
         </is>
       </c>
       <c r="B16" s="52" t="inlineStr">
@@ -24425,17 +24705,17 @@
       </c>
       <c r="C16" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="D16" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>希望</t>
         </is>
       </c>
       <c r="E16" s="44" t="inlineStr">
         <is>
-          <t>進修</t>
+          <t>接送小孩</t>
         </is>
       </c>
       <c r="F16" s="56">
@@ -24446,12 +24726,12 @@
     <row r="17" ht="15" customHeight="1" s="36">
       <c r="A17" s="44" t="inlineStr">
         <is>
-          <t>資訊乙</t>
+          <t>體育乙</t>
         </is>
       </c>
       <c r="B17" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C17" s="52" t="inlineStr">
@@ -24473,17 +24753,17 @@
     <row r="18" ht="15" customHeight="1" s="36">
       <c r="A18" s="44" t="inlineStr">
         <is>
-          <t>社會甲</t>
+          <t>自然乙</t>
         </is>
       </c>
       <c r="B18" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C18" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D18" s="52" t="inlineStr">
@@ -24491,7 +24771,11 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="E18" s="44" t="n"/>
+      <c r="E18" s="44" t="inlineStr">
+        <is>
+          <t>進修</t>
+        </is>
+      </c>
       <c r="F18" s="56">
         <f>IF(A18="","",COUNTIFS($A$5:$A$304,A18,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24500,17 +24784,17 @@
     <row r="19" ht="15" customHeight="1" s="36">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>社會甲</t>
+          <t>自然乙</t>
         </is>
       </c>
       <c r="B19" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C19" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D19" s="52" t="inlineStr">
@@ -24518,7 +24802,11 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="E19" s="44" t="n"/>
+      <c r="E19" s="44" t="inlineStr">
+        <is>
+          <t>兼任行政會議</t>
+        </is>
+      </c>
       <c r="F19" s="56">
         <f>IF(A19="","",COUNTIFS($A$5:$A$304,A19,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24527,29 +24815,25 @@
     <row r="20" ht="15" customHeight="1" s="36">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>社會甲</t>
+          <t>體育丙</t>
         </is>
       </c>
       <c r="B20" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C20" s="52" t="inlineStr">
         <is>
-          <t>下午</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D20" s="52" t="inlineStr">
         <is>
-          <t>希望</t>
-        </is>
-      </c>
-      <c r="E20" s="44" t="inlineStr">
-        <is>
-          <t>接送小孩</t>
-        </is>
-      </c>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E20" s="44" t="n"/>
       <c r="F20" s="56">
         <f>IF(A20="","",COUNTIFS($A$5:$A$304,A20,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24558,7 +24842,7 @@
     <row r="21" ht="15" customHeight="1" s="36">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>社會甲</t>
+          <t>體育己</t>
         </is>
       </c>
       <c r="B21" s="52" t="inlineStr">
@@ -24568,15 +24852,19 @@
       </c>
       <c r="C21" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D21" s="52" t="inlineStr">
         <is>
-          <t>希望</t>
-        </is>
-      </c>
-      <c r="E21" s="44" t="n"/>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E21" s="44" t="inlineStr">
+        <is>
+          <t>兼任行政會議</t>
+        </is>
+      </c>
       <c r="F21" s="56">
         <f>IF(A21="","",COUNTIFS($A$5:$A$304,A21,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24585,17 +24873,17 @@
     <row r="22" ht="15" customHeight="1" s="36">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>自然乙</t>
+          <t>體育己</t>
         </is>
       </c>
       <c r="B22" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C22" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D22" s="52" t="inlineStr">
@@ -24605,7 +24893,7 @@
       </c>
       <c r="E22" s="44" t="inlineStr">
         <is>
-          <t>身體因素</t>
+          <t>兼任行政會議</t>
         </is>
       </c>
       <c r="F22" s="56">
@@ -24616,29 +24904,25 @@
     <row r="23" ht="15" customHeight="1" s="36">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>自然乙</t>
+          <t>體育己</t>
         </is>
       </c>
       <c r="B23" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C23" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D23" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E23" s="44" t="inlineStr">
-        <is>
-          <t>進修</t>
-        </is>
-      </c>
+          <t>希望</t>
+        </is>
+      </c>
+      <c r="E23" s="44" t="n"/>
       <c r="F23" s="56">
         <f>IF(A23="","",COUNTIFS($A$5:$A$304,A23,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24647,17 +24931,17 @@
     <row r="24" ht="15" customHeight="1" s="36">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>自然乙</t>
+          <t>音樂丙</t>
         </is>
       </c>
       <c r="B24" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C24" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D24" s="52" t="inlineStr">
@@ -24665,7 +24949,11 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="E24" s="44" t="n"/>
+      <c r="E24" s="44" t="inlineStr">
+        <is>
+          <t>身體因素</t>
+        </is>
+      </c>
       <c r="F24" s="56">
         <f>IF(A24="","",COUNTIFS($A$5:$A$304,A24,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24674,29 +24962,25 @@
     <row r="25" ht="15" customHeight="1" s="36">
       <c r="A25" s="44" t="inlineStr">
         <is>
-          <t>自然乙</t>
+          <t>音樂丙</t>
         </is>
       </c>
       <c r="B25" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C25" s="52" t="inlineStr">
         <is>
-          <t>下午</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D25" s="52" t="inlineStr">
         <is>
-          <t>希望</t>
-        </is>
-      </c>
-      <c r="E25" s="44" t="inlineStr">
-        <is>
-          <t>接送小孩</t>
-        </is>
-      </c>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E25" s="44" t="n"/>
       <c r="F25" s="56">
         <f>IF(A25="","",COUNTIFS($A$5:$A$304,A25,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24705,12 +24989,12 @@
     <row r="26" ht="15" customHeight="1" s="36">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>音樂甲</t>
+          <t>音樂丙</t>
         </is>
       </c>
       <c r="B26" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C26" s="52" t="inlineStr">
@@ -24736,17 +25020,17 @@
     <row r="27" ht="15" customHeight="1" s="36">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>音樂甲</t>
+          <t>英語戊</t>
         </is>
       </c>
       <c r="B27" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C27" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D27" s="52" t="inlineStr">
@@ -24767,17 +25051,17 @@
     <row r="28" ht="15" customHeight="1" s="36">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>音樂甲</t>
+          <t>英語戊</t>
         </is>
       </c>
       <c r="B28" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C28" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D28" s="52" t="inlineStr">
@@ -24787,7 +25071,7 @@
       </c>
       <c r="E28" s="44" t="inlineStr">
         <is>
-          <t>接送小孩</t>
+          <t>兼任行政會議</t>
         </is>
       </c>
       <c r="F28" s="56">
@@ -24798,7 +25082,7 @@
     <row r="29" ht="15" customHeight="1" s="36">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>音樂甲</t>
+          <t>英語戊</t>
         </is>
       </c>
       <c r="B29" s="52" t="inlineStr">
@@ -24829,7 +25113,7 @@
     <row r="30" ht="15" customHeight="1" s="36">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>音樂己</t>
+          <t>社會丁</t>
         </is>
       </c>
       <c r="B30" s="52" t="inlineStr">
@@ -24858,57 +25142,21 @@
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="36">
-      <c r="A31" s="44" t="inlineStr">
-        <is>
-          <t>英語丙</t>
-        </is>
-      </c>
-      <c r="B31" s="52" t="inlineStr">
-        <is>
-          <t>四</t>
-        </is>
-      </c>
-      <c r="C31" s="52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D31" s="52" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E31" s="44" t="inlineStr">
-        <is>
-          <t>接送小孩</t>
-        </is>
-      </c>
+      <c r="A31" s="44" t="n"/>
+      <c r="B31" s="52" t="n"/>
+      <c r="C31" s="52" t="n"/>
+      <c r="D31" s="52" t="n"/>
+      <c r="E31" s="44" t="n"/>
       <c r="F31" s="56">
         <f>IF(A31="","",COUNTIFS($A$5:$A$304,A31,$D$5:$D$304,"必須"))</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="36">
-      <c r="A32" s="44" t="inlineStr">
-        <is>
-          <t>英語丙</t>
-        </is>
-      </c>
-      <c r="B32" s="52" t="inlineStr">
-        <is>
-          <t>四</t>
-        </is>
-      </c>
-      <c r="C32" s="52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D32" s="52" t="inlineStr">
-        <is>
-          <t>希望</t>
-        </is>
-      </c>
+      <c r="A32" s="44" t="n"/>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
       <c r="E32" s="44" t="n"/>
       <c r="F32" s="56">
         <f>IF(A32="","",COUNTIFS($A$5:$A$304,A32,$D$5:$D$304,"必須"))</f>
@@ -24916,31 +25164,11 @@
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="36">
-      <c r="A33" s="44" t="inlineStr">
-        <is>
-          <t>自然丁</t>
-        </is>
-      </c>
-      <c r="B33" s="52" t="inlineStr">
-        <is>
-          <t>五</t>
-        </is>
-      </c>
-      <c r="C33" s="52" t="inlineStr">
-        <is>
-          <t>下午</t>
-        </is>
-      </c>
-      <c r="D33" s="52" t="inlineStr">
-        <is>
-          <t>希望</t>
-        </is>
-      </c>
-      <c r="E33" s="44" t="inlineStr">
-        <is>
-          <t>接送小孩</t>
-        </is>
-      </c>
+      <c r="A33" s="44" t="n"/>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+      <c r="E33" s="44" t="n"/>
       <c r="F33" s="56">
         <f>IF(A33="","",COUNTIFS($A$5:$A$304,A33,$D$5:$D$304,"必須"))</f>
         <v/>

--- a/試跑/試跑資料_排課需求收集表.xlsx
+++ b/試跑/試跑資料_排課需求收集表.xlsx
@@ -16667,17 +16667,17 @@
     <row r="5" ht="15" customHeight="1" s="36">
       <c r="A5" s="52" t="inlineStr">
         <is>
-          <t>1年1班</t>
+          <t>6年3班</t>
         </is>
       </c>
       <c r="B5" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C5" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D5" s="52" t="inlineStr">
@@ -16700,17 +16700,17 @@
     <row r="6" ht="15" customHeight="1" s="36">
       <c r="A6" s="52" t="inlineStr">
         <is>
-          <t>2年1班</t>
+          <t>3年7班</t>
         </is>
       </c>
       <c r="B6" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C6" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D6" s="52" t="inlineStr">
@@ -16733,17 +16733,17 @@
     <row r="7" ht="15" customHeight="1" s="36">
       <c r="A7" s="52" t="inlineStr">
         <is>
-          <t>3年1班</t>
+          <t>4年5班</t>
         </is>
       </c>
       <c r="B7" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C7" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D7" s="52" t="inlineStr">
@@ -16766,17 +16766,17 @@
     <row r="8" ht="15" customHeight="1" s="36">
       <c r="A8" s="52" t="inlineStr">
         <is>
-          <t>4年1班</t>
+          <t>1年2班</t>
         </is>
       </c>
       <c r="B8" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C8" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" s="52" t="inlineStr">
@@ -16799,7 +16799,7 @@
     <row r="9" ht="15" customHeight="1" s="36">
       <c r="A9" s="52" t="inlineStr">
         <is>
-          <t>5年1班</t>
+          <t>5年9班</t>
         </is>
       </c>
       <c r="B9" s="52" t="inlineStr">
@@ -16809,7 +16809,7 @@
       </c>
       <c r="C9" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D9" s="52" t="inlineStr">
@@ -16832,17 +16832,17 @@
     <row r="10" ht="15" customHeight="1" s="36">
       <c r="A10" s="52" t="inlineStr">
         <is>
-          <t>6年1班</t>
+          <t>6年11班</t>
         </is>
       </c>
       <c r="B10" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C10" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="52" t="inlineStr">
@@ -16865,17 +16865,17 @@
     <row r="11" ht="15" customHeight="1" s="36">
       <c r="A11" s="52" t="inlineStr">
         <is>
-          <t>1年2班</t>
+          <t>1年8班</t>
         </is>
       </c>
       <c r="B11" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C11" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D11" s="52" t="inlineStr">
@@ -16898,7 +16898,7 @@
     <row r="12" ht="15" customHeight="1" s="36">
       <c r="A12" s="52" t="inlineStr">
         <is>
-          <t>2年2班</t>
+          <t>1年5班</t>
         </is>
       </c>
       <c r="B12" s="52" t="inlineStr">
@@ -16908,7 +16908,7 @@
       </c>
       <c r="C12" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" s="52" t="inlineStr">
@@ -16931,7 +16931,7 @@
     <row r="13" ht="15" customHeight="1" s="36">
       <c r="A13" s="52" t="inlineStr">
         <is>
-          <t>3年2班</t>
+          <t>6年5班</t>
         </is>
       </c>
       <c r="B13" s="52" t="inlineStr">
@@ -16941,7 +16941,7 @@
       </c>
       <c r="C13" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="52" t="inlineStr">
@@ -16964,17 +16964,17 @@
     <row r="14" ht="15" customHeight="1" s="36">
       <c r="A14" s="52" t="inlineStr">
         <is>
-          <t>4年2班</t>
+          <t>3年2班</t>
         </is>
       </c>
       <c r="B14" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C14" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" s="52" t="inlineStr">
@@ -16997,7 +16997,7 @@
     <row r="15" ht="15" customHeight="1" s="36">
       <c r="A15" s="52" t="inlineStr">
         <is>
-          <t>5年2班</t>
+          <t>3年10班</t>
         </is>
       </c>
       <c r="B15" s="52" t="inlineStr">
@@ -17007,7 +17007,7 @@
       </c>
       <c r="C15" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D15" s="52" t="inlineStr">
@@ -17030,17 +17030,17 @@
     <row r="16" ht="15" customHeight="1" s="36">
       <c r="A16" s="52" t="inlineStr">
         <is>
-          <t>6年2班</t>
+          <t>5年10班</t>
         </is>
       </c>
       <c r="B16" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C16" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D16" s="52" t="inlineStr">
@@ -17063,17 +17063,17 @@
     <row r="17" ht="15" customHeight="1" s="36">
       <c r="A17" s="52" t="inlineStr">
         <is>
-          <t>1年3班</t>
+          <t>3年1班</t>
         </is>
       </c>
       <c r="B17" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C17" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D17" s="52" t="inlineStr">
@@ -17096,17 +17096,17 @@
     <row r="18" ht="15" customHeight="1" s="36">
       <c r="A18" s="52" t="inlineStr">
         <is>
-          <t>2年3班</t>
+          <t>1年9班</t>
         </is>
       </c>
       <c r="B18" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C18" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D18" s="52" t="inlineStr">
@@ -17129,17 +17129,17 @@
     <row r="19" ht="15" customHeight="1" s="36">
       <c r="A19" s="52" t="inlineStr">
         <is>
-          <t>3年3班</t>
+          <t>3年6班</t>
         </is>
       </c>
       <c r="B19" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C19" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D19" s="52" t="inlineStr">
@@ -17162,17 +17162,17 @@
     <row r="20" ht="15" customHeight="1" s="36">
       <c r="A20" s="52" t="inlineStr">
         <is>
-          <t>4年3班</t>
+          <t>5年7班</t>
         </is>
       </c>
       <c r="B20" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C20" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D20" s="52" t="inlineStr">
@@ -17195,7 +17195,7 @@
     <row r="21" ht="15" customHeight="1" s="36">
       <c r="A21" s="52" t="inlineStr">
         <is>
-          <t>5年3班</t>
+          <t>6年8班</t>
         </is>
       </c>
       <c r="B21" s="52" t="inlineStr">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="C21" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D21" s="52" t="inlineStr">
@@ -17228,17 +17228,17 @@
     <row r="22" ht="15" customHeight="1" s="36">
       <c r="A22" s="52" t="inlineStr">
         <is>
-          <t>6年3班</t>
+          <t>5年3班</t>
         </is>
       </c>
       <c r="B22" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C22" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D22" s="52" t="inlineStr">
@@ -17261,17 +17261,17 @@
     <row r="23" ht="15" customHeight="1" s="36">
       <c r="A23" s="52" t="inlineStr">
         <is>
-          <t>1年4班</t>
+          <t>4年4班</t>
         </is>
       </c>
       <c r="B23" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C23" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D23" s="52" t="inlineStr">
@@ -17294,17 +17294,17 @@
     <row r="24" ht="15" customHeight="1" s="36">
       <c r="A24" s="52" t="inlineStr">
         <is>
-          <t>2年4班</t>
+          <t>2年9班</t>
         </is>
       </c>
       <c r="B24" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C24" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D24" s="52" t="inlineStr">
@@ -17327,7 +17327,7 @@
     <row r="25" ht="15" customHeight="1" s="36">
       <c r="A25" s="52" t="inlineStr">
         <is>
-          <t>3年4班</t>
+          <t>2年8班</t>
         </is>
       </c>
       <c r="B25" s="52" t="inlineStr">
@@ -17337,7 +17337,7 @@
       </c>
       <c r="C25" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D25" s="52" t="inlineStr">
@@ -17360,17 +17360,17 @@
     <row r="26" ht="15" customHeight="1" s="36">
       <c r="A26" s="52" t="inlineStr">
         <is>
-          <t>4年4班</t>
+          <t>1年6班</t>
         </is>
       </c>
       <c r="B26" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C26" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D26" s="52" t="inlineStr">
@@ -17398,12 +17398,12 @@
       </c>
       <c r="B27" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C27" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D27" s="52" t="inlineStr">
@@ -17426,7 +17426,7 @@
     <row r="28" ht="15" customHeight="1" s="36">
       <c r="A28" s="52" t="inlineStr">
         <is>
-          <t>6年4班</t>
+          <t>2年11班</t>
         </is>
       </c>
       <c r="B28" s="52" t="inlineStr">
@@ -17436,7 +17436,7 @@
       </c>
       <c r="C28" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D28" s="52" t="inlineStr">
@@ -17459,7 +17459,7 @@
     <row r="29" ht="15" customHeight="1" s="36">
       <c r="A29" s="52" t="inlineStr">
         <is>
-          <t>1年5班</t>
+          <t>6年6班</t>
         </is>
       </c>
       <c r="B29" s="52" t="inlineStr">
@@ -17469,7 +17469,7 @@
       </c>
       <c r="C29" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D29" s="52" t="inlineStr">
@@ -17492,12 +17492,12 @@
     <row r="30" ht="15" customHeight="1" s="36">
       <c r="A30" s="52" t="inlineStr">
         <is>
-          <t>2年5班</t>
+          <t>6年1班</t>
         </is>
       </c>
       <c r="B30" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C30" s="52" t="inlineStr">
@@ -17525,17 +17525,17 @@
     <row r="31" ht="15" customHeight="1" s="36">
       <c r="A31" s="52" t="inlineStr">
         <is>
-          <t>3年5班</t>
+          <t>1年7班</t>
         </is>
       </c>
       <c r="B31" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C31" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D31" s="52" t="inlineStr">
@@ -17558,17 +17558,17 @@
     <row r="32" ht="15" customHeight="1" s="36">
       <c r="A32" s="52" t="inlineStr">
         <is>
-          <t>4年5班</t>
+          <t>6年4班</t>
         </is>
       </c>
       <c r="B32" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C32" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D32" s="52" t="inlineStr">
@@ -17591,17 +17591,17 @@
     <row r="33" ht="15" customHeight="1" s="36">
       <c r="A33" s="52" t="inlineStr">
         <is>
-          <t>5年5班</t>
+          <t>3年12班</t>
         </is>
       </c>
       <c r="B33" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C33" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D33" s="52" t="inlineStr">
@@ -17624,17 +17624,17 @@
     <row r="34" ht="15" customHeight="1" s="36">
       <c r="A34" s="52" t="inlineStr">
         <is>
-          <t>6年5班</t>
+          <t>4年12班</t>
         </is>
       </c>
       <c r="B34" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C34" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D34" s="52" t="inlineStr">
@@ -17657,17 +17657,17 @@
     <row r="35" ht="15" customHeight="1" s="36">
       <c r="A35" s="52" t="inlineStr">
         <is>
-          <t>1年6班</t>
+          <t>4年7班</t>
         </is>
       </c>
       <c r="B35" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C35" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D35" s="52" t="inlineStr">
@@ -17690,17 +17690,17 @@
     <row r="36" ht="15" customHeight="1" s="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
-          <t>2年6班</t>
+          <t>3年4班</t>
         </is>
       </c>
       <c r="B36" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C36" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D36" s="52" t="inlineStr">
@@ -17723,17 +17723,17 @@
     <row r="37" ht="15" customHeight="1" s="36">
       <c r="A37" s="52" t="inlineStr">
         <is>
-          <t>3年6班</t>
+          <t>2年5班</t>
         </is>
       </c>
       <c r="B37" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C37" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D37" s="52" t="inlineStr">
@@ -17756,17 +17756,17 @@
     <row r="38" ht="15" customHeight="1" s="36">
       <c r="A38" s="52" t="inlineStr">
         <is>
-          <t>4年6班</t>
+          <t>6年9班</t>
         </is>
       </c>
       <c r="B38" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C38" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D38" s="52" t="inlineStr">
@@ -17789,17 +17789,17 @@
     <row r="39" ht="15" customHeight="1" s="36">
       <c r="A39" s="52" t="inlineStr">
         <is>
-          <t>5年6班</t>
+          <t>2年6班</t>
         </is>
       </c>
       <c r="B39" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C39" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D39" s="52" t="inlineStr">
@@ -17822,17 +17822,17 @@
     <row r="40" ht="15" customHeight="1" s="36">
       <c r="A40" s="52" t="inlineStr">
         <is>
-          <t>6年6班</t>
+          <t>5年2班</t>
         </is>
       </c>
       <c r="B40" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C40" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D40" s="52" t="inlineStr">
@@ -17855,17 +17855,17 @@
     <row r="41" ht="15" customHeight="1" s="36">
       <c r="A41" s="52" t="inlineStr">
         <is>
-          <t>1年7班</t>
+          <t>2年10班</t>
         </is>
       </c>
       <c r="B41" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C41" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D41" s="52" t="inlineStr">
@@ -17888,7 +17888,7 @@
     <row r="42" ht="15" customHeight="1" s="36">
       <c r="A42" s="52" t="inlineStr">
         <is>
-          <t>2年7班</t>
+          <t>4年10班</t>
         </is>
       </c>
       <c r="B42" s="52" t="inlineStr">
@@ -17898,7 +17898,7 @@
       </c>
       <c r="C42" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D42" s="52" t="inlineStr">
@@ -17921,12 +17921,12 @@
     <row r="43" ht="15" customHeight="1" s="36">
       <c r="A43" s="52" t="inlineStr">
         <is>
-          <t>3年7班</t>
+          <t>2年1班</t>
         </is>
       </c>
       <c r="B43" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C43" s="52" t="inlineStr">
@@ -17954,7 +17954,7 @@
     <row r="44" ht="15" customHeight="1" s="36">
       <c r="A44" s="52" t="inlineStr">
         <is>
-          <t>4年7班</t>
+          <t>1年1班</t>
         </is>
       </c>
       <c r="B44" s="52" t="inlineStr">
@@ -17964,7 +17964,7 @@
       </c>
       <c r="C44" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D44" s="52" t="inlineStr">
@@ -17987,17 +17987,17 @@
     <row r="45" ht="15" customHeight="1" s="36">
       <c r="A45" s="52" t="inlineStr">
         <is>
-          <t>5年7班</t>
+          <t>3年5班</t>
         </is>
       </c>
       <c r="B45" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C45" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D45" s="52" t="inlineStr">
@@ -18020,17 +18020,17 @@
     <row r="46" ht="15" customHeight="1" s="36">
       <c r="A46" s="52" t="inlineStr">
         <is>
-          <t>6年7班</t>
+          <t>4年6班</t>
         </is>
       </c>
       <c r="B46" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C46" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D46" s="52" t="inlineStr">
@@ -18053,17 +18053,17 @@
     <row r="47" ht="15" customHeight="1" s="36">
       <c r="A47" s="52" t="inlineStr">
         <is>
-          <t>1年8班</t>
+          <t>4年11班</t>
         </is>
       </c>
       <c r="B47" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C47" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D47" s="52" t="inlineStr">
@@ -18086,17 +18086,17 @@
     <row r="48" ht="15" customHeight="1" s="36">
       <c r="A48" s="52" t="inlineStr">
         <is>
-          <t>2年8班</t>
+          <t>2年2班</t>
         </is>
       </c>
       <c r="B48" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C48" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D48" s="52" t="inlineStr">
@@ -18119,12 +18119,12 @@
     <row r="49" ht="15" customHeight="1" s="36">
       <c r="A49" s="52" t="inlineStr">
         <is>
-          <t>3年8班</t>
+          <t>3年11班</t>
         </is>
       </c>
       <c r="B49" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C49" s="52" t="inlineStr">
@@ -18152,17 +18152,17 @@
     <row r="50" ht="15" customHeight="1" s="36">
       <c r="A50" s="52" t="inlineStr">
         <is>
-          <t>4年8班</t>
+          <t>5年11班</t>
         </is>
       </c>
       <c r="B50" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C50" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D50" s="52" t="inlineStr">
@@ -18190,12 +18190,12 @@
       </c>
       <c r="B51" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C51" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D51" s="52" t="inlineStr">
@@ -18218,17 +18218,17 @@
     <row r="52" ht="15" customHeight="1" s="36">
       <c r="A52" s="52" t="inlineStr">
         <is>
-          <t>6年8班</t>
+          <t>1年11班</t>
         </is>
       </c>
       <c r="B52" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C52" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D52" s="52" t="inlineStr">
@@ -18251,12 +18251,12 @@
     <row r="53" ht="15" customHeight="1" s="36">
       <c r="A53" s="52" t="inlineStr">
         <is>
-          <t>1年9班</t>
+          <t>2年4班</t>
         </is>
       </c>
       <c r="B53" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C53" s="52" t="inlineStr">
@@ -18284,17 +18284,17 @@
     <row r="54" ht="15" customHeight="1" s="36">
       <c r="A54" s="52" t="inlineStr">
         <is>
-          <t>2年9班</t>
+          <t>6年7班</t>
         </is>
       </c>
       <c r="B54" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C54" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D54" s="52" t="inlineStr">
@@ -18317,17 +18317,17 @@
     <row r="55" ht="15" customHeight="1" s="36">
       <c r="A55" s="52" t="inlineStr">
         <is>
-          <t>3年9班</t>
+          <t>5年1班</t>
         </is>
       </c>
       <c r="B55" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C55" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D55" s="52" t="inlineStr">
@@ -18350,17 +18350,17 @@
     <row r="56" ht="15" customHeight="1" s="36">
       <c r="A56" s="52" t="inlineStr">
         <is>
-          <t>4年9班</t>
+          <t>3年9班</t>
         </is>
       </c>
       <c r="B56" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C56" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D56" s="52" t="inlineStr">
@@ -18383,17 +18383,17 @@
     <row r="57" ht="15" customHeight="1" s="36">
       <c r="A57" s="52" t="inlineStr">
         <is>
-          <t>5年9班</t>
+          <t>1年12班</t>
         </is>
       </c>
       <c r="B57" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C57" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D57" s="52" t="inlineStr">
@@ -18416,17 +18416,17 @@
     <row r="58" ht="15" customHeight="1" s="36">
       <c r="A58" s="52" t="inlineStr">
         <is>
-          <t>6年9班</t>
+          <t>5年5班</t>
         </is>
       </c>
       <c r="B58" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C58" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D58" s="52" t="inlineStr">
@@ -18449,17 +18449,17 @@
     <row r="59" ht="15" customHeight="1" s="36">
       <c r="A59" s="52" t="inlineStr">
         <is>
-          <t>1年10班</t>
+          <t>5年6班</t>
         </is>
       </c>
       <c r="B59" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C59" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D59" s="52" t="inlineStr">
@@ -18482,12 +18482,12 @@
     <row r="60" ht="15" customHeight="1" s="36">
       <c r="A60" s="52" t="inlineStr">
         <is>
-          <t>2年10班</t>
+          <t>2年7班</t>
         </is>
       </c>
       <c r="B60" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C60" s="52" t="inlineStr">
@@ -18515,12 +18515,12 @@
     <row r="61" ht="15" customHeight="1" s="36">
       <c r="A61" s="52" t="inlineStr">
         <is>
-          <t>3年10班</t>
+          <t>1年3班</t>
         </is>
       </c>
       <c r="B61" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C61" s="52" t="inlineStr">
@@ -18548,7 +18548,7 @@
     <row r="62" ht="15" customHeight="1" s="36">
       <c r="A62" s="52" t="inlineStr">
         <is>
-          <t>4年10班</t>
+          <t>5年12班</t>
         </is>
       </c>
       <c r="B62" s="52" t="inlineStr">
@@ -18558,7 +18558,7 @@
       </c>
       <c r="C62" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D62" s="52" t="inlineStr">
@@ -18581,7 +18581,7 @@
     <row r="63" ht="15" customHeight="1" s="36">
       <c r="A63" s="52" t="inlineStr">
         <is>
-          <t>5年10班</t>
+          <t>1年10班</t>
         </is>
       </c>
       <c r="B63" s="52" t="inlineStr">
@@ -18591,7 +18591,7 @@
       </c>
       <c r="C63" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D63" s="52" t="inlineStr">
@@ -18614,17 +18614,17 @@
     <row r="64" ht="15" customHeight="1" s="36">
       <c r="A64" s="52" t="inlineStr">
         <is>
-          <t>6年10班</t>
+          <t>6年2班</t>
         </is>
       </c>
       <c r="B64" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C64" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D64" s="52" t="inlineStr">
@@ -18647,7 +18647,7 @@
     <row r="65" ht="15" customHeight="1" s="36">
       <c r="A65" s="52" t="inlineStr">
         <is>
-          <t>1年11班</t>
+          <t>4年1班</t>
         </is>
       </c>
       <c r="B65" s="52" t="inlineStr">
@@ -18657,7 +18657,7 @@
       </c>
       <c r="C65" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D65" s="52" t="inlineStr">
@@ -18680,17 +18680,17 @@
     <row r="66" ht="15" customHeight="1" s="36">
       <c r="A66" s="52" t="inlineStr">
         <is>
-          <t>2年11班</t>
+          <t>1年4班</t>
         </is>
       </c>
       <c r="B66" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C66" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D66" s="52" t="inlineStr">
@@ -18713,7 +18713,7 @@
     <row r="67" ht="15" customHeight="1" s="36">
       <c r="A67" s="52" t="inlineStr">
         <is>
-          <t>3年11班</t>
+          <t>3年8班</t>
         </is>
       </c>
       <c r="B67" s="52" t="inlineStr">
@@ -18723,7 +18723,7 @@
       </c>
       <c r="C67" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D67" s="52" t="inlineStr">
@@ -18746,17 +18746,17 @@
     <row r="68" ht="15" customHeight="1" s="36">
       <c r="A68" s="52" t="inlineStr">
         <is>
-          <t>4年11班</t>
+          <t>4年9班</t>
         </is>
       </c>
       <c r="B68" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C68" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D68" s="52" t="inlineStr">
@@ -18779,17 +18779,17 @@
     <row r="69" ht="15" customHeight="1" s="36">
       <c r="A69" s="52" t="inlineStr">
         <is>
-          <t>5年11班</t>
+          <t>6年12班</t>
         </is>
       </c>
       <c r="B69" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C69" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D69" s="52" t="inlineStr">
@@ -18812,17 +18812,17 @@
     <row r="70" ht="15" customHeight="1" s="36">
       <c r="A70" s="52" t="inlineStr">
         <is>
-          <t>6年11班</t>
+          <t>4年3班</t>
         </is>
       </c>
       <c r="B70" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C70" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D70" s="52" t="inlineStr">
@@ -18845,17 +18845,17 @@
     <row r="71" ht="15" customHeight="1" s="36">
       <c r="A71" s="52" t="inlineStr">
         <is>
-          <t>1年12班</t>
+          <t>4年8班</t>
         </is>
       </c>
       <c r="B71" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C71" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D71" s="52" t="inlineStr">
@@ -18878,17 +18878,17 @@
     <row r="72" ht="15" customHeight="1" s="36">
       <c r="A72" s="52" t="inlineStr">
         <is>
-          <t>3年12班</t>
+          <t>6年10班</t>
         </is>
       </c>
       <c r="B72" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C72" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D72" s="52" t="inlineStr">
@@ -18911,17 +18911,17 @@
     <row r="73" ht="15" customHeight="1" s="36">
       <c r="A73" s="52" t="inlineStr">
         <is>
-          <t>4年12班</t>
+          <t>2年3班</t>
         </is>
       </c>
       <c r="B73" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C73" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D73" s="52" t="inlineStr">
@@ -18944,7 +18944,7 @@
     <row r="74" ht="15" customHeight="1" s="36">
       <c r="A74" s="52" t="inlineStr">
         <is>
-          <t>5年12班</t>
+          <t>3年3班</t>
         </is>
       </c>
       <c r="B74" s="52" t="inlineStr">
@@ -18954,7 +18954,7 @@
       </c>
       <c r="C74" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D74" s="52" t="inlineStr">
@@ -18981,7 +18981,7 @@
     <row r="75" ht="15" customHeight="1" s="36">
       <c r="A75" s="52" t="inlineStr">
         <is>
-          <t>6年12班</t>
+          <t>4年2班</t>
         </is>
       </c>
       <c r="B75" s="52" t="inlineStr">
@@ -18991,7 +18991,7 @@
       </c>
       <c r="C75" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D75" s="52" t="inlineStr">
@@ -19018,27 +19018,27 @@
     <row r="76" ht="15" customHeight="1" s="36">
       <c r="A76" s="52" t="inlineStr">
         <is>
-          <t>6年3班</t>
+          <t>4年6班</t>
         </is>
       </c>
       <c r="B76" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C76" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D76" s="52" t="inlineStr">
         <is>
-          <t>新住民語</t>
+          <t>客語</t>
         </is>
       </c>
       <c r="E76" s="44" t="inlineStr">
         <is>
-          <t>新住民語甲</t>
+          <t>客語甲</t>
         </is>
       </c>
       <c r="F76" s="44" t="inlineStr">
@@ -19055,27 +19055,27 @@
     <row r="77" ht="15" customHeight="1" s="36">
       <c r="A77" s="52" t="inlineStr">
         <is>
-          <t>1年2班</t>
+          <t>3年7班</t>
         </is>
       </c>
       <c r="B77" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C77" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D77" s="52" t="inlineStr">
         <is>
-          <t>客語</t>
+          <t>族語</t>
         </is>
       </c>
       <c r="E77" s="44" t="inlineStr">
         <is>
-          <t>客語甲</t>
+          <t>族語甲</t>
         </is>
       </c>
       <c r="F77" s="44" t="inlineStr">
@@ -19092,17 +19092,17 @@
     <row r="78" ht="15" customHeight="1" s="36">
       <c r="A78" s="52" t="inlineStr">
         <is>
-          <t>6年11班</t>
+          <t>6年7班</t>
         </is>
       </c>
       <c r="B78" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C78" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D78" s="52" t="inlineStr">
@@ -19129,7 +19129,7 @@
     <row r="79" ht="15" customHeight="1" s="36">
       <c r="A79" s="52" t="inlineStr">
         <is>
-          <t>2年7班</t>
+          <t>5年10班</t>
         </is>
       </c>
       <c r="B79" s="52" t="inlineStr">
@@ -19166,7 +19166,7 @@
     <row r="80" ht="15" customHeight="1" s="36">
       <c r="A80" s="52" t="inlineStr">
         <is>
-          <t>6年9班</t>
+          <t>4年12班</t>
         </is>
       </c>
       <c r="B80" s="52" t="inlineStr">
@@ -19176,17 +19176,17 @@
       </c>
       <c r="C80" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D80" s="52" t="inlineStr">
         <is>
-          <t>客語</t>
+          <t>族語</t>
         </is>
       </c>
       <c r="E80" s="44" t="inlineStr">
         <is>
-          <t>客語甲</t>
+          <t>族語甲</t>
         </is>
       </c>
       <c r="F80" s="44" t="inlineStr">
@@ -19203,27 +19203,27 @@
     <row r="81" ht="15" customHeight="1" s="36">
       <c r="A81" s="52" t="inlineStr">
         <is>
-          <t>1年9班</t>
+          <t>3年6班</t>
         </is>
       </c>
       <c r="B81" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C81" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D81" s="52" t="inlineStr">
         <is>
-          <t>客語</t>
+          <t>族語</t>
         </is>
       </c>
       <c r="E81" s="44" t="inlineStr">
         <is>
-          <t>客語甲</t>
+          <t>族語甲</t>
         </is>
       </c>
       <c r="F81" s="44" t="inlineStr">
@@ -19240,12 +19240,12 @@
     <row r="82" ht="15" customHeight="1" s="36">
       <c r="A82" s="52" t="inlineStr">
         <is>
-          <t>6年6班</t>
+          <t>4年7班</t>
         </is>
       </c>
       <c r="B82" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C82" s="52" t="inlineStr">
@@ -19255,12 +19255,12 @@
       </c>
       <c r="D82" s="52" t="inlineStr">
         <is>
-          <t>族語</t>
+          <t>新住民語</t>
         </is>
       </c>
       <c r="E82" s="44" t="inlineStr">
         <is>
-          <t>族語甲</t>
+          <t>新住民語甲</t>
         </is>
       </c>
       <c r="F82" s="44" t="inlineStr">
@@ -19277,27 +19277,27 @@
     <row r="83" ht="15" customHeight="1" s="36">
       <c r="A83" s="52" t="inlineStr">
         <is>
-          <t>3年12班</t>
+          <t>3年11班</t>
         </is>
       </c>
       <c r="B83" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C83" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D83" s="52" t="inlineStr">
         <is>
-          <t>客語</t>
+          <t>族語</t>
         </is>
       </c>
       <c r="E83" s="44" t="inlineStr">
         <is>
-          <t>客語甲</t>
+          <t>族語甲</t>
         </is>
       </c>
       <c r="F83" s="44" t="inlineStr">
@@ -19314,27 +19314,27 @@
     <row r="84" ht="15" customHeight="1" s="36">
       <c r="A84" s="52" t="inlineStr">
         <is>
-          <t>6年4班</t>
+          <t>1年10班</t>
         </is>
       </c>
       <c r="B84" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C84" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D84" s="52" t="inlineStr">
         <is>
-          <t>族語</t>
+          <t>新住民語</t>
         </is>
       </c>
       <c r="E84" s="44" t="inlineStr">
         <is>
-          <t>族語甲</t>
+          <t>新住民語甲</t>
         </is>
       </c>
       <c r="F84" s="44" t="inlineStr">
@@ -19351,12 +19351,12 @@
     <row r="85" ht="15" customHeight="1" s="36">
       <c r="A85" s="52" t="inlineStr">
         <is>
-          <t>1年11班</t>
+          <t>1年6班</t>
         </is>
       </c>
       <c r="B85" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C85" s="52" t="inlineStr">
@@ -19366,12 +19366,12 @@
       </c>
       <c r="D85" s="52" t="inlineStr">
         <is>
-          <t>族語</t>
+          <t>客語</t>
         </is>
       </c>
       <c r="E85" s="44" t="inlineStr">
         <is>
-          <t>族語甲</t>
+          <t>客語甲</t>
         </is>
       </c>
       <c r="F85" s="44" t="inlineStr">
@@ -20156,7 +20156,7 @@
       </c>
       <c r="B5" s="52" t="inlineStr">
         <is>
-          <t>4年10班</t>
+          <t>6年12班</t>
         </is>
       </c>
       <c r="C5" s="44" t="inlineStr">
@@ -20171,7 +20171,7 @@
       </c>
       <c r="E5" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F5" s="44" t="inlineStr">
@@ -20180,7 +20180,7 @@
         </is>
       </c>
       <c r="G5" s="44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" s="44" t="n"/>
     </row>
@@ -20192,22 +20192,22 @@
       </c>
       <c r="B6" s="52" t="inlineStr">
         <is>
-          <t>6年3班</t>
+          <t>2年1班</t>
         </is>
       </c>
       <c r="C6" s="44" t="inlineStr">
         <is>
-          <t>數學</t>
+          <t>國語</t>
         </is>
       </c>
       <c r="D6" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>三</t>
         </is>
       </c>
       <c r="E6" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F6" s="44" t="inlineStr">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="B7" s="52" t="inlineStr">
         <is>
-          <t>4年11班</t>
+          <t>3年1班</t>
         </is>
       </c>
       <c r="C7" s="44" t="inlineStr">
@@ -20238,12 +20238,12 @@
       </c>
       <c r="D7" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>三</t>
         </is>
       </c>
       <c r="E7" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F7" s="44" t="inlineStr">
@@ -20252,7 +20252,7 @@
         </is>
       </c>
       <c r="G7" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="44" t="n"/>
     </row>
@@ -20264,17 +20264,17 @@
       </c>
       <c r="B8" s="52" t="inlineStr">
         <is>
-          <t>3年1班</t>
+          <t>5年6班</t>
         </is>
       </c>
       <c r="C8" s="44" t="inlineStr">
         <is>
-          <t>國語</t>
+          <t>數學</t>
         </is>
       </c>
       <c r="D8" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>四</t>
         </is>
       </c>
       <c r="E8" s="52" t="inlineStr">
@@ -20300,7 +20300,7 @@
       </c>
       <c r="B9" s="52" t="inlineStr">
         <is>
-          <t>3年7班</t>
+          <t>4年8班</t>
         </is>
       </c>
       <c r="C9" s="44" t="inlineStr">
@@ -20310,12 +20310,12 @@
       </c>
       <c r="D9" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>三</t>
         </is>
       </c>
       <c r="E9" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F9" s="44" t="inlineStr">
@@ -20336,22 +20336,22 @@
       </c>
       <c r="B10" s="52" t="inlineStr">
         <is>
-          <t>4年5班</t>
+          <t>3年2班</t>
         </is>
       </c>
       <c r="C10" s="44" t="inlineStr">
         <is>
-          <t>國語</t>
+          <t>數學</t>
         </is>
       </c>
       <c r="D10" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="E10" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F10" s="44" t="inlineStr">
@@ -20360,7 +20360,7 @@
         </is>
       </c>
       <c r="G10" s="44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" s="44" t="n"/>
     </row>
@@ -20372,7 +20372,7 @@
       </c>
       <c r="B11" s="52" t="inlineStr">
         <is>
-          <t>4年12班</t>
+          <t>6年3班</t>
         </is>
       </c>
       <c r="C11" s="44" t="inlineStr">
@@ -20382,12 +20382,12 @@
       </c>
       <c r="D11" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>四</t>
         </is>
       </c>
       <c r="E11" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F11" s="44" t="inlineStr">
@@ -20408,12 +20408,12 @@
       </c>
       <c r="B12" s="52" t="inlineStr">
         <is>
-          <t>5年3班</t>
+          <t>5年8班</t>
         </is>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>國語</t>
+          <t>數學</t>
         </is>
       </c>
       <c r="D12" s="52" t="inlineStr">
@@ -20444,17 +20444,17 @@
       </c>
       <c r="B13" s="52" t="inlineStr">
         <is>
-          <t>6年6班</t>
+          <t>4年11班</t>
         </is>
       </c>
       <c r="C13" s="44" t="inlineStr">
         <is>
-          <t>國語</t>
+          <t>數學</t>
         </is>
       </c>
       <c r="D13" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="E13" s="52" t="inlineStr">
@@ -20468,7 +20468,7 @@
         </is>
       </c>
       <c r="G13" s="44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" s="44" t="n"/>
     </row>
@@ -20480,7 +20480,7 @@
       </c>
       <c r="B14" s="52" t="inlineStr">
         <is>
-          <t>4年9班</t>
+          <t>4年7班</t>
         </is>
       </c>
       <c r="C14" s="44" t="inlineStr">
@@ -20490,12 +20490,12 @@
       </c>
       <c r="D14" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="E14" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F14" s="44" t="inlineStr">
@@ -20504,7 +20504,7 @@
         </is>
       </c>
       <c r="G14" s="44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" s="44" t="n"/>
     </row>
@@ -24370,7 +24370,7 @@
     <row r="5" ht="15" customHeight="1" s="36">
       <c r="A5" s="44" t="inlineStr">
         <is>
-          <t>體育甲</t>
+          <t>音樂己</t>
         </is>
       </c>
       <c r="B5" s="52" t="inlineStr">
@@ -24380,7 +24380,7 @@
       </c>
       <c r="C5" s="52" t="inlineStr">
         <is>
-          <t>下午</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D5" s="52" t="inlineStr">
@@ -24388,11 +24388,7 @@
           <t>希望</t>
         </is>
       </c>
-      <c r="E5" s="44" t="inlineStr">
-        <is>
-          <t>接送小孩</t>
-        </is>
-      </c>
+      <c r="E5" s="44" t="n"/>
       <c r="F5" s="56">
         <f>IF(A5="","",COUNTIFS($A$5:$A$304,A5,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24401,7 +24397,7 @@
     <row r="6" ht="15" customHeight="1" s="36">
       <c r="A6" s="44" t="inlineStr">
         <is>
-          <t>體育甲</t>
+          <t>體育丁</t>
         </is>
       </c>
       <c r="B6" s="52" t="inlineStr">
@@ -24411,15 +24407,19 @@
       </c>
       <c r="C6" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D6" s="52" t="inlineStr">
         <is>
-          <t>希望</t>
-        </is>
-      </c>
-      <c r="E6" s="44" t="n"/>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E6" s="44" t="inlineStr">
+        <is>
+          <t>身體因素</t>
+        </is>
+      </c>
       <c r="F6" s="56">
         <f>IF(A6="","",COUNTIFS($A$5:$A$304,A6,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24428,17 +24428,17 @@
     <row r="7" ht="15" customHeight="1" s="36">
       <c r="A7" s="44" t="inlineStr">
         <is>
-          <t>自然戊</t>
+          <t>體育丁</t>
         </is>
       </c>
       <c r="B7" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C7" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D7" s="52" t="inlineStr">
@@ -24446,11 +24446,7 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="E7" s="44" t="inlineStr">
-        <is>
-          <t>身體因素</t>
-        </is>
-      </c>
+      <c r="E7" s="44" t="n"/>
       <c r="F7" s="56">
         <f>IF(A7="","",COUNTIFS($A$5:$A$304,A7,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24459,12 +24455,12 @@
     <row r="8" ht="15" customHeight="1" s="36">
       <c r="A8" s="44" t="inlineStr">
         <is>
-          <t>自然戊</t>
+          <t>體育丁</t>
         </is>
       </c>
       <c r="B8" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C8" s="52" t="inlineStr">
@@ -24486,7 +24482,7 @@
     <row r="9" ht="15" customHeight="1" s="36">
       <c r="A9" s="44" t="inlineStr">
         <is>
-          <t>社會乙</t>
+          <t>健康丙</t>
         </is>
       </c>
       <c r="B9" s="52" t="inlineStr">
@@ -24517,12 +24513,12 @@
     <row r="10" ht="15" customHeight="1" s="36">
       <c r="A10" s="44" t="inlineStr">
         <is>
-          <t>社會乙</t>
+          <t>社會丙</t>
         </is>
       </c>
       <c r="B10" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C10" s="52" t="inlineStr">
@@ -24532,10 +24528,14 @@
       </c>
       <c r="D10" s="52" t="inlineStr">
         <is>
-          <t>希望</t>
-        </is>
-      </c>
-      <c r="E10" s="44" t="n"/>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E10" s="44" t="inlineStr">
+        <is>
+          <t>身體因素</t>
+        </is>
+      </c>
       <c r="F10" s="56">
         <f>IF(A10="","",COUNTIFS($A$5:$A$304,A10,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24544,17 +24544,17 @@
     <row r="11" ht="15" customHeight="1" s="36">
       <c r="A11" s="44" t="inlineStr">
         <is>
-          <t>音樂戊</t>
+          <t>社會丙</t>
         </is>
       </c>
       <c r="B11" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C11" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D11" s="52" t="inlineStr">
@@ -24564,7 +24564,7 @@
       </c>
       <c r="E11" s="44" t="inlineStr">
         <is>
-          <t>接送小孩</t>
+          <t>身體因素</t>
         </is>
       </c>
       <c r="F11" s="56">
@@ -24575,29 +24575,25 @@
     <row r="12" ht="15" customHeight="1" s="36">
       <c r="A12" s="44" t="inlineStr">
         <is>
-          <t>音樂戊</t>
+          <t>社會丙</t>
         </is>
       </c>
       <c r="B12" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C12" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E12" s="44" t="inlineStr">
-        <is>
-          <t>進修</t>
-        </is>
-      </c>
+          <t>希望</t>
+        </is>
+      </c>
+      <c r="E12" s="44" t="n"/>
       <c r="F12" s="56">
         <f>IF(A12="","",COUNTIFS($A$5:$A$304,A12,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24606,27 +24602,27 @@
     <row r="13" ht="15" customHeight="1" s="36">
       <c r="A13" s="44" t="inlineStr">
         <is>
-          <t>體育乙</t>
+          <t>資訊甲</t>
         </is>
       </c>
       <c r="B13" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C13" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="D13" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>希望</t>
         </is>
       </c>
       <c r="E13" s="44" t="inlineStr">
         <is>
-          <t>兼任行政會議</t>
+          <t>接送小孩</t>
         </is>
       </c>
       <c r="F13" s="56">
@@ -24637,12 +24633,12 @@
     <row r="14" ht="15" customHeight="1" s="36">
       <c r="A14" s="44" t="inlineStr">
         <is>
-          <t>體育乙</t>
+          <t>健康甲</t>
         </is>
       </c>
       <c r="B14" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C14" s="52" t="inlineStr">
@@ -24655,11 +24651,7 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="E14" s="44" t="inlineStr">
-        <is>
-          <t>兼任行政會議</t>
-        </is>
-      </c>
+      <c r="E14" s="44" t="n"/>
       <c r="F14" s="56">
         <f>IF(A14="","",COUNTIFS($A$5:$A$304,A14,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24668,7 +24660,7 @@
     <row r="15" ht="15" customHeight="1" s="36">
       <c r="A15" s="44" t="inlineStr">
         <is>
-          <t>體育乙</t>
+          <t>健康甲</t>
         </is>
       </c>
       <c r="B15" s="52" t="inlineStr">
@@ -24686,7 +24678,11 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="E15" s="44" t="n"/>
+      <c r="E15" s="44" t="inlineStr">
+        <is>
+          <t>身體因素</t>
+        </is>
+      </c>
       <c r="F15" s="56">
         <f>IF(A15="","",COUNTIFS($A$5:$A$304,A15,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24695,7 +24691,7 @@
     <row r="16" ht="15" customHeight="1" s="36">
       <c r="A16" s="44" t="inlineStr">
         <is>
-          <t>體育乙</t>
+          <t>健康甲</t>
         </is>
       </c>
       <c r="B16" s="52" t="inlineStr">
@@ -24726,25 +24722,29 @@
     <row r="17" ht="15" customHeight="1" s="36">
       <c r="A17" s="44" t="inlineStr">
         <is>
-          <t>體育乙</t>
+          <t>英語丁</t>
         </is>
       </c>
       <c r="B17" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C17" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D17" s="52" t="inlineStr">
         <is>
-          <t>希望</t>
-        </is>
-      </c>
-      <c r="E17" s="44" t="n"/>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E17" s="44" t="inlineStr">
+        <is>
+          <t>進修</t>
+        </is>
+      </c>
       <c r="F17" s="56">
         <f>IF(A17="","",COUNTIFS($A$5:$A$304,A17,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24753,12 +24753,12 @@
     <row r="18" ht="15" customHeight="1" s="36">
       <c r="A18" s="44" t="inlineStr">
         <is>
-          <t>自然乙</t>
+          <t>英語丁</t>
         </is>
       </c>
       <c r="B18" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C18" s="52" t="inlineStr">
@@ -24773,7 +24773,7 @@
       </c>
       <c r="E18" s="44" t="inlineStr">
         <is>
-          <t>進修</t>
+          <t>兼任行政會議</t>
         </is>
       </c>
       <c r="F18" s="56">
@@ -24784,17 +24784,17 @@
     <row r="19" ht="15" customHeight="1" s="36">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>自然乙</t>
+          <t>英語丁</t>
         </is>
       </c>
       <c r="B19" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C19" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D19" s="52" t="inlineStr">
@@ -24804,7 +24804,7 @@
       </c>
       <c r="E19" s="44" t="inlineStr">
         <is>
-          <t>兼任行政會議</t>
+          <t>身體因素</t>
         </is>
       </c>
       <c r="F19" s="56">
@@ -24815,25 +24815,29 @@
     <row r="20" ht="15" customHeight="1" s="36">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>體育丙</t>
+          <t>英語丁</t>
         </is>
       </c>
       <c r="B20" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C20" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="D20" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E20" s="44" t="n"/>
+          <t>希望</t>
+        </is>
+      </c>
+      <c r="E20" s="44" t="inlineStr">
+        <is>
+          <t>接送小孩</t>
+        </is>
+      </c>
       <c r="F20" s="56">
         <f>IF(A20="","",COUNTIFS($A$5:$A$304,A20,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24842,12 +24846,12 @@
     <row r="21" ht="15" customHeight="1" s="36">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>體育己</t>
+          <t>自然丙</t>
         </is>
       </c>
       <c r="B21" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C21" s="52" t="inlineStr">
@@ -24860,11 +24864,7 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="E21" s="44" t="inlineStr">
-        <is>
-          <t>兼任行政會議</t>
-        </is>
-      </c>
+      <c r="E21" s="44" t="n"/>
       <c r="F21" s="56">
         <f>IF(A21="","",COUNTIFS($A$5:$A$304,A21,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24873,27 +24873,27 @@
     <row r="22" ht="15" customHeight="1" s="36">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>體育己</t>
+          <t>自然丙</t>
         </is>
       </c>
       <c r="B22" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C22" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="D22" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>希望</t>
         </is>
       </c>
       <c r="E22" s="44" t="inlineStr">
         <is>
-          <t>兼任行政會議</t>
+          <t>接送小孩</t>
         </is>
       </c>
       <c r="F22" s="56">
@@ -24904,25 +24904,29 @@
     <row r="23" ht="15" customHeight="1" s="36">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>體育己</t>
+          <t>音樂丁</t>
         </is>
       </c>
       <c r="B23" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C23" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D23" s="52" t="inlineStr">
         <is>
-          <t>希望</t>
-        </is>
-      </c>
-      <c r="E23" s="44" t="n"/>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E23" s="44" t="inlineStr">
+        <is>
+          <t>接送小孩</t>
+        </is>
+      </c>
       <c r="F23" s="56">
         <f>IF(A23="","",COUNTIFS($A$5:$A$304,A23,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24931,7 +24935,7 @@
     <row r="24" ht="15" customHeight="1" s="36">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>音樂丙</t>
+          <t>音樂丁</t>
         </is>
       </c>
       <c r="B24" s="52" t="inlineStr">
@@ -24941,7 +24945,7 @@
       </c>
       <c r="C24" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D24" s="52" t="inlineStr">
@@ -24951,7 +24955,7 @@
       </c>
       <c r="E24" s="44" t="inlineStr">
         <is>
-          <t>身體因素</t>
+          <t>接送小孩</t>
         </is>
       </c>
       <c r="F24" s="56">
@@ -24962,12 +24966,12 @@
     <row r="25" ht="15" customHeight="1" s="36">
       <c r="A25" s="44" t="inlineStr">
         <is>
-          <t>音樂丙</t>
+          <t>音樂丁</t>
         </is>
       </c>
       <c r="B25" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C25" s="52" t="inlineStr">
@@ -24980,7 +24984,11 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="E25" s="44" t="n"/>
+      <c r="E25" s="44" t="inlineStr">
+        <is>
+          <t>接送小孩</t>
+        </is>
+      </c>
       <c r="F25" s="56">
         <f>IF(A25="","",COUNTIFS($A$5:$A$304,A25,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24989,7 +24997,7 @@
     <row r="26" ht="15" customHeight="1" s="36">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>音樂丙</t>
+          <t>音樂丁</t>
         </is>
       </c>
       <c r="B26" s="52" t="inlineStr">
@@ -24999,12 +25007,12 @@
       </c>
       <c r="C26" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="D26" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>希望</t>
         </is>
       </c>
       <c r="E26" s="44" t="inlineStr">
@@ -25020,7 +25028,7 @@
     <row r="27" ht="15" customHeight="1" s="36">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>英語戊</t>
+          <t>社會丁</t>
         </is>
       </c>
       <c r="B27" s="52" t="inlineStr">
@@ -25030,12 +25038,12 @@
       </c>
       <c r="C27" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="D27" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>希望</t>
         </is>
       </c>
       <c r="E27" s="44" t="inlineStr">
@@ -25051,7 +25059,7 @@
     <row r="28" ht="15" customHeight="1" s="36">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>英語戊</t>
+          <t>自然乙</t>
         </is>
       </c>
       <c r="B28" s="52" t="inlineStr">
@@ -25061,7 +25069,7 @@
       </c>
       <c r="C28" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D28" s="52" t="inlineStr">
@@ -25071,7 +25079,7 @@
       </c>
       <c r="E28" s="44" t="inlineStr">
         <is>
-          <t>兼任行政會議</t>
+          <t>接送小孩</t>
         </is>
       </c>
       <c r="F28" s="56">
@@ -25082,17 +25090,17 @@
     <row r="29" ht="15" customHeight="1" s="36">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>英語戊</t>
+          <t>自然乙</t>
         </is>
       </c>
       <c r="B29" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C29" s="52" t="inlineStr">
         <is>
-          <t>下午</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D29" s="52" t="inlineStr">
@@ -25100,42 +25108,18 @@
           <t>希望</t>
         </is>
       </c>
-      <c r="E29" s="44" t="inlineStr">
-        <is>
-          <t>接送小孩</t>
-        </is>
-      </c>
+      <c r="E29" s="44" t="n"/>
       <c r="F29" s="56">
         <f>IF(A29="","",COUNTIFS($A$5:$A$304,A29,$D$5:$D$304,"必須"))</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="36">
-      <c r="A30" s="44" t="inlineStr">
-        <is>
-          <t>社會丁</t>
-        </is>
-      </c>
-      <c r="B30" s="52" t="inlineStr">
-        <is>
-          <t>五</t>
-        </is>
-      </c>
-      <c r="C30" s="52" t="inlineStr">
-        <is>
-          <t>下午</t>
-        </is>
-      </c>
-      <c r="D30" s="52" t="inlineStr">
-        <is>
-          <t>希望</t>
-        </is>
-      </c>
-      <c r="E30" s="44" t="inlineStr">
-        <is>
-          <t>接送小孩</t>
-        </is>
-      </c>
+      <c r="A30" s="44" t="n"/>
+      <c r="B30" s="52" t="n"/>
+      <c r="C30" s="52" t="n"/>
+      <c r="D30" s="52" t="n"/>
+      <c r="E30" s="44" t="n"/>
       <c r="F30" s="56">
         <f>IF(A30="","",COUNTIFS($A$5:$A$304,A30,$D$5:$D$304,"必須"))</f>
         <v/>

--- a/試跑/試跑資料_排課需求收集表.xlsx
+++ b/試跑/試跑資料_排課需求收集表.xlsx
@@ -1334,8 +1334,8 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A8:F8"/>
@@ -3548,7 +3548,7 @@
           <t>整天</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" s="35" t="inlineStr">
         <is>
           <t>同科分散</t>
         </is>
@@ -3563,6 +3563,11 @@
       <c r="B12" s="35" t="inlineStr">
         <is>
           <t>1年11班</t>
+        </is>
+      </c>
+      <c r="M12" s="35" t="inlineStr">
+        <is>
+          <t>間隔天數</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="35" min="1" max="1"/>
@@ -4516,7 +4521,7 @@
       </c>
       <c r="E14" s="53" t="inlineStr">
         <is>
-          <t>每班每週3節：2節連堂在自然教室＋1節在原班，三節不連續</t>
+          <t>每班每週3節：2節連堂在自然教室（可跨大下課）＋1節在原班，原班那節排不同天</t>
         </is>
       </c>
       <c r="F14" s="52" t="inlineStr">
@@ -4746,44 +4751,86 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>R17</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>3 盡量</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>同科分散</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="35" t="inlineStr">
         <is>
           <t>所有科任</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="35" t="inlineStr">
         <is>
           <t>同一班同一科一天最多 1 次（連堂算 1 次）</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="35" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="35" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="35" t="inlineStr">
         <is>
           <t>避免同一天上兩次同科</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="inlineStr">
+        <is>
+          <t>R18</t>
+        </is>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>3 盡量</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="inlineStr">
+        <is>
+          <t>間隔天數</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="inlineStr">
+        <is>
+          <t>自然</t>
+        </is>
+      </c>
+      <c r="E21" s="35" t="inlineStr">
+        <is>
+          <t>同一班自然各次上課至少隔 1 天（例：星期一上連堂，原班那節排星期三以後）</t>
+        </is>
+      </c>
+      <c r="F21" s="35" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G21" s="35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H21" s="35" t="inlineStr">
+        <is>
+          <t>Bing 2026-10-21：原班那節要不同天，最好差一天</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4845,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="C4:C40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>選項!$M$2:$M$11</formula1>
+      <formula1>選項!$M$2:$M$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="F4:F40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">

--- a/試跑/試跑資料_排課需求收集表.xlsx
+++ b/試跑/試跑資料_排課需求收集表.xlsx
@@ -17016,7 +17016,7 @@
       </c>
       <c r="B14" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C14" s="52" t="inlineStr">
@@ -17054,7 +17054,7 @@
       </c>
       <c r="C15" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D15" s="52" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="B18" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C18" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D18" s="52" t="inlineStr">
@@ -17186,7 +17186,7 @@
       </c>
       <c r="C19" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D19" s="52" t="inlineStr">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C20" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D20" s="52" t="inlineStr">
@@ -17313,12 +17313,12 @@
       </c>
       <c r="B23" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C23" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D23" s="52" t="inlineStr">
@@ -17351,7 +17351,7 @@
       </c>
       <c r="C24" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D24" s="52" t="inlineStr">
@@ -17379,12 +17379,12 @@
       </c>
       <c r="B25" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C25" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D25" s="52" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="C26" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D26" s="52" t="inlineStr">
@@ -17742,7 +17742,7 @@
       </c>
       <c r="B36" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C36" s="52" t="inlineStr">
@@ -17780,7 +17780,7 @@
       </c>
       <c r="C37" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D37" s="52" t="inlineStr">
@@ -17808,12 +17808,12 @@
       </c>
       <c r="B38" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C38" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D38" s="52" t="inlineStr">
@@ -17841,7 +17841,7 @@
       </c>
       <c r="B39" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C39" s="52" t="inlineStr">
@@ -17874,12 +17874,12 @@
       </c>
       <c r="B40" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C40" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D40" s="52" t="inlineStr">
@@ -17940,12 +17940,12 @@
       </c>
       <c r="B42" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C42" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D42" s="52" t="inlineStr">
@@ -17973,12 +17973,12 @@
       </c>
       <c r="B43" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C43" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D43" s="52" t="inlineStr">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="B44" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C44" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D44" s="52" t="inlineStr">
@@ -18039,12 +18039,12 @@
       </c>
       <c r="B45" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C45" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D45" s="52" t="inlineStr">
@@ -18072,12 +18072,12 @@
       </c>
       <c r="B46" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C46" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D46" s="52" t="inlineStr">
@@ -18105,12 +18105,12 @@
       </c>
       <c r="B47" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C47" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D47" s="52" t="inlineStr">
@@ -18143,7 +18143,7 @@
       </c>
       <c r="C48" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D48" s="52" t="inlineStr">
@@ -18171,12 +18171,12 @@
       </c>
       <c r="B49" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C49" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D49" s="52" t="inlineStr">
@@ -18209,7 +18209,7 @@
       </c>
       <c r="C50" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D50" s="52" t="inlineStr">
@@ -18237,12 +18237,12 @@
       </c>
       <c r="B51" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C51" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D51" s="52" t="inlineStr">
@@ -18270,12 +18270,12 @@
       </c>
       <c r="B52" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C52" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D52" s="52" t="inlineStr">
@@ -18303,12 +18303,12 @@
       </c>
       <c r="B53" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C53" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D53" s="52" t="inlineStr">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="B54" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C54" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D54" s="52" t="inlineStr">
@@ -18369,12 +18369,12 @@
       </c>
       <c r="B55" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C55" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D55" s="52" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="B56" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C56" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D56" s="52" t="inlineStr">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="B57" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C57" s="52" t="inlineStr">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="B58" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C58" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D58" s="52" t="inlineStr">
@@ -18501,7 +18501,7 @@
       </c>
       <c r="B59" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C59" s="52" t="inlineStr">
@@ -18534,12 +18534,12 @@
       </c>
       <c r="B60" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C60" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D60" s="52" t="inlineStr">
@@ -18567,12 +18567,12 @@
       </c>
       <c r="B61" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C61" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D61" s="52" t="inlineStr">
@@ -18600,12 +18600,12 @@
       </c>
       <c r="B62" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C62" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D62" s="52" t="inlineStr">
@@ -18633,12 +18633,12 @@
       </c>
       <c r="B63" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C63" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D63" s="52" t="inlineStr">
@@ -18666,12 +18666,12 @@
       </c>
       <c r="B64" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C64" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D64" s="52" t="inlineStr">
@@ -18699,12 +18699,12 @@
       </c>
       <c r="B65" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C65" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D65" s="52" t="inlineStr">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="B66" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C66" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D66" s="52" t="inlineStr">
@@ -18770,7 +18770,7 @@
       </c>
       <c r="C67" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D67" s="52" t="inlineStr">
@@ -18798,12 +18798,12 @@
       </c>
       <c r="B68" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C68" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D68" s="52" t="inlineStr">
@@ -18831,12 +18831,12 @@
       </c>
       <c r="B69" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C69" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D69" s="52" t="inlineStr">
@@ -18869,7 +18869,7 @@
       </c>
       <c r="C70" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D70" s="52" t="inlineStr">
@@ -18897,12 +18897,12 @@
       </c>
       <c r="B71" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C71" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D71" s="52" t="inlineStr">
@@ -18930,12 +18930,12 @@
       </c>
       <c r="B72" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C72" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D72" s="52" t="inlineStr">
@@ -18968,7 +18968,7 @@
       </c>
       <c r="C73" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D73" s="52" t="inlineStr">
@@ -18996,12 +18996,12 @@
       </c>
       <c r="B74" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C74" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D74" s="52" t="inlineStr">
@@ -19033,12 +19033,12 @@
       </c>
       <c r="B75" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C75" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D75" s="52" t="inlineStr">
@@ -19065,17 +19065,17 @@
     <row r="76" ht="15" customHeight="1" s="36">
       <c r="A76" s="52" t="inlineStr">
         <is>
-          <t>4年6班</t>
+          <t>3年10班</t>
         </is>
       </c>
       <c r="B76" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C76" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D76" s="52" t="inlineStr">
@@ -19102,7 +19102,7 @@
     <row r="77" ht="15" customHeight="1" s="36">
       <c r="A77" s="52" t="inlineStr">
         <is>
-          <t>3年7班</t>
+          <t>1年1班</t>
         </is>
       </c>
       <c r="B77" s="52" t="inlineStr">
@@ -19112,17 +19112,17 @@
       </c>
       <c r="C77" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D77" s="52" t="inlineStr">
         <is>
-          <t>族語</t>
+          <t>客語</t>
         </is>
       </c>
       <c r="E77" s="44" t="inlineStr">
         <is>
-          <t>族語甲</t>
+          <t>客語甲</t>
         </is>
       </c>
       <c r="F77" s="44" t="inlineStr">
@@ -19139,7 +19139,7 @@
     <row r="78" ht="15" customHeight="1" s="36">
       <c r="A78" s="52" t="inlineStr">
         <is>
-          <t>6年7班</t>
+          <t>5年4班</t>
         </is>
       </c>
       <c r="B78" s="52" t="inlineStr">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="C78" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D78" s="52" t="inlineStr">
@@ -19176,27 +19176,27 @@
     <row r="79" ht="15" customHeight="1" s="36">
       <c r="A79" s="52" t="inlineStr">
         <is>
-          <t>5年10班</t>
+          <t>5年7班</t>
         </is>
       </c>
       <c r="B79" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C79" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D79" s="52" t="inlineStr">
         <is>
-          <t>客語</t>
+          <t>族語</t>
         </is>
       </c>
       <c r="E79" s="44" t="inlineStr">
         <is>
-          <t>客語甲</t>
+          <t>族語甲</t>
         </is>
       </c>
       <c r="F79" s="44" t="inlineStr">
@@ -19213,17 +19213,17 @@
     <row r="80" ht="15" customHeight="1" s="36">
       <c r="A80" s="52" t="inlineStr">
         <is>
-          <t>4年12班</t>
+          <t>1年2班</t>
         </is>
       </c>
       <c r="B80" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C80" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D80" s="52" t="inlineStr">
@@ -19250,7 +19250,7 @@
     <row r="81" ht="15" customHeight="1" s="36">
       <c r="A81" s="52" t="inlineStr">
         <is>
-          <t>3年6班</t>
+          <t>4年6班</t>
         </is>
       </c>
       <c r="B81" s="52" t="inlineStr">
@@ -19260,17 +19260,17 @@
       </c>
       <c r="C81" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D81" s="52" t="inlineStr">
         <is>
-          <t>族語</t>
+          <t>客語</t>
         </is>
       </c>
       <c r="E81" s="44" t="inlineStr">
         <is>
-          <t>族語甲</t>
+          <t>客語甲</t>
         </is>
       </c>
       <c r="F81" s="44" t="inlineStr">
@@ -19287,27 +19287,27 @@
     <row r="82" ht="15" customHeight="1" s="36">
       <c r="A82" s="52" t="inlineStr">
         <is>
-          <t>4年7班</t>
+          <t>3年7班</t>
         </is>
       </c>
       <c r="B82" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C82" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D82" s="52" t="inlineStr">
         <is>
-          <t>新住民語</t>
+          <t>族語</t>
         </is>
       </c>
       <c r="E82" s="44" t="inlineStr">
         <is>
-          <t>新住民語甲</t>
+          <t>族語甲</t>
         </is>
       </c>
       <c r="F82" s="44" t="inlineStr">
@@ -19324,7 +19324,7 @@
     <row r="83" ht="15" customHeight="1" s="36">
       <c r="A83" s="52" t="inlineStr">
         <is>
-          <t>3年11班</t>
+          <t>6年7班</t>
         </is>
       </c>
       <c r="B83" s="52" t="inlineStr">
@@ -19334,17 +19334,17 @@
       </c>
       <c r="C83" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D83" s="52" t="inlineStr">
         <is>
-          <t>族語</t>
+          <t>客語</t>
         </is>
       </c>
       <c r="E83" s="44" t="inlineStr">
         <is>
-          <t>族語甲</t>
+          <t>客語甲</t>
         </is>
       </c>
       <c r="F83" s="44" t="inlineStr">
@@ -19361,27 +19361,27 @@
     <row r="84" ht="15" customHeight="1" s="36">
       <c r="A84" s="52" t="inlineStr">
         <is>
-          <t>1年10班</t>
+          <t>1年11班</t>
         </is>
       </c>
       <c r="B84" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C84" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D84" s="52" t="inlineStr">
         <is>
-          <t>新住民語</t>
+          <t>客語</t>
         </is>
       </c>
       <c r="E84" s="44" t="inlineStr">
         <is>
-          <t>新住民語甲</t>
+          <t>客語甲</t>
         </is>
       </c>
       <c r="F84" s="44" t="inlineStr">
@@ -19398,7 +19398,7 @@
     <row r="85" ht="15" customHeight="1" s="36">
       <c r="A85" s="52" t="inlineStr">
         <is>
-          <t>1年6班</t>
+          <t>6年11班</t>
         </is>
       </c>
       <c r="B85" s="52" t="inlineStr">
@@ -19408,17 +19408,17 @@
       </c>
       <c r="C85" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D85" s="52" t="inlineStr">
         <is>
-          <t>客語</t>
+          <t>族語</t>
         </is>
       </c>
       <c r="E85" s="44" t="inlineStr">
         <is>
-          <t>客語甲</t>
+          <t>族語甲</t>
         </is>
       </c>
       <c r="F85" s="44" t="inlineStr">
@@ -20203,7 +20203,7 @@
       </c>
       <c r="B5" s="52" t="inlineStr">
         <is>
-          <t>6年12班</t>
+          <t>5年4班</t>
         </is>
       </c>
       <c r="C5" s="44" t="inlineStr">
@@ -20218,7 +20218,7 @@
       </c>
       <c r="E5" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F5" s="44" t="inlineStr">
@@ -20227,7 +20227,7 @@
         </is>
       </c>
       <c r="G5" s="44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" s="44" t="n"/>
     </row>
@@ -20239,17 +20239,17 @@
       </c>
       <c r="B6" s="52" t="inlineStr">
         <is>
-          <t>2年1班</t>
+          <t>4年1班</t>
         </is>
       </c>
       <c r="C6" s="44" t="inlineStr">
         <is>
-          <t>國語</t>
+          <t>數學</t>
         </is>
       </c>
       <c r="D6" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>二</t>
         </is>
       </c>
       <c r="E6" s="52" t="inlineStr">
@@ -20275,7 +20275,7 @@
       </c>
       <c r="B7" s="52" t="inlineStr">
         <is>
-          <t>3年1班</t>
+          <t>4年8班</t>
         </is>
       </c>
       <c r="C7" s="44" t="inlineStr">
@@ -20290,7 +20290,7 @@
       </c>
       <c r="E7" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F7" s="44" t="inlineStr">
@@ -20311,22 +20311,22 @@
       </c>
       <c r="B8" s="52" t="inlineStr">
         <is>
-          <t>5年6班</t>
+          <t>6年11班</t>
         </is>
       </c>
       <c r="C8" s="44" t="inlineStr">
         <is>
-          <t>數學</t>
+          <t>國語</t>
         </is>
       </c>
       <c r="D8" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>三</t>
         </is>
       </c>
       <c r="E8" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F8" s="44" t="inlineStr">
@@ -20335,7 +20335,7 @@
         </is>
       </c>
       <c r="G8" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="44" t="n"/>
     </row>
@@ -20347,22 +20347,22 @@
       </c>
       <c r="B9" s="52" t="inlineStr">
         <is>
-          <t>4年8班</t>
+          <t>4年5班</t>
         </is>
       </c>
       <c r="C9" s="44" t="inlineStr">
         <is>
-          <t>國語</t>
+          <t>數學</t>
         </is>
       </c>
       <c r="D9" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>四</t>
         </is>
       </c>
       <c r="E9" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F9" s="44" t="inlineStr">
@@ -20371,7 +20371,7 @@
         </is>
       </c>
       <c r="G9" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="44" t="n"/>
     </row>
@@ -20383,22 +20383,22 @@
       </c>
       <c r="B10" s="52" t="inlineStr">
         <is>
-          <t>3年2班</t>
+          <t>2年1班</t>
         </is>
       </c>
       <c r="C10" s="44" t="inlineStr">
         <is>
-          <t>數學</t>
+          <t>國語</t>
         </is>
       </c>
       <c r="D10" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>三</t>
         </is>
       </c>
       <c r="E10" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F10" s="44" t="inlineStr">
@@ -20407,7 +20407,7 @@
         </is>
       </c>
       <c r="G10" s="44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" s="44" t="n"/>
     </row>
@@ -20419,7 +20419,7 @@
       </c>
       <c r="B11" s="52" t="inlineStr">
         <is>
-          <t>6年3班</t>
+          <t>6年7班</t>
         </is>
       </c>
       <c r="C11" s="44" t="inlineStr">
@@ -20429,12 +20429,12 @@
       </c>
       <c r="D11" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="E11" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F11" s="44" t="inlineStr">
@@ -20443,7 +20443,7 @@
         </is>
       </c>
       <c r="G11" s="44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="44" t="n"/>
     </row>
@@ -20455,7 +20455,7 @@
       </c>
       <c r="B12" s="52" t="inlineStr">
         <is>
-          <t>5年8班</t>
+          <t>3年1班</t>
         </is>
       </c>
       <c r="C12" s="44" t="inlineStr">
@@ -20465,12 +20465,12 @@
       </c>
       <c r="D12" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>四</t>
         </is>
       </c>
       <c r="E12" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F12" s="44" t="inlineStr">
@@ -20479,7 +20479,7 @@
         </is>
       </c>
       <c r="G12" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="44" t="n"/>
     </row>
@@ -20491,7 +20491,7 @@
       </c>
       <c r="B13" s="52" t="inlineStr">
         <is>
-          <t>4年11班</t>
+          <t>5年6班</t>
         </is>
       </c>
       <c r="C13" s="44" t="inlineStr">
@@ -20506,7 +20506,7 @@
       </c>
       <c r="E13" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F13" s="44" t="inlineStr">
@@ -20515,7 +20515,7 @@
         </is>
       </c>
       <c r="G13" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" s="44" t="n"/>
     </row>
@@ -20527,22 +20527,22 @@
       </c>
       <c r="B14" s="52" t="inlineStr">
         <is>
-          <t>4年7班</t>
+          <t>6年10班</t>
         </is>
       </c>
       <c r="C14" s="44" t="inlineStr">
         <is>
-          <t>國語</t>
+          <t>數學</t>
         </is>
       </c>
       <c r="D14" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="E14" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F14" s="44" t="inlineStr">
@@ -21893,7 +21893,7 @@
       </c>
       <c r="G7" s="44" t="inlineStr">
         <is>
-          <t>（試跑假設）星期三下午全校不上課</t>
+          <t>星期三下午半天</t>
         </is>
       </c>
     </row>
@@ -21930,7 +21930,7 @@
       </c>
       <c r="G8" s="44" t="inlineStr">
         <is>
-          <t>（試跑假設）低年級只有星期二整天</t>
+          <t>低年級只有星期二整天</t>
         </is>
       </c>
     </row>
@@ -21967,7 +21967,7 @@
       </c>
       <c r="G9" s="44" t="inlineStr">
         <is>
-          <t>（試跑假設）低年級只有星期二整天</t>
+          <t>低年級只有星期二整天</t>
         </is>
       </c>
     </row>
@@ -22004,7 +22004,7 @@
       </c>
       <c r="G10" s="44" t="inlineStr">
         <is>
-          <t>（試跑假設）低年級只有星期二整天</t>
+          <t>低年級只有星期二整天</t>
         </is>
       </c>
     </row>
@@ -22041,27 +22041,63 @@
       </c>
       <c r="G11" s="44" t="inlineStr">
         <is>
-          <t>（試跑假設）低年級只有星期二整天</t>
+          <t>低年級只有星期二整天</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="36">
-      <c r="A12" s="44" t="n"/>
-      <c r="B12" s="52" t="n"/>
-      <c r="C12" s="44" t="n"/>
-      <c r="D12" s="44" t="n"/>
-      <c r="E12" s="44" t="n"/>
-      <c r="F12" s="44" t="n"/>
-      <c r="G12" s="44" t="n"/>
+      <c r="A12" s="44" t="inlineStr">
+        <is>
+          <t>三、四年級</t>
+        </is>
+      </c>
+      <c r="B12" s="52" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C12" s="44" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D12" s="44" t="inlineStr">
+        <is>
+          <t>不上課</t>
+        </is>
+      </c>
+      <c r="E12" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="44" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G12" s="44" t="inlineStr">
+        <is>
+          <t>中年級星期一、二、四整天</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="36">
       <c r="A13" s="44" t="n"/>
       <c r="B13" s="52" t="n"/>
       <c r="C13" s="44" t="n"/>
-      <c r="D13" s="44" t="n"/>
+      <c r="D13" s="44" t="inlineStr">
+        <is>
+          <t>（學校共同課）</t>
+        </is>
+      </c>
       <c r="E13" s="44" t="n"/>
       <c r="F13" s="44" t="n"/>
-      <c r="G13" s="44" t="n"/>
+      <c r="G13" s="44" t="inlineStr">
+        <is>
+          <t>請補填</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="36">
       <c r="A14" s="44" t="n"/>
@@ -22196,7 +22232,7 @@
       <c r="E4" s="54" t="n"/>
       <c r="G4" s="54" t="inlineStr">
         <is>
-          <t>英語丙</t>
+          <t>英語戊</t>
         </is>
       </c>
       <c r="H4" s="54" t="inlineStr">
@@ -22229,7 +22265,7 @@
       <c r="E5" s="44" t="n"/>
       <c r="G5" s="44" t="inlineStr">
         <is>
-          <t>自然丁</t>
+          <t>自然戊</t>
         </is>
       </c>
       <c r="H5" s="44" t="inlineStr">
@@ -24417,7 +24453,7 @@
     <row r="5" ht="15" customHeight="1" s="36">
       <c r="A5" s="44" t="inlineStr">
         <is>
-          <t>音樂己</t>
+          <t>體育己</t>
         </is>
       </c>
       <c r="B5" s="52" t="inlineStr">
@@ -24427,7 +24463,7 @@
       </c>
       <c r="C5" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="D5" s="52" t="inlineStr">
@@ -24435,7 +24471,11 @@
           <t>希望</t>
         </is>
       </c>
-      <c r="E5" s="44" t="n"/>
+      <c r="E5" s="44" t="inlineStr">
+        <is>
+          <t>接送小孩</t>
+        </is>
+      </c>
       <c r="F5" s="56">
         <f>IF(A5="","",COUNTIFS($A$5:$A$304,A5,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24444,29 +24484,25 @@
     <row r="6" ht="15" customHeight="1" s="36">
       <c r="A6" s="44" t="inlineStr">
         <is>
-          <t>體育丁</t>
+          <t>體育甲</t>
         </is>
       </c>
       <c r="B6" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C6" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E6" s="44" t="inlineStr">
-        <is>
-          <t>身體因素</t>
-        </is>
-      </c>
+          <t>希望</t>
+        </is>
+      </c>
+      <c r="E6" s="44" t="n"/>
       <c r="F6" s="56">
         <f>IF(A6="","",COUNTIFS($A$5:$A$304,A6,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24475,22 +24511,22 @@
     <row r="7" ht="15" customHeight="1" s="36">
       <c r="A7" s="44" t="inlineStr">
         <is>
-          <t>體育丁</t>
+          <t>英語甲</t>
         </is>
       </c>
       <c r="B7" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C7" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>希望</t>
         </is>
       </c>
       <c r="E7" s="44" t="n"/>
@@ -24502,17 +24538,17 @@
     <row r="8" ht="15" customHeight="1" s="36">
       <c r="A8" s="44" t="inlineStr">
         <is>
-          <t>體育丁</t>
+          <t>音樂甲</t>
         </is>
       </c>
       <c r="B8" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C8" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="D8" s="52" t="inlineStr">
@@ -24520,7 +24556,11 @@
           <t>希望</t>
         </is>
       </c>
-      <c r="E8" s="44" t="n"/>
+      <c r="E8" s="44" t="inlineStr">
+        <is>
+          <t>接送小孩</t>
+        </is>
+      </c>
       <c r="F8" s="56">
         <f>IF(A8="","",COUNTIFS($A$5:$A$304,A8,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24529,7 +24569,7 @@
     <row r="9" ht="15" customHeight="1" s="36">
       <c r="A9" s="44" t="inlineStr">
         <is>
-          <t>健康丙</t>
+          <t>音樂戊</t>
         </is>
       </c>
       <c r="B9" s="52" t="inlineStr">
@@ -24539,12 +24579,12 @@
       </c>
       <c r="C9" s="52" t="inlineStr">
         <is>
-          <t>下午</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D9" s="52" t="inlineStr">
         <is>
-          <t>希望</t>
+          <t>必須</t>
         </is>
       </c>
       <c r="E9" s="44" t="inlineStr">
@@ -24560,12 +24600,12 @@
     <row r="10" ht="15" customHeight="1" s="36">
       <c r="A10" s="44" t="inlineStr">
         <is>
-          <t>社會丙</t>
+          <t>音樂戊</t>
         </is>
       </c>
       <c r="B10" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C10" s="52" t="inlineStr">
@@ -24580,7 +24620,7 @@
       </c>
       <c r="E10" s="44" t="inlineStr">
         <is>
-          <t>身體因素</t>
+          <t>兼任行政會議</t>
         </is>
       </c>
       <c r="F10" s="56">
@@ -24591,7 +24631,7 @@
     <row r="11" ht="15" customHeight="1" s="36">
       <c r="A11" s="44" t="inlineStr">
         <is>
-          <t>社會丙</t>
+          <t>音樂戊</t>
         </is>
       </c>
       <c r="B11" s="52" t="inlineStr">
@@ -24601,17 +24641,17 @@
       </c>
       <c r="C11" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="D11" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>希望</t>
         </is>
       </c>
       <c r="E11" s="44" t="inlineStr">
         <is>
-          <t>身體因素</t>
+          <t>接送小孩</t>
         </is>
       </c>
       <c r="F11" s="56">
@@ -24622,17 +24662,17 @@
     <row r="12" ht="15" customHeight="1" s="36">
       <c r="A12" s="44" t="inlineStr">
         <is>
-          <t>社會丙</t>
+          <t>體育戊</t>
         </is>
       </c>
       <c r="B12" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C12" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="D12" s="52" t="inlineStr">
@@ -24640,7 +24680,11 @@
           <t>希望</t>
         </is>
       </c>
-      <c r="E12" s="44" t="n"/>
+      <c r="E12" s="44" t="inlineStr">
+        <is>
+          <t>接送小孩</t>
+        </is>
+      </c>
       <c r="F12" s="56">
         <f>IF(A12="","",COUNTIFS($A$5:$A$304,A12,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24649,22 +24693,22 @@
     <row r="13" ht="15" customHeight="1" s="36">
       <c r="A13" s="44" t="inlineStr">
         <is>
-          <t>資訊甲</t>
+          <t>資訊乙</t>
         </is>
       </c>
       <c r="B13" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C13" s="52" t="inlineStr">
         <is>
-          <t>下午</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D13" s="52" t="inlineStr">
         <is>
-          <t>希望</t>
+          <t>必須</t>
         </is>
       </c>
       <c r="E13" s="44" t="inlineStr">
@@ -24680,7 +24724,7 @@
     <row r="14" ht="15" customHeight="1" s="36">
       <c r="A14" s="44" t="inlineStr">
         <is>
-          <t>健康甲</t>
+          <t>資訊乙</t>
         </is>
       </c>
       <c r="B14" s="52" t="inlineStr">
@@ -24690,7 +24734,7 @@
       </c>
       <c r="C14" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D14" s="52" t="inlineStr">
@@ -24698,7 +24742,11 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="E14" s="44" t="n"/>
+      <c r="E14" s="44" t="inlineStr">
+        <is>
+          <t>進修</t>
+        </is>
+      </c>
       <c r="F14" s="56">
         <f>IF(A14="","",COUNTIFS($A$5:$A$304,A14,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24707,29 +24755,25 @@
     <row r="15" ht="15" customHeight="1" s="36">
       <c r="A15" s="44" t="inlineStr">
         <is>
-          <t>健康甲</t>
+          <t>資訊乙</t>
         </is>
       </c>
       <c r="B15" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C15" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D15" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E15" s="44" t="inlineStr">
-        <is>
-          <t>身體因素</t>
-        </is>
-      </c>
+          <t>希望</t>
+        </is>
+      </c>
+      <c r="E15" s="44" t="n"/>
       <c r="F15" s="56">
         <f>IF(A15="","",COUNTIFS($A$5:$A$304,A15,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24738,7 +24782,7 @@
     <row r="16" ht="15" customHeight="1" s="36">
       <c r="A16" s="44" t="inlineStr">
         <is>
-          <t>健康甲</t>
+          <t>健康丙</t>
         </is>
       </c>
       <c r="B16" s="52" t="inlineStr">
@@ -24748,19 +24792,15 @@
       </c>
       <c r="C16" s="52" t="inlineStr">
         <is>
-          <t>下午</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D16" s="52" t="inlineStr">
         <is>
-          <t>希望</t>
-        </is>
-      </c>
-      <c r="E16" s="44" t="inlineStr">
-        <is>
-          <t>接送小孩</t>
-        </is>
-      </c>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E16" s="44" t="n"/>
       <c r="F16" s="56">
         <f>IF(A16="","",COUNTIFS($A$5:$A$304,A16,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24769,7 +24809,7 @@
     <row r="17" ht="15" customHeight="1" s="36">
       <c r="A17" s="44" t="inlineStr">
         <is>
-          <t>英語丁</t>
+          <t>健康丙</t>
         </is>
       </c>
       <c r="B17" s="52" t="inlineStr">
@@ -24779,7 +24819,7 @@
       </c>
       <c r="C17" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D17" s="52" t="inlineStr">
@@ -24787,11 +24827,7 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="E17" s="44" t="inlineStr">
-        <is>
-          <t>進修</t>
-        </is>
-      </c>
+      <c r="E17" s="44" t="n"/>
       <c r="F17" s="56">
         <f>IF(A17="","",COUNTIFS($A$5:$A$304,A17,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24800,27 +24836,27 @@
     <row r="18" ht="15" customHeight="1" s="36">
       <c r="A18" s="44" t="inlineStr">
         <is>
-          <t>英語丁</t>
+          <t>健康丙</t>
         </is>
       </c>
       <c r="B18" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C18" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="D18" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>希望</t>
         </is>
       </c>
       <c r="E18" s="44" t="inlineStr">
         <is>
-          <t>兼任行政會議</t>
+          <t>接送小孩</t>
         </is>
       </c>
       <c r="F18" s="56">
@@ -24831,29 +24867,25 @@
     <row r="19" ht="15" customHeight="1" s="36">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>英語丁</t>
+          <t>健康丙</t>
         </is>
       </c>
       <c r="B19" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C19" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E19" s="44" t="inlineStr">
-        <is>
-          <t>身體因素</t>
-        </is>
-      </c>
+          <t>希望</t>
+        </is>
+      </c>
+      <c r="E19" s="44" t="n"/>
       <c r="F19" s="56">
         <f>IF(A19="","",COUNTIFS($A$5:$A$304,A19,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24862,27 +24894,27 @@
     <row r="20" ht="15" customHeight="1" s="36">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>英語丁</t>
+          <t>社會丙</t>
         </is>
       </c>
       <c r="B20" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C20" s="52" t="inlineStr">
         <is>
-          <t>下午</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D20" s="52" t="inlineStr">
         <is>
-          <t>希望</t>
+          <t>必須</t>
         </is>
       </c>
       <c r="E20" s="44" t="inlineStr">
         <is>
-          <t>接送小孩</t>
+          <t>身體因素</t>
         </is>
       </c>
       <c r="F20" s="56">
@@ -24893,7 +24925,7 @@
     <row r="21" ht="15" customHeight="1" s="36">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>自然丙</t>
+          <t>社會丙</t>
         </is>
       </c>
       <c r="B21" s="52" t="inlineStr">
@@ -24903,7 +24935,7 @@
       </c>
       <c r="C21" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D21" s="52" t="inlineStr">
@@ -24911,7 +24943,11 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="E21" s="44" t="n"/>
+      <c r="E21" s="44" t="inlineStr">
+        <is>
+          <t>進修</t>
+        </is>
+      </c>
       <c r="F21" s="56">
         <f>IF(A21="","",COUNTIFS($A$5:$A$304,A21,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24920,7 +24956,7 @@
     <row r="22" ht="15" customHeight="1" s="36">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>自然丙</t>
+          <t>社會丙</t>
         </is>
       </c>
       <c r="B22" s="52" t="inlineStr">
@@ -24930,19 +24966,15 @@
       </c>
       <c r="C22" s="52" t="inlineStr">
         <is>
-          <t>下午</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D22" s="52" t="inlineStr">
         <is>
-          <t>希望</t>
-        </is>
-      </c>
-      <c r="E22" s="44" t="inlineStr">
-        <is>
-          <t>接送小孩</t>
-        </is>
-      </c>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E22" s="44" t="n"/>
       <c r="F22" s="56">
         <f>IF(A22="","",COUNTIFS($A$5:$A$304,A22,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24951,22 +24983,22 @@
     <row r="23" ht="15" customHeight="1" s="36">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>音樂丁</t>
+          <t>社會丙</t>
         </is>
       </c>
       <c r="B23" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C23" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="D23" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>希望</t>
         </is>
       </c>
       <c r="E23" s="44" t="inlineStr">
@@ -24980,181 +25012,65 @@
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="36">
-      <c r="A24" s="44" t="inlineStr">
-        <is>
-          <t>音樂丁</t>
-        </is>
-      </c>
-      <c r="B24" s="52" t="inlineStr">
-        <is>
-          <t>三</t>
-        </is>
-      </c>
-      <c r="C24" s="52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D24" s="52" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E24" s="44" t="inlineStr">
-        <is>
-          <t>接送小孩</t>
-        </is>
-      </c>
+      <c r="A24" s="44" t="n"/>
+      <c r="B24" s="52" t="n"/>
+      <c r="C24" s="52" t="n"/>
+      <c r="D24" s="52" t="n"/>
+      <c r="E24" s="44" t="n"/>
       <c r="F24" s="56">
         <f>IF(A24="","",COUNTIFS($A$5:$A$304,A24,$D$5:$D$304,"必須"))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="36">
-      <c r="A25" s="44" t="inlineStr">
-        <is>
-          <t>音樂丁</t>
-        </is>
-      </c>
-      <c r="B25" s="52" t="inlineStr">
-        <is>
-          <t>二</t>
-        </is>
-      </c>
-      <c r="C25" s="52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D25" s="52" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E25" s="44" t="inlineStr">
-        <is>
-          <t>接送小孩</t>
-        </is>
-      </c>
+      <c r="A25" s="44" t="n"/>
+      <c r="B25" s="52" t="n"/>
+      <c r="C25" s="52" t="n"/>
+      <c r="D25" s="52" t="n"/>
+      <c r="E25" s="44" t="n"/>
       <c r="F25" s="56">
         <f>IF(A25="","",COUNTIFS($A$5:$A$304,A25,$D$5:$D$304,"必須"))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="36">
-      <c r="A26" s="44" t="inlineStr">
-        <is>
-          <t>音樂丁</t>
-        </is>
-      </c>
-      <c r="B26" s="52" t="inlineStr">
-        <is>
-          <t>五</t>
-        </is>
-      </c>
-      <c r="C26" s="52" t="inlineStr">
-        <is>
-          <t>下午</t>
-        </is>
-      </c>
-      <c r="D26" s="52" t="inlineStr">
-        <is>
-          <t>希望</t>
-        </is>
-      </c>
-      <c r="E26" s="44" t="inlineStr">
-        <is>
-          <t>接送小孩</t>
-        </is>
-      </c>
+      <c r="A26" s="44" t="n"/>
+      <c r="B26" s="52" t="n"/>
+      <c r="C26" s="52" t="n"/>
+      <c r="D26" s="52" t="n"/>
+      <c r="E26" s="44" t="n"/>
       <c r="F26" s="56">
         <f>IF(A26="","",COUNTIFS($A$5:$A$304,A26,$D$5:$D$304,"必須"))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="36">
-      <c r="A27" s="44" t="inlineStr">
-        <is>
-          <t>社會丁</t>
-        </is>
-      </c>
-      <c r="B27" s="52" t="inlineStr">
-        <is>
-          <t>五</t>
-        </is>
-      </c>
-      <c r="C27" s="52" t="inlineStr">
-        <is>
-          <t>下午</t>
-        </is>
-      </c>
-      <c r="D27" s="52" t="inlineStr">
-        <is>
-          <t>希望</t>
-        </is>
-      </c>
-      <c r="E27" s="44" t="inlineStr">
-        <is>
-          <t>接送小孩</t>
-        </is>
-      </c>
+      <c r="A27" s="44" t="n"/>
+      <c r="B27" s="52" t="n"/>
+      <c r="C27" s="52" t="n"/>
+      <c r="D27" s="52" t="n"/>
+      <c r="E27" s="44" t="n"/>
       <c r="F27" s="56">
         <f>IF(A27="","",COUNTIFS($A$5:$A$304,A27,$D$5:$D$304,"必須"))</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="36">
-      <c r="A28" s="44" t="inlineStr">
-        <is>
-          <t>自然乙</t>
-        </is>
-      </c>
-      <c r="B28" s="52" t="inlineStr">
-        <is>
-          <t>四</t>
-        </is>
-      </c>
-      <c r="C28" s="52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D28" s="52" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E28" s="44" t="inlineStr">
-        <is>
-          <t>接送小孩</t>
-        </is>
-      </c>
+      <c r="A28" s="44" t="n"/>
+      <c r="B28" s="52" t="n"/>
+      <c r="C28" s="52" t="n"/>
+      <c r="D28" s="52" t="n"/>
+      <c r="E28" s="44" t="n"/>
       <c r="F28" s="56">
         <f>IF(A28="","",COUNTIFS($A$5:$A$304,A28,$D$5:$D$304,"必須"))</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="36">
-      <c r="A29" s="44" t="inlineStr">
-        <is>
-          <t>自然乙</t>
-        </is>
-      </c>
-      <c r="B29" s="52" t="inlineStr">
-        <is>
-          <t>四</t>
-        </is>
-      </c>
-      <c r="C29" s="52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D29" s="52" t="inlineStr">
-        <is>
-          <t>希望</t>
-        </is>
-      </c>
+      <c r="A29" s="44" t="n"/>
+      <c r="B29" s="52" t="n"/>
+      <c r="C29" s="52" t="n"/>
+      <c r="D29" s="52" t="n"/>
       <c r="E29" s="44" t="n"/>
       <c r="F29" s="56">
         <f>IF(A29="","",COUNTIFS($A$5:$A$304,A29,$D$5:$D$304,"必須"))</f>

--- a/試跑/試跑資料_排課需求收集表.xlsx
+++ b/試跑/試跑資料_排課需求收集表.xlsx
@@ -4788,7 +4788,7 @@
       </c>
       <c r="H20" s="35" t="inlineStr">
         <is>
-          <t>避免同一天上兩次同科</t>
+          <t>避免同一天上兩次同科（Bing 2026-10-21 確認保留）</t>
         </is>
       </c>
     </row>

--- a/試跑/試跑資料_排課需求收集表.xlsx
+++ b/試跑/試跑資料_排課需求收集表.xlsx
@@ -16,9 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="職務限制" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="班級教室" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老師需求" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老師需求單" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="節數檢核" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="選項" sheetId="12" state="hidden" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="班級需求" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老師需求單" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="節數檢核" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="選項" sheetId="13" state="hidden" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'規則表'!$3:$3</definedName>
@@ -29,7 +30,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'職務限制'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'班級教室'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'老師需求'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'節數檢核'!$3:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'節數檢核'!$3:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -1127,6 +1128,959 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="36" min="1" max="1"/>
+    <col width="14" customWidth="1" style="36" min="2" max="2"/>
+    <col width="14" customWidth="1" style="36" min="3" max="3"/>
+    <col width="10" customWidth="1" style="36" min="4" max="4"/>
+    <col width="36" customWidth="1" style="36" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>8-2. 班級需求（導師的需求）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>一列＝一個班級不想排科任的時段。班級可填單一班（3年1班）或整個年級（一、二年級）；星期可填一～五、「每天」或「二、四擇一」（系統挑一天）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>班級</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>星期</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>節次／時段</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>程度</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>原因（選填）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>一、二年級</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>每天</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1、4</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>第 1、4 節導師上課（低年級全部）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3年10班</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>二、四擇一</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>至少一個整天的下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3年11班</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>二、四擇一</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>至少一個整天的下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3年12班</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>二、四擇一</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>至少一個整天的下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3年1班</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>二、四擇一</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>至少一個整天的下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3年2班</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>二、四擇一</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>至少一個整天的下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3年4班</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>二、四擇一</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>至少一個整天的下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3年5班</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>二、四擇一</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>至少一個整天的下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3年9班</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>二、四擇一</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>至少一個整天的下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>4年12班</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>二、四擇一</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>至少一個整天的下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4年1班</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>二、四擇一</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>至少一個整天的下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4年6班</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>二、四擇一</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>至少一個整天的下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4年9班</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>二、四擇一</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>至少一個整天的下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>5年10班</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>星期五下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>5年11班</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>星期五下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5年12班</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>星期五下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5年1班</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>星期五下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>5年2班</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>星期五下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>5年3班</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>星期五下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>5年5班</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>星期五下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>5年6班</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>星期五下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>5年7班</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>星期五下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>5年8班</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>星期五下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>5年9班</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>星期五下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6年10班</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>星期五下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>6年11班</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>星期五下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>6年12班</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>星期五下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>6年1班</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>星期五下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>6年2班</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>星期五下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>6年3班</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>星期五下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>6年4班</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>星期五下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>6年5班</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>星期五下午不排科任</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>6年9班</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>星期五下午不排科任</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
@@ -1350,7 +2304,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3073,7 +4027,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3580,6 +4534,11 @@
       <c r="B13" s="35" t="inlineStr">
         <is>
           <t>1年12班</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>班級不排時段</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="35" min="1" max="1"/>
@@ -4831,6 +5790,90 @@
       <c r="H21" s="35" t="inlineStr">
         <is>
           <t>Bing 2026-10-21：原班那節要不同天，最好差一天</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>R19</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2 必須</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>班級不排時段</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>個別班級</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>導師勾「必須」的時段不排科任（依「班級需求」頁；可填「每天」「二、四擇一」）</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>導師需要自己上課的時段</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>R20</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>3 盡量</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>班級不排時段</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>個別班級</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>導師勾「希望」的時段盡量不排科任（依「班級需求」頁）</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>導師的希望</t>
         </is>
       </c>
     </row>
@@ -5016,7 +6059,7 @@
       </c>
       <c r="C6" s="52" t="inlineStr">
         <is>
-          <t>1年2班</t>
+          <t>2年1班</t>
         </is>
       </c>
       <c r="D6" s="44" t="n">
@@ -5047,11 +6090,11 @@
       </c>
       <c r="C7" s="52" t="inlineStr">
         <is>
-          <t>1年3班</t>
+          <t>3年1班</t>
         </is>
       </c>
       <c r="D7" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="52" t="inlineStr">
         <is>
@@ -5078,11 +6121,11 @@
       </c>
       <c r="C8" s="52" t="inlineStr">
         <is>
-          <t>1年4班</t>
+          <t>4年1班</t>
         </is>
       </c>
       <c r="D8" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="52" t="inlineStr">
         <is>
@@ -5109,11 +6152,11 @@
       </c>
       <c r="C9" s="52" t="inlineStr">
         <is>
-          <t>1年5班</t>
+          <t>5年1班</t>
         </is>
       </c>
       <c r="D9" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="52" t="inlineStr">
         <is>
@@ -5140,11 +6183,11 @@
       </c>
       <c r="C10" s="52" t="inlineStr">
         <is>
-          <t>1年6班</t>
+          <t>6年1班</t>
         </is>
       </c>
       <c r="D10" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="52" t="inlineStr">
         <is>
@@ -5171,7 +6214,7 @@
       </c>
       <c r="C11" s="52" t="inlineStr">
         <is>
-          <t>1年7班</t>
+          <t>1年2班</t>
         </is>
       </c>
       <c r="D11" s="44" t="n">
@@ -5202,7 +6245,7 @@
       </c>
       <c r="C12" s="52" t="inlineStr">
         <is>
-          <t>1年8班</t>
+          <t>2年2班</t>
         </is>
       </c>
       <c r="D12" s="44" t="n">
@@ -5233,11 +6276,11 @@
       </c>
       <c r="C13" s="52" t="inlineStr">
         <is>
-          <t>1年9班</t>
+          <t>3年2班</t>
         </is>
       </c>
       <c r="D13" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="52" t="inlineStr">
         <is>
@@ -5264,11 +6307,11 @@
       </c>
       <c r="C14" s="52" t="inlineStr">
         <is>
-          <t>1年10班</t>
+          <t>4年2班</t>
         </is>
       </c>
       <c r="D14" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="52" t="inlineStr">
         <is>
@@ -5295,11 +6338,11 @@
       </c>
       <c r="C15" s="52" t="inlineStr">
         <is>
-          <t>1年11班</t>
+          <t>5年2班</t>
         </is>
       </c>
       <c r="D15" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="52" t="inlineStr">
         <is>
@@ -5326,11 +6369,11 @@
       </c>
       <c r="C16" s="52" t="inlineStr">
         <is>
-          <t>1年12班</t>
+          <t>6年2班</t>
         </is>
       </c>
       <c r="D16" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="52" t="inlineStr">
         <is>
@@ -5347,7 +6390,7 @@
     <row r="17" ht="15" customHeight="1" s="36">
       <c r="A17" s="44" t="inlineStr">
         <is>
-          <t>英語甲</t>
+          <t>英語乙</t>
         </is>
       </c>
       <c r="B17" s="52" t="inlineStr">
@@ -5357,7 +6400,7 @@
       </c>
       <c r="C17" s="52" t="inlineStr">
         <is>
-          <t>2年1班</t>
+          <t>1年3班</t>
         </is>
       </c>
       <c r="D17" s="44" t="n">
@@ -5378,7 +6421,7 @@
     <row r="18" ht="15" customHeight="1" s="36">
       <c r="A18" s="44" t="inlineStr">
         <is>
-          <t>英語甲</t>
+          <t>英語乙</t>
         </is>
       </c>
       <c r="B18" s="52" t="inlineStr">
@@ -5388,7 +6431,7 @@
       </c>
       <c r="C18" s="52" t="inlineStr">
         <is>
-          <t>2年2班</t>
+          <t>2年3班</t>
         </is>
       </c>
       <c r="D18" s="44" t="n">
@@ -5409,7 +6452,7 @@
     <row r="19" ht="15" customHeight="1" s="36">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>英語甲</t>
+          <t>英語乙</t>
         </is>
       </c>
       <c r="B19" s="52" t="inlineStr">
@@ -5419,11 +6462,11 @@
       </c>
       <c r="C19" s="52" t="inlineStr">
         <is>
-          <t>2年3班</t>
+          <t>3年3班</t>
         </is>
       </c>
       <c r="D19" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="52" t="inlineStr">
         <is>
@@ -5440,7 +6483,7 @@
     <row r="20" ht="15" customHeight="1" s="36">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>英語甲</t>
+          <t>英語乙</t>
         </is>
       </c>
       <c r="B20" s="52" t="inlineStr">
@@ -5450,11 +6493,11 @@
       </c>
       <c r="C20" s="52" t="inlineStr">
         <is>
-          <t>2年4班</t>
+          <t>4年3班</t>
         </is>
       </c>
       <c r="D20" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="52" t="inlineStr">
         <is>
@@ -5471,7 +6514,7 @@
     <row r="21" ht="15" customHeight="1" s="36">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>英語甲</t>
+          <t>英語乙</t>
         </is>
       </c>
       <c r="B21" s="52" t="inlineStr">
@@ -5481,11 +6524,11 @@
       </c>
       <c r="C21" s="52" t="inlineStr">
         <is>
-          <t>2年5班</t>
+          <t>5年3班</t>
         </is>
       </c>
       <c r="D21" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="52" t="inlineStr">
         <is>
@@ -5502,7 +6545,7 @@
     <row r="22" ht="15" customHeight="1" s="36">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>英語甲</t>
+          <t>英語乙</t>
         </is>
       </c>
       <c r="B22" s="52" t="inlineStr">
@@ -5512,11 +6555,11 @@
       </c>
       <c r="C22" s="52" t="inlineStr">
         <is>
-          <t>2年6班</t>
+          <t>6年3班</t>
         </is>
       </c>
       <c r="D22" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="52" t="inlineStr">
         <is>
@@ -5533,7 +6576,7 @@
     <row r="23" ht="15" customHeight="1" s="36">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>英語甲</t>
+          <t>英語乙</t>
         </is>
       </c>
       <c r="B23" s="52" t="inlineStr">
@@ -5543,7 +6586,7 @@
       </c>
       <c r="C23" s="52" t="inlineStr">
         <is>
-          <t>2年7班</t>
+          <t>1年4班</t>
         </is>
       </c>
       <c r="D23" s="44" t="n">
@@ -5564,7 +6607,7 @@
     <row r="24" ht="15" customHeight="1" s="36">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>英語甲</t>
+          <t>英語乙</t>
         </is>
       </c>
       <c r="B24" s="52" t="inlineStr">
@@ -5574,7 +6617,7 @@
       </c>
       <c r="C24" s="52" t="inlineStr">
         <is>
-          <t>2年8班</t>
+          <t>2年4班</t>
         </is>
       </c>
       <c r="D24" s="44" t="n">
@@ -5605,11 +6648,11 @@
       </c>
       <c r="C25" s="52" t="inlineStr">
         <is>
-          <t>2年9班</t>
+          <t>3年4班</t>
         </is>
       </c>
       <c r="D25" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="52" t="inlineStr">
         <is>
@@ -5636,11 +6679,11 @@
       </c>
       <c r="C26" s="52" t="inlineStr">
         <is>
-          <t>2年10班</t>
+          <t>4年4班</t>
         </is>
       </c>
       <c r="D26" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="52" t="inlineStr">
         <is>
@@ -5667,11 +6710,11 @@
       </c>
       <c r="C27" s="52" t="inlineStr">
         <is>
-          <t>2年11班</t>
+          <t>5年4班</t>
         </is>
       </c>
       <c r="D27" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="52" t="inlineStr">
         <is>
@@ -5698,7 +6741,7 @@
       </c>
       <c r="C28" s="52" t="inlineStr">
         <is>
-          <t>3年1班</t>
+          <t>6年4班</t>
         </is>
       </c>
       <c r="D28" s="44" t="n">
@@ -5719,7 +6762,7 @@
     <row r="29" ht="15" customHeight="1" s="36">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>英語乙</t>
+          <t>英語丙</t>
         </is>
       </c>
       <c r="B29" s="52" t="inlineStr">
@@ -5729,11 +6772,11 @@
       </c>
       <c r="C29" s="52" t="inlineStr">
         <is>
-          <t>3年2班</t>
+          <t>1年5班</t>
         </is>
       </c>
       <c r="D29" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="52" t="inlineStr">
         <is>
@@ -5750,7 +6793,7 @@
     <row r="30" ht="15" customHeight="1" s="36">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>英語乙</t>
+          <t>英語丙</t>
         </is>
       </c>
       <c r="B30" s="52" t="inlineStr">
@@ -5760,11 +6803,11 @@
       </c>
       <c r="C30" s="52" t="inlineStr">
         <is>
-          <t>3年3班</t>
+          <t>2年5班</t>
         </is>
       </c>
       <c r="D30" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="52" t="inlineStr">
         <is>
@@ -5781,7 +6824,7 @@
     <row r="31" ht="15" customHeight="1" s="36">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>英語乙</t>
+          <t>英語丙</t>
         </is>
       </c>
       <c r="B31" s="52" t="inlineStr">
@@ -5791,7 +6834,7 @@
       </c>
       <c r="C31" s="52" t="inlineStr">
         <is>
-          <t>3年4班</t>
+          <t>3年5班</t>
         </is>
       </c>
       <c r="D31" s="44" t="n">
@@ -5812,7 +6855,7 @@
     <row r="32" ht="15" customHeight="1" s="36">
       <c r="A32" s="44" t="inlineStr">
         <is>
-          <t>英語乙</t>
+          <t>英語丙</t>
         </is>
       </c>
       <c r="B32" s="52" t="inlineStr">
@@ -5822,7 +6865,7 @@
       </c>
       <c r="C32" s="52" t="inlineStr">
         <is>
-          <t>3年5班</t>
+          <t>4年5班</t>
         </is>
       </c>
       <c r="D32" s="44" t="n">
@@ -5843,7 +6886,7 @@
     <row r="33" ht="15" customHeight="1" s="36">
       <c r="A33" s="44" t="inlineStr">
         <is>
-          <t>英語乙</t>
+          <t>英語丙</t>
         </is>
       </c>
       <c r="B33" s="52" t="inlineStr">
@@ -5853,7 +6896,7 @@
       </c>
       <c r="C33" s="52" t="inlineStr">
         <is>
-          <t>3年6班</t>
+          <t>5年5班</t>
         </is>
       </c>
       <c r="D33" s="44" t="n">
@@ -5874,7 +6917,7 @@
     <row r="34" ht="15" customHeight="1" s="36">
       <c r="A34" s="44" t="inlineStr">
         <is>
-          <t>英語乙</t>
+          <t>英語丙</t>
         </is>
       </c>
       <c r="B34" s="52" t="inlineStr">
@@ -5884,7 +6927,7 @@
       </c>
       <c r="C34" s="52" t="inlineStr">
         <is>
-          <t>3年7班</t>
+          <t>6年5班</t>
         </is>
       </c>
       <c r="D34" s="44" t="n">
@@ -5905,7 +6948,7 @@
     <row r="35" ht="15" customHeight="1" s="36">
       <c r="A35" s="44" t="inlineStr">
         <is>
-          <t>英語乙</t>
+          <t>英語丙</t>
         </is>
       </c>
       <c r="B35" s="52" t="inlineStr">
@@ -5915,11 +6958,11 @@
       </c>
       <c r="C35" s="52" t="inlineStr">
         <is>
-          <t>3年8班</t>
+          <t>1年6班</t>
         </is>
       </c>
       <c r="D35" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" s="52" t="inlineStr">
         <is>
@@ -5946,11 +6989,11 @@
       </c>
       <c r="C36" s="52" t="inlineStr">
         <is>
-          <t>3年9班</t>
+          <t>2年6班</t>
         </is>
       </c>
       <c r="D36" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" s="52" t="inlineStr">
         <is>
@@ -5977,7 +7020,7 @@
       </c>
       <c r="C37" s="52" t="inlineStr">
         <is>
-          <t>3年10班</t>
+          <t>3年6班</t>
         </is>
       </c>
       <c r="D37" s="44" t="n">
@@ -6008,7 +7051,7 @@
       </c>
       <c r="C38" s="52" t="inlineStr">
         <is>
-          <t>3年11班</t>
+          <t>4年6班</t>
         </is>
       </c>
       <c r="D38" s="44" t="n">
@@ -6039,7 +7082,7 @@
       </c>
       <c r="C39" s="52" t="inlineStr">
         <is>
-          <t>3年12班</t>
+          <t>5年6班</t>
         </is>
       </c>
       <c r="D39" s="44" t="n">
@@ -6070,7 +7113,7 @@
       </c>
       <c r="C40" s="52" t="inlineStr">
         <is>
-          <t>4年1班</t>
+          <t>6年6班</t>
         </is>
       </c>
       <c r="D40" s="44" t="n">
@@ -6091,7 +7134,7 @@
     <row r="41" ht="15" customHeight="1" s="36">
       <c r="A41" s="44" t="inlineStr">
         <is>
-          <t>英語丙</t>
+          <t>英語丁</t>
         </is>
       </c>
       <c r="B41" s="52" t="inlineStr">
@@ -6101,11 +7144,11 @@
       </c>
       <c r="C41" s="52" t="inlineStr">
         <is>
-          <t>4年2班</t>
+          <t>1年7班</t>
         </is>
       </c>
       <c r="D41" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" s="52" t="inlineStr">
         <is>
@@ -6122,7 +7165,7 @@
     <row r="42" ht="15" customHeight="1" s="36">
       <c r="A42" s="44" t="inlineStr">
         <is>
-          <t>英語丙</t>
+          <t>英語丁</t>
         </is>
       </c>
       <c r="B42" s="52" t="inlineStr">
@@ -6132,11 +7175,11 @@
       </c>
       <c r="C42" s="52" t="inlineStr">
         <is>
-          <t>4年3班</t>
+          <t>2年7班</t>
         </is>
       </c>
       <c r="D42" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" s="52" t="inlineStr">
         <is>
@@ -6153,7 +7196,7 @@
     <row r="43" ht="15" customHeight="1" s="36">
       <c r="A43" s="44" t="inlineStr">
         <is>
-          <t>英語丙</t>
+          <t>英語丁</t>
         </is>
       </c>
       <c r="B43" s="52" t="inlineStr">
@@ -6163,7 +7206,7 @@
       </c>
       <c r="C43" s="52" t="inlineStr">
         <is>
-          <t>4年4班</t>
+          <t>3年7班</t>
         </is>
       </c>
       <c r="D43" s="44" t="n">
@@ -6184,7 +7227,7 @@
     <row r="44" ht="15" customHeight="1" s="36">
       <c r="A44" s="44" t="inlineStr">
         <is>
-          <t>英語丙</t>
+          <t>英語丁</t>
         </is>
       </c>
       <c r="B44" s="52" t="inlineStr">
@@ -6194,7 +7237,7 @@
       </c>
       <c r="C44" s="52" t="inlineStr">
         <is>
-          <t>4年5班</t>
+          <t>4年7班</t>
         </is>
       </c>
       <c r="D44" s="44" t="n">
@@ -6215,7 +7258,7 @@
     <row r="45" ht="15" customHeight="1" s="36">
       <c r="A45" s="44" t="inlineStr">
         <is>
-          <t>英語丙</t>
+          <t>英語丁</t>
         </is>
       </c>
       <c r="B45" s="52" t="inlineStr">
@@ -6225,7 +7268,7 @@
       </c>
       <c r="C45" s="52" t="inlineStr">
         <is>
-          <t>4年6班</t>
+          <t>5年7班</t>
         </is>
       </c>
       <c r="D45" s="44" t="n">
@@ -6256,7 +7299,7 @@
       </c>
       <c r="C46" s="52" t="inlineStr">
         <is>
-          <t>4年7班</t>
+          <t>6年7班</t>
         </is>
       </c>
       <c r="D46" s="44" t="n">
@@ -6287,11 +7330,11 @@
       </c>
       <c r="C47" s="52" t="inlineStr">
         <is>
-          <t>4年8班</t>
+          <t>1年8班</t>
         </is>
       </c>
       <c r="D47" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" s="52" t="inlineStr">
         <is>
@@ -6318,11 +7361,11 @@
       </c>
       <c r="C48" s="52" t="inlineStr">
         <is>
-          <t>4年9班</t>
+          <t>2年8班</t>
         </is>
       </c>
       <c r="D48" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" s="52" t="inlineStr">
         <is>
@@ -6349,7 +7392,7 @@
       </c>
       <c r="C49" s="52" t="inlineStr">
         <is>
-          <t>4年10班</t>
+          <t>3年8班</t>
         </is>
       </c>
       <c r="D49" s="44" t="n">
@@ -6380,7 +7423,7 @@
       </c>
       <c r="C50" s="52" t="inlineStr">
         <is>
-          <t>4年11班</t>
+          <t>4年8班</t>
         </is>
       </c>
       <c r="D50" s="44" t="n">
@@ -6411,7 +7454,7 @@
       </c>
       <c r="C51" s="52" t="inlineStr">
         <is>
-          <t>4年12班</t>
+          <t>5年8班</t>
         </is>
       </c>
       <c r="D51" s="44" t="n">
@@ -6442,7 +7485,7 @@
       </c>
       <c r="C52" s="52" t="inlineStr">
         <is>
-          <t>5年1班</t>
+          <t>6年8班</t>
         </is>
       </c>
       <c r="D52" s="44" t="n">
@@ -6463,7 +7506,7 @@
     <row r="53" ht="15" customHeight="1" s="36">
       <c r="A53" s="44" t="inlineStr">
         <is>
-          <t>英語丁</t>
+          <t>英語戊</t>
         </is>
       </c>
       <c r="B53" s="52" t="inlineStr">
@@ -6473,11 +7516,11 @@
       </c>
       <c r="C53" s="52" t="inlineStr">
         <is>
-          <t>5年2班</t>
+          <t>1年9班</t>
         </is>
       </c>
       <c r="D53" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" s="52" t="inlineStr">
         <is>
@@ -6494,7 +7537,7 @@
     <row r="54" ht="15" customHeight="1" s="36">
       <c r="A54" s="44" t="inlineStr">
         <is>
-          <t>英語丁</t>
+          <t>英語戊</t>
         </is>
       </c>
       <c r="B54" s="52" t="inlineStr">
@@ -6504,11 +7547,11 @@
       </c>
       <c r="C54" s="52" t="inlineStr">
         <is>
-          <t>5年3班</t>
+          <t>2年9班</t>
         </is>
       </c>
       <c r="D54" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" s="52" t="inlineStr">
         <is>
@@ -6525,7 +7568,7 @@
     <row r="55" ht="15" customHeight="1" s="36">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>英語丁</t>
+          <t>英語戊</t>
         </is>
       </c>
       <c r="B55" s="52" t="inlineStr">
@@ -6535,7 +7578,7 @@
       </c>
       <c r="C55" s="52" t="inlineStr">
         <is>
-          <t>5年4班</t>
+          <t>3年9班</t>
         </is>
       </c>
       <c r="D55" s="44" t="n">
@@ -6566,7 +7609,7 @@
       </c>
       <c r="C56" s="52" t="inlineStr">
         <is>
-          <t>5年5班</t>
+          <t>4年9班</t>
         </is>
       </c>
       <c r="D56" s="44" t="n">
@@ -6597,7 +7640,7 @@
       </c>
       <c r="C57" s="52" t="inlineStr">
         <is>
-          <t>5年6班</t>
+          <t>5年9班</t>
         </is>
       </c>
       <c r="D57" s="44" t="n">
@@ -6628,7 +7671,7 @@
       </c>
       <c r="C58" s="52" t="inlineStr">
         <is>
-          <t>5年7班</t>
+          <t>6年9班</t>
         </is>
       </c>
       <c r="D58" s="44" t="n">
@@ -6659,11 +7702,11 @@
       </c>
       <c r="C59" s="52" t="inlineStr">
         <is>
-          <t>5年8班</t>
+          <t>1年10班</t>
         </is>
       </c>
       <c r="D59" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" s="52" t="inlineStr">
         <is>
@@ -6690,11 +7733,11 @@
       </c>
       <c r="C60" s="52" t="inlineStr">
         <is>
-          <t>5年9班</t>
+          <t>2年10班</t>
         </is>
       </c>
       <c r="D60" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" s="52" t="inlineStr">
         <is>
@@ -6721,7 +7764,7 @@
       </c>
       <c r="C61" s="52" t="inlineStr">
         <is>
-          <t>5年10班</t>
+          <t>3年10班</t>
         </is>
       </c>
       <c r="D61" s="44" t="n">
@@ -6752,7 +7795,7 @@
       </c>
       <c r="C62" s="52" t="inlineStr">
         <is>
-          <t>5年11班</t>
+          <t>4年10班</t>
         </is>
       </c>
       <c r="D62" s="44" t="n">
@@ -6783,7 +7826,7 @@
       </c>
       <c r="C63" s="52" t="inlineStr">
         <is>
-          <t>5年12班</t>
+          <t>5年10班</t>
         </is>
       </c>
       <c r="D63" s="44" t="n">
@@ -6814,7 +7857,7 @@
       </c>
       <c r="C64" s="52" t="inlineStr">
         <is>
-          <t>6年1班</t>
+          <t>6年10班</t>
         </is>
       </c>
       <c r="D64" s="44" t="n">
@@ -6835,7 +7878,7 @@
     <row r="65" ht="15" customHeight="1" s="36">
       <c r="A65" s="44" t="inlineStr">
         <is>
-          <t>英語戊</t>
+          <t>英語己</t>
         </is>
       </c>
       <c r="B65" s="52" t="inlineStr">
@@ -6845,11 +7888,11 @@
       </c>
       <c r="C65" s="52" t="inlineStr">
         <is>
-          <t>6年2班</t>
+          <t>1年11班</t>
         </is>
       </c>
       <c r="D65" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" s="52" t="inlineStr">
         <is>
@@ -6876,11 +7919,11 @@
       </c>
       <c r="C66" s="52" t="inlineStr">
         <is>
-          <t>6年3班</t>
+          <t>2年11班</t>
         </is>
       </c>
       <c r="D66" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" s="52" t="inlineStr">
         <is>
@@ -6907,7 +7950,7 @@
       </c>
       <c r="C67" s="52" t="inlineStr">
         <is>
-          <t>6年4班</t>
+          <t>3年11班</t>
         </is>
       </c>
       <c r="D67" s="44" t="n">
@@ -6938,7 +7981,7 @@
       </c>
       <c r="C68" s="52" t="inlineStr">
         <is>
-          <t>6年5班</t>
+          <t>4年11班</t>
         </is>
       </c>
       <c r="D68" s="44" t="n">
@@ -6969,7 +8012,7 @@
       </c>
       <c r="C69" s="52" t="inlineStr">
         <is>
-          <t>6年6班</t>
+          <t>5年11班</t>
         </is>
       </c>
       <c r="D69" s="44" t="n">
@@ -7000,7 +8043,7 @@
       </c>
       <c r="C70" s="52" t="inlineStr">
         <is>
-          <t>6年7班</t>
+          <t>6年11班</t>
         </is>
       </c>
       <c r="D70" s="44" t="n">
@@ -7031,11 +8074,11 @@
       </c>
       <c r="C71" s="52" t="inlineStr">
         <is>
-          <t>6年8班</t>
+          <t>1年12班</t>
         </is>
       </c>
       <c r="D71" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71" s="52" t="inlineStr">
         <is>
@@ -7062,7 +8105,7 @@
       </c>
       <c r="C72" s="52" t="inlineStr">
         <is>
-          <t>6年9班</t>
+          <t>3年12班</t>
         </is>
       </c>
       <c r="D72" s="44" t="n">
@@ -7093,7 +8136,7 @@
       </c>
       <c r="C73" s="52" t="inlineStr">
         <is>
-          <t>6年10班</t>
+          <t>4年12班</t>
         </is>
       </c>
       <c r="D73" s="44" t="n">
@@ -7124,7 +8167,7 @@
       </c>
       <c r="C74" s="52" t="inlineStr">
         <is>
-          <t>6年11班</t>
+          <t>5年12班</t>
         </is>
       </c>
       <c r="D74" s="44" t="n">
@@ -7217,7 +8260,7 @@
       </c>
       <c r="C77" s="52" t="inlineStr">
         <is>
-          <t>1年2班</t>
+          <t>2年1班</t>
         </is>
       </c>
       <c r="D77" s="44" t="n">
@@ -7248,11 +8291,11 @@
       </c>
       <c r="C78" s="52" t="inlineStr">
         <is>
-          <t>1年3班</t>
+          <t>3年1班</t>
         </is>
       </c>
       <c r="D78" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78" s="52" t="inlineStr">
         <is>
@@ -7279,11 +8322,11 @@
       </c>
       <c r="C79" s="52" t="inlineStr">
         <is>
-          <t>1年4班</t>
+          <t>4年1班</t>
         </is>
       </c>
       <c r="D79" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79" s="52" t="inlineStr">
         <is>
@@ -7310,11 +8353,11 @@
       </c>
       <c r="C80" s="52" t="inlineStr">
         <is>
-          <t>1年5班</t>
+          <t>5年1班</t>
         </is>
       </c>
       <c r="D80" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" s="52" t="inlineStr">
         <is>
@@ -7341,11 +8384,11 @@
       </c>
       <c r="C81" s="52" t="inlineStr">
         <is>
-          <t>1年6班</t>
+          <t>6年1班</t>
         </is>
       </c>
       <c r="D81" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81" s="52" t="inlineStr">
         <is>
@@ -7372,7 +8415,7 @@
       </c>
       <c r="C82" s="52" t="inlineStr">
         <is>
-          <t>1年7班</t>
+          <t>1年2班</t>
         </is>
       </c>
       <c r="D82" s="44" t="n">
@@ -7403,7 +8446,7 @@
       </c>
       <c r="C83" s="52" t="inlineStr">
         <is>
-          <t>1年8班</t>
+          <t>2年2班</t>
         </is>
       </c>
       <c r="D83" s="44" t="n">
@@ -7434,11 +8477,11 @@
       </c>
       <c r="C84" s="52" t="inlineStr">
         <is>
-          <t>1年9班</t>
+          <t>3年2班</t>
         </is>
       </c>
       <c r="D84" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" s="52" t="inlineStr">
         <is>
@@ -7465,11 +8508,11 @@
       </c>
       <c r="C85" s="52" t="inlineStr">
         <is>
-          <t>1年10班</t>
+          <t>4年2班</t>
         </is>
       </c>
       <c r="D85" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" s="52" t="inlineStr">
         <is>
@@ -7496,11 +8539,11 @@
       </c>
       <c r="C86" s="52" t="inlineStr">
         <is>
-          <t>1年11班</t>
+          <t>5年2班</t>
         </is>
       </c>
       <c r="D86" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" s="52" t="inlineStr">
         <is>
@@ -7527,11 +8570,11 @@
       </c>
       <c r="C87" s="52" t="inlineStr">
         <is>
-          <t>1年12班</t>
+          <t>6年2班</t>
         </is>
       </c>
       <c r="D87" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" s="52" t="inlineStr">
         <is>
@@ -7548,7 +8591,7 @@
     <row r="88" ht="15" customHeight="1" s="36">
       <c r="A88" s="44" t="inlineStr">
         <is>
-          <t>體育甲</t>
+          <t>體育乙</t>
         </is>
       </c>
       <c r="B88" s="52" t="inlineStr">
@@ -7558,7 +8601,7 @@
       </c>
       <c r="C88" s="52" t="inlineStr">
         <is>
-          <t>2年1班</t>
+          <t>1年3班</t>
         </is>
       </c>
       <c r="D88" s="44" t="n">
@@ -7579,7 +8622,7 @@
     <row r="89" ht="15" customHeight="1" s="36">
       <c r="A89" s="44" t="inlineStr">
         <is>
-          <t>體育甲</t>
+          <t>體育乙</t>
         </is>
       </c>
       <c r="B89" s="52" t="inlineStr">
@@ -7589,7 +8632,7 @@
       </c>
       <c r="C89" s="52" t="inlineStr">
         <is>
-          <t>2年2班</t>
+          <t>2年3班</t>
         </is>
       </c>
       <c r="D89" s="44" t="n">
@@ -7610,7 +8653,7 @@
     <row r="90" ht="15" customHeight="1" s="36">
       <c r="A90" s="44" t="inlineStr">
         <is>
-          <t>體育甲</t>
+          <t>體育乙</t>
         </is>
       </c>
       <c r="B90" s="52" t="inlineStr">
@@ -7620,11 +8663,11 @@
       </c>
       <c r="C90" s="52" t="inlineStr">
         <is>
-          <t>2年3班</t>
+          <t>3年3班</t>
         </is>
       </c>
       <c r="D90" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" s="52" t="inlineStr">
         <is>
@@ -7641,7 +8684,7 @@
     <row r="91" ht="15" customHeight="1" s="36">
       <c r="A91" s="44" t="inlineStr">
         <is>
-          <t>體育甲</t>
+          <t>體育乙</t>
         </is>
       </c>
       <c r="B91" s="52" t="inlineStr">
@@ -7651,11 +8694,11 @@
       </c>
       <c r="C91" s="52" t="inlineStr">
         <is>
-          <t>2年4班</t>
+          <t>4年3班</t>
         </is>
       </c>
       <c r="D91" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" s="52" t="inlineStr">
         <is>
@@ -7672,7 +8715,7 @@
     <row r="92" ht="15" customHeight="1" s="36">
       <c r="A92" s="44" t="inlineStr">
         <is>
-          <t>體育甲</t>
+          <t>體育乙</t>
         </is>
       </c>
       <c r="B92" s="52" t="inlineStr">
@@ -7682,11 +8725,11 @@
       </c>
       <c r="C92" s="52" t="inlineStr">
         <is>
-          <t>2年5班</t>
+          <t>5年3班</t>
         </is>
       </c>
       <c r="D92" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" s="52" t="inlineStr">
         <is>
@@ -7703,7 +8746,7 @@
     <row r="93" ht="15" customHeight="1" s="36">
       <c r="A93" s="44" t="inlineStr">
         <is>
-          <t>體育甲</t>
+          <t>體育乙</t>
         </is>
       </c>
       <c r="B93" s="52" t="inlineStr">
@@ -7713,11 +8756,11 @@
       </c>
       <c r="C93" s="52" t="inlineStr">
         <is>
-          <t>2年6班</t>
+          <t>6年3班</t>
         </is>
       </c>
       <c r="D93" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93" s="52" t="inlineStr">
         <is>
@@ -7734,7 +8777,7 @@
     <row r="94" ht="15" customHeight="1" s="36">
       <c r="A94" s="44" t="inlineStr">
         <is>
-          <t>體育甲</t>
+          <t>體育乙</t>
         </is>
       </c>
       <c r="B94" s="52" t="inlineStr">
@@ -7744,7 +8787,7 @@
       </c>
       <c r="C94" s="52" t="inlineStr">
         <is>
-          <t>2年7班</t>
+          <t>1年4班</t>
         </is>
       </c>
       <c r="D94" s="44" t="n">
@@ -7765,7 +8808,7 @@
     <row r="95" ht="15" customHeight="1" s="36">
       <c r="A95" s="44" t="inlineStr">
         <is>
-          <t>體育甲</t>
+          <t>體育乙</t>
         </is>
       </c>
       <c r="B95" s="52" t="inlineStr">
@@ -7775,7 +8818,7 @@
       </c>
       <c r="C95" s="52" t="inlineStr">
         <is>
-          <t>2年8班</t>
+          <t>2年4班</t>
         </is>
       </c>
       <c r="D95" s="44" t="n">
@@ -7806,11 +8849,11 @@
       </c>
       <c r="C96" s="52" t="inlineStr">
         <is>
-          <t>2年9班</t>
+          <t>3年4班</t>
         </is>
       </c>
       <c r="D96" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" s="52" t="inlineStr">
         <is>
@@ -7837,11 +8880,11 @@
       </c>
       <c r="C97" s="52" t="inlineStr">
         <is>
-          <t>2年10班</t>
+          <t>4年4班</t>
         </is>
       </c>
       <c r="D97" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" s="52" t="inlineStr">
         <is>
@@ -7868,11 +8911,11 @@
       </c>
       <c r="C98" s="52" t="inlineStr">
         <is>
-          <t>2年11班</t>
+          <t>5年4班</t>
         </is>
       </c>
       <c r="D98" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" s="52" t="inlineStr">
         <is>
@@ -7899,7 +8942,7 @@
       </c>
       <c r="C99" s="52" t="inlineStr">
         <is>
-          <t>3年1班</t>
+          <t>6年4班</t>
         </is>
       </c>
       <c r="D99" s="44" t="n">
@@ -7920,7 +8963,7 @@
     <row r="100" ht="15" customHeight="1" s="36">
       <c r="A100" s="44" t="inlineStr">
         <is>
-          <t>體育乙</t>
+          <t>體育丙</t>
         </is>
       </c>
       <c r="B100" s="52" t="inlineStr">
@@ -7930,11 +8973,11 @@
       </c>
       <c r="C100" s="52" t="inlineStr">
         <is>
-          <t>3年2班</t>
+          <t>1年5班</t>
         </is>
       </c>
       <c r="D100" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" s="52" t="inlineStr">
         <is>
@@ -7951,7 +8994,7 @@
     <row r="101" ht="15" customHeight="1" s="36">
       <c r="A101" s="44" t="inlineStr">
         <is>
-          <t>體育乙</t>
+          <t>體育丙</t>
         </is>
       </c>
       <c r="B101" s="52" t="inlineStr">
@@ -7961,11 +9004,11 @@
       </c>
       <c r="C101" s="52" t="inlineStr">
         <is>
-          <t>3年3班</t>
+          <t>2年5班</t>
         </is>
       </c>
       <c r="D101" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" s="52" t="inlineStr">
         <is>
@@ -7982,7 +9025,7 @@
     <row r="102" ht="15" customHeight="1" s="36">
       <c r="A102" s="44" t="inlineStr">
         <is>
-          <t>體育乙</t>
+          <t>體育丙</t>
         </is>
       </c>
       <c r="B102" s="52" t="inlineStr">
@@ -7992,7 +9035,7 @@
       </c>
       <c r="C102" s="52" t="inlineStr">
         <is>
-          <t>3年4班</t>
+          <t>3年5班</t>
         </is>
       </c>
       <c r="D102" s="44" t="n">
@@ -8013,7 +9056,7 @@
     <row r="103" ht="15" customHeight="1" s="36">
       <c r="A103" s="44" t="inlineStr">
         <is>
-          <t>體育乙</t>
+          <t>體育丙</t>
         </is>
       </c>
       <c r="B103" s="52" t="inlineStr">
@@ -8023,7 +9066,7 @@
       </c>
       <c r="C103" s="52" t="inlineStr">
         <is>
-          <t>3年5班</t>
+          <t>4年5班</t>
         </is>
       </c>
       <c r="D103" s="44" t="n">
@@ -8044,7 +9087,7 @@
     <row r="104" ht="15" customHeight="1" s="36">
       <c r="A104" s="44" t="inlineStr">
         <is>
-          <t>體育乙</t>
+          <t>體育丙</t>
         </is>
       </c>
       <c r="B104" s="52" t="inlineStr">
@@ -8054,7 +9097,7 @@
       </c>
       <c r="C104" s="52" t="inlineStr">
         <is>
-          <t>3年6班</t>
+          <t>5年5班</t>
         </is>
       </c>
       <c r="D104" s="44" t="n">
@@ -8075,7 +9118,7 @@
     <row r="105" ht="15" customHeight="1" s="36">
       <c r="A105" s="44" t="inlineStr">
         <is>
-          <t>體育乙</t>
+          <t>體育丙</t>
         </is>
       </c>
       <c r="B105" s="52" t="inlineStr">
@@ -8085,7 +9128,7 @@
       </c>
       <c r="C105" s="52" t="inlineStr">
         <is>
-          <t>3年7班</t>
+          <t>6年5班</t>
         </is>
       </c>
       <c r="D105" s="44" t="n">
@@ -8106,7 +9149,7 @@
     <row r="106" ht="15" customHeight="1" s="36">
       <c r="A106" s="44" t="inlineStr">
         <is>
-          <t>體育乙</t>
+          <t>體育丙</t>
         </is>
       </c>
       <c r="B106" s="52" t="inlineStr">
@@ -8116,11 +9159,11 @@
       </c>
       <c r="C106" s="52" t="inlineStr">
         <is>
-          <t>3年8班</t>
+          <t>1年6班</t>
         </is>
       </c>
       <c r="D106" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E106" s="52" t="inlineStr">
         <is>
@@ -8147,11 +9190,11 @@
       </c>
       <c r="C107" s="52" t="inlineStr">
         <is>
-          <t>3年9班</t>
+          <t>2年6班</t>
         </is>
       </c>
       <c r="D107" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107" s="52" t="inlineStr">
         <is>
@@ -8178,7 +9221,7 @@
       </c>
       <c r="C108" s="52" t="inlineStr">
         <is>
-          <t>3年10班</t>
+          <t>3年6班</t>
         </is>
       </c>
       <c r="D108" s="44" t="n">
@@ -8209,7 +9252,7 @@
       </c>
       <c r="C109" s="52" t="inlineStr">
         <is>
-          <t>3年11班</t>
+          <t>4年6班</t>
         </is>
       </c>
       <c r="D109" s="44" t="n">
@@ -8240,7 +9283,7 @@
       </c>
       <c r="C110" s="52" t="inlineStr">
         <is>
-          <t>3年12班</t>
+          <t>5年6班</t>
         </is>
       </c>
       <c r="D110" s="44" t="n">
@@ -8271,7 +9314,7 @@
       </c>
       <c r="C111" s="52" t="inlineStr">
         <is>
-          <t>4年1班</t>
+          <t>6年6班</t>
         </is>
       </c>
       <c r="D111" s="44" t="n">
@@ -8292,7 +9335,7 @@
     <row r="112" ht="15" customHeight="1" s="36">
       <c r="A112" s="44" t="inlineStr">
         <is>
-          <t>體育丙</t>
+          <t>體育丁</t>
         </is>
       </c>
       <c r="B112" s="52" t="inlineStr">
@@ -8302,11 +9345,11 @@
       </c>
       <c r="C112" s="52" t="inlineStr">
         <is>
-          <t>4年2班</t>
+          <t>1年7班</t>
         </is>
       </c>
       <c r="D112" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E112" s="52" t="inlineStr">
         <is>
@@ -8323,7 +9366,7 @@
     <row r="113" ht="15" customHeight="1" s="36">
       <c r="A113" s="44" t="inlineStr">
         <is>
-          <t>體育丙</t>
+          <t>體育丁</t>
         </is>
       </c>
       <c r="B113" s="52" t="inlineStr">
@@ -8333,11 +9376,11 @@
       </c>
       <c r="C113" s="52" t="inlineStr">
         <is>
-          <t>4年3班</t>
+          <t>2年7班</t>
         </is>
       </c>
       <c r="D113" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E113" s="52" t="inlineStr">
         <is>
@@ -8354,7 +9397,7 @@
     <row r="114" ht="15" customHeight="1" s="36">
       <c r="A114" s="44" t="inlineStr">
         <is>
-          <t>體育丙</t>
+          <t>體育丁</t>
         </is>
       </c>
       <c r="B114" s="52" t="inlineStr">
@@ -8364,7 +9407,7 @@
       </c>
       <c r="C114" s="52" t="inlineStr">
         <is>
-          <t>4年4班</t>
+          <t>3年7班</t>
         </is>
       </c>
       <c r="D114" s="44" t="n">
@@ -8385,7 +9428,7 @@
     <row r="115" ht="15" customHeight="1" s="36">
       <c r="A115" s="44" t="inlineStr">
         <is>
-          <t>體育丙</t>
+          <t>體育丁</t>
         </is>
       </c>
       <c r="B115" s="52" t="inlineStr">
@@ -8395,7 +9438,7 @@
       </c>
       <c r="C115" s="52" t="inlineStr">
         <is>
-          <t>4年5班</t>
+          <t>4年7班</t>
         </is>
       </c>
       <c r="D115" s="44" t="n">
@@ -8416,7 +9459,7 @@
     <row r="116" ht="15" customHeight="1" s="36">
       <c r="A116" s="44" t="inlineStr">
         <is>
-          <t>體育丙</t>
+          <t>體育丁</t>
         </is>
       </c>
       <c r="B116" s="52" t="inlineStr">
@@ -8426,7 +9469,7 @@
       </c>
       <c r="C116" s="52" t="inlineStr">
         <is>
-          <t>4年6班</t>
+          <t>5年7班</t>
         </is>
       </c>
       <c r="D116" s="44" t="n">
@@ -8457,7 +9500,7 @@
       </c>
       <c r="C117" s="52" t="inlineStr">
         <is>
-          <t>4年7班</t>
+          <t>6年7班</t>
         </is>
       </c>
       <c r="D117" s="44" t="n">
@@ -8488,11 +9531,11 @@
       </c>
       <c r="C118" s="52" t="inlineStr">
         <is>
-          <t>4年8班</t>
+          <t>1年8班</t>
         </is>
       </c>
       <c r="D118" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118" s="52" t="inlineStr">
         <is>
@@ -8519,11 +9562,11 @@
       </c>
       <c r="C119" s="52" t="inlineStr">
         <is>
-          <t>4年9班</t>
+          <t>2年8班</t>
         </is>
       </c>
       <c r="D119" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E119" s="52" t="inlineStr">
         <is>
@@ -8550,7 +9593,7 @@
       </c>
       <c r="C120" s="52" t="inlineStr">
         <is>
-          <t>4年10班</t>
+          <t>3年8班</t>
         </is>
       </c>
       <c r="D120" s="44" t="n">
@@ -8581,7 +9624,7 @@
       </c>
       <c r="C121" s="52" t="inlineStr">
         <is>
-          <t>4年11班</t>
+          <t>4年8班</t>
         </is>
       </c>
       <c r="D121" s="44" t="n">
@@ -8612,7 +9655,7 @@
       </c>
       <c r="C122" s="52" t="inlineStr">
         <is>
-          <t>4年12班</t>
+          <t>5年8班</t>
         </is>
       </c>
       <c r="D122" s="44" t="n">
@@ -8643,7 +9686,7 @@
       </c>
       <c r="C123" s="52" t="inlineStr">
         <is>
-          <t>5年1班</t>
+          <t>6年8班</t>
         </is>
       </c>
       <c r="D123" s="44" t="n">
@@ -8664,7 +9707,7 @@
     <row r="124" ht="15" customHeight="1" s="36">
       <c r="A124" s="44" t="inlineStr">
         <is>
-          <t>體育丁</t>
+          <t>體育戊</t>
         </is>
       </c>
       <c r="B124" s="52" t="inlineStr">
@@ -8674,11 +9717,11 @@
       </c>
       <c r="C124" s="52" t="inlineStr">
         <is>
-          <t>5年2班</t>
+          <t>1年9班</t>
         </is>
       </c>
       <c r="D124" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E124" s="52" t="inlineStr">
         <is>
@@ -8695,7 +9738,7 @@
     <row r="125" ht="15" customHeight="1" s="36">
       <c r="A125" s="44" t="inlineStr">
         <is>
-          <t>體育丁</t>
+          <t>體育戊</t>
         </is>
       </c>
       <c r="B125" s="52" t="inlineStr">
@@ -8705,11 +9748,11 @@
       </c>
       <c r="C125" s="52" t="inlineStr">
         <is>
-          <t>5年3班</t>
+          <t>2年9班</t>
         </is>
       </c>
       <c r="D125" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125" s="52" t="inlineStr">
         <is>
@@ -8726,7 +9769,7 @@
     <row r="126" ht="15" customHeight="1" s="36">
       <c r="A126" s="44" t="inlineStr">
         <is>
-          <t>體育丁</t>
+          <t>體育戊</t>
         </is>
       </c>
       <c r="B126" s="52" t="inlineStr">
@@ -8736,7 +9779,7 @@
       </c>
       <c r="C126" s="52" t="inlineStr">
         <is>
-          <t>5年4班</t>
+          <t>3年9班</t>
         </is>
       </c>
       <c r="D126" s="44" t="n">
@@ -8767,7 +9810,7 @@
       </c>
       <c r="C127" s="52" t="inlineStr">
         <is>
-          <t>5年5班</t>
+          <t>4年9班</t>
         </is>
       </c>
       <c r="D127" s="44" t="n">
@@ -8798,7 +9841,7 @@
       </c>
       <c r="C128" s="52" t="inlineStr">
         <is>
-          <t>5年6班</t>
+          <t>5年9班</t>
         </is>
       </c>
       <c r="D128" s="44" t="n">
@@ -8829,7 +9872,7 @@
       </c>
       <c r="C129" s="52" t="inlineStr">
         <is>
-          <t>5年7班</t>
+          <t>6年9班</t>
         </is>
       </c>
       <c r="D129" s="44" t="n">
@@ -8860,11 +9903,11 @@
       </c>
       <c r="C130" s="52" t="inlineStr">
         <is>
-          <t>5年8班</t>
+          <t>1年10班</t>
         </is>
       </c>
       <c r="D130" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E130" s="52" t="inlineStr">
         <is>
@@ -8891,11 +9934,11 @@
       </c>
       <c r="C131" s="52" t="inlineStr">
         <is>
-          <t>5年9班</t>
+          <t>2年10班</t>
         </is>
       </c>
       <c r="D131" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E131" s="52" t="inlineStr">
         <is>
@@ -8922,7 +9965,7 @@
       </c>
       <c r="C132" s="52" t="inlineStr">
         <is>
-          <t>5年10班</t>
+          <t>3年10班</t>
         </is>
       </c>
       <c r="D132" s="44" t="n">
@@ -8953,7 +9996,7 @@
       </c>
       <c r="C133" s="52" t="inlineStr">
         <is>
-          <t>5年11班</t>
+          <t>4年10班</t>
         </is>
       </c>
       <c r="D133" s="44" t="n">
@@ -8984,7 +10027,7 @@
       </c>
       <c r="C134" s="52" t="inlineStr">
         <is>
-          <t>5年12班</t>
+          <t>5年10班</t>
         </is>
       </c>
       <c r="D134" s="44" t="n">
@@ -9015,7 +10058,7 @@
       </c>
       <c r="C135" s="52" t="inlineStr">
         <is>
-          <t>6年1班</t>
+          <t>6年10班</t>
         </is>
       </c>
       <c r="D135" s="44" t="n">
@@ -9036,7 +10079,7 @@
     <row r="136" ht="15" customHeight="1" s="36">
       <c r="A136" s="44" t="inlineStr">
         <is>
-          <t>體育戊</t>
+          <t>體育己</t>
         </is>
       </c>
       <c r="B136" s="52" t="inlineStr">
@@ -9046,11 +10089,11 @@
       </c>
       <c r="C136" s="52" t="inlineStr">
         <is>
-          <t>6年2班</t>
+          <t>1年11班</t>
         </is>
       </c>
       <c r="D136" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E136" s="52" t="inlineStr">
         <is>
@@ -9077,11 +10120,11 @@
       </c>
       <c r="C137" s="52" t="inlineStr">
         <is>
-          <t>6年3班</t>
+          <t>2年11班</t>
         </is>
       </c>
       <c r="D137" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E137" s="52" t="inlineStr">
         <is>
@@ -9108,7 +10151,7 @@
       </c>
       <c r="C138" s="52" t="inlineStr">
         <is>
-          <t>6年4班</t>
+          <t>3年11班</t>
         </is>
       </c>
       <c r="D138" s="44" t="n">
@@ -9139,7 +10182,7 @@
       </c>
       <c r="C139" s="52" t="inlineStr">
         <is>
-          <t>6年5班</t>
+          <t>4年11班</t>
         </is>
       </c>
       <c r="D139" s="44" t="n">
@@ -9170,7 +10213,7 @@
       </c>
       <c r="C140" s="52" t="inlineStr">
         <is>
-          <t>6年6班</t>
+          <t>5年11班</t>
         </is>
       </c>
       <c r="D140" s="44" t="n">
@@ -9201,7 +10244,7 @@
       </c>
       <c r="C141" s="52" t="inlineStr">
         <is>
-          <t>6年7班</t>
+          <t>6年11班</t>
         </is>
       </c>
       <c r="D141" s="44" t="n">
@@ -9232,11 +10275,11 @@
       </c>
       <c r="C142" s="52" t="inlineStr">
         <is>
-          <t>6年8班</t>
+          <t>1年12班</t>
         </is>
       </c>
       <c r="D142" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E142" s="52" t="inlineStr">
         <is>
@@ -9263,7 +10306,7 @@
       </c>
       <c r="C143" s="52" t="inlineStr">
         <is>
-          <t>6年9班</t>
+          <t>3年12班</t>
         </is>
       </c>
       <c r="D143" s="44" t="n">
@@ -9294,7 +10337,7 @@
       </c>
       <c r="C144" s="52" t="inlineStr">
         <is>
-          <t>6年10班</t>
+          <t>4年12班</t>
         </is>
       </c>
       <c r="D144" s="44" t="n">
@@ -9325,7 +10368,7 @@
       </c>
       <c r="C145" s="52" t="inlineStr">
         <is>
-          <t>6年11班</t>
+          <t>5年12班</t>
         </is>
       </c>
       <c r="D145" s="44" t="n">
@@ -9418,7 +10461,7 @@
       </c>
       <c r="C148" s="52" t="inlineStr">
         <is>
-          <t>1年2班</t>
+          <t>2年1班</t>
         </is>
       </c>
       <c r="D148" s="44" t="n">
@@ -9449,11 +10492,11 @@
       </c>
       <c r="C149" s="52" t="inlineStr">
         <is>
-          <t>1年3班</t>
+          <t>3年1班</t>
         </is>
       </c>
       <c r="D149" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E149" s="52" t="inlineStr">
         <is>
@@ -9480,11 +10523,11 @@
       </c>
       <c r="C150" s="52" t="inlineStr">
         <is>
-          <t>1年4班</t>
+          <t>4年1班</t>
         </is>
       </c>
       <c r="D150" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E150" s="52" t="inlineStr">
         <is>
@@ -9511,11 +10554,11 @@
       </c>
       <c r="C151" s="52" t="inlineStr">
         <is>
-          <t>1年5班</t>
+          <t>5年1班</t>
         </is>
       </c>
       <c r="D151" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E151" s="52" t="inlineStr">
         <is>
@@ -9542,11 +10585,11 @@
       </c>
       <c r="C152" s="52" t="inlineStr">
         <is>
-          <t>1年6班</t>
+          <t>6年1班</t>
         </is>
       </c>
       <c r="D152" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E152" s="52" t="inlineStr">
         <is>
@@ -9573,7 +10616,7 @@
       </c>
       <c r="C153" s="52" t="inlineStr">
         <is>
-          <t>1年7班</t>
+          <t>1年2班</t>
         </is>
       </c>
       <c r="D153" s="44" t="n">
@@ -9604,7 +10647,7 @@
       </c>
       <c r="C154" s="52" t="inlineStr">
         <is>
-          <t>1年8班</t>
+          <t>2年2班</t>
         </is>
       </c>
       <c r="D154" s="44" t="n">
@@ -9635,11 +10678,11 @@
       </c>
       <c r="C155" s="52" t="inlineStr">
         <is>
-          <t>1年9班</t>
+          <t>3年2班</t>
         </is>
       </c>
       <c r="D155" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E155" s="52" t="inlineStr">
         <is>
@@ -9666,11 +10709,11 @@
       </c>
       <c r="C156" s="52" t="inlineStr">
         <is>
-          <t>1年10班</t>
+          <t>4年2班</t>
         </is>
       </c>
       <c r="D156" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E156" s="52" t="inlineStr">
         <is>
@@ -9697,11 +10740,11 @@
       </c>
       <c r="C157" s="52" t="inlineStr">
         <is>
-          <t>1年11班</t>
+          <t>5年2班</t>
         </is>
       </c>
       <c r="D157" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E157" s="52" t="inlineStr">
         <is>
@@ -9728,11 +10771,11 @@
       </c>
       <c r="C158" s="52" t="inlineStr">
         <is>
-          <t>1年12班</t>
+          <t>6年2班</t>
         </is>
       </c>
       <c r="D158" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E158" s="52" t="inlineStr">
         <is>
@@ -9749,7 +10792,7 @@
     <row r="159" ht="15" customHeight="1" s="36">
       <c r="A159" s="44" t="inlineStr">
         <is>
-          <t>音樂甲</t>
+          <t>音樂乙</t>
         </is>
       </c>
       <c r="B159" s="52" t="inlineStr">
@@ -9759,7 +10802,7 @@
       </c>
       <c r="C159" s="52" t="inlineStr">
         <is>
-          <t>2年1班</t>
+          <t>1年3班</t>
         </is>
       </c>
       <c r="D159" s="44" t="n">
@@ -9780,7 +10823,7 @@
     <row r="160" ht="15" customHeight="1" s="36">
       <c r="A160" s="44" t="inlineStr">
         <is>
-          <t>音樂甲</t>
+          <t>音樂乙</t>
         </is>
       </c>
       <c r="B160" s="52" t="inlineStr">
@@ -9790,7 +10833,7 @@
       </c>
       <c r="C160" s="52" t="inlineStr">
         <is>
-          <t>2年2班</t>
+          <t>2年3班</t>
         </is>
       </c>
       <c r="D160" s="44" t="n">
@@ -9811,7 +10854,7 @@
     <row r="161" ht="15" customHeight="1" s="36">
       <c r="A161" s="44" t="inlineStr">
         <is>
-          <t>音樂甲</t>
+          <t>音樂乙</t>
         </is>
       </c>
       <c r="B161" s="52" t="inlineStr">
@@ -9821,11 +10864,11 @@
       </c>
       <c r="C161" s="52" t="inlineStr">
         <is>
-          <t>2年3班</t>
+          <t>3年3班</t>
         </is>
       </c>
       <c r="D161" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E161" s="52" t="inlineStr">
         <is>
@@ -9842,7 +10885,7 @@
     <row r="162" ht="15" customHeight="1" s="36">
       <c r="A162" s="44" t="inlineStr">
         <is>
-          <t>音樂甲</t>
+          <t>音樂乙</t>
         </is>
       </c>
       <c r="B162" s="52" t="inlineStr">
@@ -9852,11 +10895,11 @@
       </c>
       <c r="C162" s="52" t="inlineStr">
         <is>
-          <t>2年4班</t>
+          <t>4年3班</t>
         </is>
       </c>
       <c r="D162" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E162" s="52" t="inlineStr">
         <is>
@@ -9873,7 +10916,7 @@
     <row r="163" ht="15" customHeight="1" s="36">
       <c r="A163" s="44" t="inlineStr">
         <is>
-          <t>音樂甲</t>
+          <t>音樂乙</t>
         </is>
       </c>
       <c r="B163" s="52" t="inlineStr">
@@ -9883,11 +10926,11 @@
       </c>
       <c r="C163" s="52" t="inlineStr">
         <is>
-          <t>2年5班</t>
+          <t>5年3班</t>
         </is>
       </c>
       <c r="D163" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E163" s="52" t="inlineStr">
         <is>
@@ -9904,7 +10947,7 @@
     <row r="164" ht="15" customHeight="1" s="36">
       <c r="A164" s="44" t="inlineStr">
         <is>
-          <t>音樂甲</t>
+          <t>音樂乙</t>
         </is>
       </c>
       <c r="B164" s="52" t="inlineStr">
@@ -9914,11 +10957,11 @@
       </c>
       <c r="C164" s="52" t="inlineStr">
         <is>
-          <t>2年6班</t>
+          <t>6年3班</t>
         </is>
       </c>
       <c r="D164" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E164" s="52" t="inlineStr">
         <is>
@@ -9935,7 +10978,7 @@
     <row r="165" ht="15" customHeight="1" s="36">
       <c r="A165" s="44" t="inlineStr">
         <is>
-          <t>音樂甲</t>
+          <t>音樂乙</t>
         </is>
       </c>
       <c r="B165" s="52" t="inlineStr">
@@ -9945,7 +10988,7 @@
       </c>
       <c r="C165" s="52" t="inlineStr">
         <is>
-          <t>2年7班</t>
+          <t>1年4班</t>
         </is>
       </c>
       <c r="D165" s="44" t="n">
@@ -9966,7 +11009,7 @@
     <row r="166" ht="15" customHeight="1" s="36">
       <c r="A166" s="44" t="inlineStr">
         <is>
-          <t>音樂甲</t>
+          <t>音樂乙</t>
         </is>
       </c>
       <c r="B166" s="52" t="inlineStr">
@@ -9976,7 +11019,7 @@
       </c>
       <c r="C166" s="52" t="inlineStr">
         <is>
-          <t>2年8班</t>
+          <t>2年4班</t>
         </is>
       </c>
       <c r="D166" s="44" t="n">
@@ -10007,11 +11050,11 @@
       </c>
       <c r="C167" s="52" t="inlineStr">
         <is>
-          <t>2年9班</t>
+          <t>3年4班</t>
         </is>
       </c>
       <c r="D167" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E167" s="52" t="inlineStr">
         <is>
@@ -10038,11 +11081,11 @@
       </c>
       <c r="C168" s="52" t="inlineStr">
         <is>
-          <t>2年10班</t>
+          <t>4年4班</t>
         </is>
       </c>
       <c r="D168" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E168" s="52" t="inlineStr">
         <is>
@@ -10069,11 +11112,11 @@
       </c>
       <c r="C169" s="52" t="inlineStr">
         <is>
-          <t>2年11班</t>
+          <t>5年4班</t>
         </is>
       </c>
       <c r="D169" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E169" s="52" t="inlineStr">
         <is>
@@ -10100,7 +11143,7 @@
       </c>
       <c r="C170" s="52" t="inlineStr">
         <is>
-          <t>3年1班</t>
+          <t>6年4班</t>
         </is>
       </c>
       <c r="D170" s="44" t="n">
@@ -10121,7 +11164,7 @@
     <row r="171" ht="15" customHeight="1" s="36">
       <c r="A171" s="44" t="inlineStr">
         <is>
-          <t>音樂乙</t>
+          <t>音樂丙</t>
         </is>
       </c>
       <c r="B171" s="52" t="inlineStr">
@@ -10131,11 +11174,11 @@
       </c>
       <c r="C171" s="52" t="inlineStr">
         <is>
-          <t>3年2班</t>
+          <t>1年5班</t>
         </is>
       </c>
       <c r="D171" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E171" s="52" t="inlineStr">
         <is>
@@ -10152,7 +11195,7 @@
     <row r="172" ht="15" customHeight="1" s="36">
       <c r="A172" s="44" t="inlineStr">
         <is>
-          <t>音樂乙</t>
+          <t>音樂丙</t>
         </is>
       </c>
       <c r="B172" s="52" t="inlineStr">
@@ -10162,11 +11205,11 @@
       </c>
       <c r="C172" s="52" t="inlineStr">
         <is>
-          <t>3年3班</t>
+          <t>2年5班</t>
         </is>
       </c>
       <c r="D172" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E172" s="52" t="inlineStr">
         <is>
@@ -10183,7 +11226,7 @@
     <row r="173" ht="15" customHeight="1" s="36">
       <c r="A173" s="44" t="inlineStr">
         <is>
-          <t>音樂乙</t>
+          <t>音樂丙</t>
         </is>
       </c>
       <c r="B173" s="52" t="inlineStr">
@@ -10193,7 +11236,7 @@
       </c>
       <c r="C173" s="52" t="inlineStr">
         <is>
-          <t>3年4班</t>
+          <t>3年5班</t>
         </is>
       </c>
       <c r="D173" s="44" t="n">
@@ -10214,7 +11257,7 @@
     <row r="174" ht="15" customHeight="1" s="36">
       <c r="A174" s="44" t="inlineStr">
         <is>
-          <t>音樂乙</t>
+          <t>音樂丙</t>
         </is>
       </c>
       <c r="B174" s="52" t="inlineStr">
@@ -10224,7 +11267,7 @@
       </c>
       <c r="C174" s="52" t="inlineStr">
         <is>
-          <t>3年5班</t>
+          <t>4年5班</t>
         </is>
       </c>
       <c r="D174" s="44" t="n">
@@ -10245,7 +11288,7 @@
     <row r="175" ht="15" customHeight="1" s="36">
       <c r="A175" s="44" t="inlineStr">
         <is>
-          <t>音樂乙</t>
+          <t>音樂丙</t>
         </is>
       </c>
       <c r="B175" s="52" t="inlineStr">
@@ -10255,7 +11298,7 @@
       </c>
       <c r="C175" s="52" t="inlineStr">
         <is>
-          <t>3年6班</t>
+          <t>5年5班</t>
         </is>
       </c>
       <c r="D175" s="44" t="n">
@@ -10276,7 +11319,7 @@
     <row r="176" ht="15" customHeight="1" s="36">
       <c r="A176" s="44" t="inlineStr">
         <is>
-          <t>音樂乙</t>
+          <t>音樂丙</t>
         </is>
       </c>
       <c r="B176" s="52" t="inlineStr">
@@ -10286,7 +11329,7 @@
       </c>
       <c r="C176" s="52" t="inlineStr">
         <is>
-          <t>3年7班</t>
+          <t>6年5班</t>
         </is>
       </c>
       <c r="D176" s="44" t="n">
@@ -10307,7 +11350,7 @@
     <row r="177" ht="15" customHeight="1" s="36">
       <c r="A177" s="44" t="inlineStr">
         <is>
-          <t>音樂乙</t>
+          <t>音樂丙</t>
         </is>
       </c>
       <c r="B177" s="52" t="inlineStr">
@@ -10317,11 +11360,11 @@
       </c>
       <c r="C177" s="52" t="inlineStr">
         <is>
-          <t>3年8班</t>
+          <t>1年6班</t>
         </is>
       </c>
       <c r="D177" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E177" s="52" t="inlineStr">
         <is>
@@ -10348,11 +11391,11 @@
       </c>
       <c r="C178" s="52" t="inlineStr">
         <is>
-          <t>3年9班</t>
+          <t>2年6班</t>
         </is>
       </c>
       <c r="D178" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E178" s="52" t="inlineStr">
         <is>
@@ -10379,7 +11422,7 @@
       </c>
       <c r="C179" s="52" t="inlineStr">
         <is>
-          <t>3年10班</t>
+          <t>3年6班</t>
         </is>
       </c>
       <c r="D179" s="44" t="n">
@@ -10410,7 +11453,7 @@
       </c>
       <c r="C180" s="52" t="inlineStr">
         <is>
-          <t>3年11班</t>
+          <t>4年6班</t>
         </is>
       </c>
       <c r="D180" s="44" t="n">
@@ -10441,7 +11484,7 @@
       </c>
       <c r="C181" s="52" t="inlineStr">
         <is>
-          <t>3年12班</t>
+          <t>5年6班</t>
         </is>
       </c>
       <c r="D181" s="44" t="n">
@@ -10472,7 +11515,7 @@
       </c>
       <c r="C182" s="52" t="inlineStr">
         <is>
-          <t>4年1班</t>
+          <t>6年6班</t>
         </is>
       </c>
       <c r="D182" s="44" t="n">
@@ -10493,7 +11536,7 @@
     <row r="183" ht="15" customHeight="1" s="36">
       <c r="A183" s="44" t="inlineStr">
         <is>
-          <t>音樂丙</t>
+          <t>音樂丁</t>
         </is>
       </c>
       <c r="B183" s="52" t="inlineStr">
@@ -10503,11 +11546,11 @@
       </c>
       <c r="C183" s="52" t="inlineStr">
         <is>
-          <t>4年2班</t>
+          <t>1年7班</t>
         </is>
       </c>
       <c r="D183" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E183" s="52" t="inlineStr">
         <is>
@@ -10524,7 +11567,7 @@
     <row r="184" ht="15" customHeight="1" s="36">
       <c r="A184" s="44" t="inlineStr">
         <is>
-          <t>音樂丙</t>
+          <t>音樂丁</t>
         </is>
       </c>
       <c r="B184" s="52" t="inlineStr">
@@ -10534,11 +11577,11 @@
       </c>
       <c r="C184" s="52" t="inlineStr">
         <is>
-          <t>4年3班</t>
+          <t>2年7班</t>
         </is>
       </c>
       <c r="D184" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E184" s="52" t="inlineStr">
         <is>
@@ -10555,7 +11598,7 @@
     <row r="185" ht="15" customHeight="1" s="36">
       <c r="A185" s="44" t="inlineStr">
         <is>
-          <t>音樂丙</t>
+          <t>音樂丁</t>
         </is>
       </c>
       <c r="B185" s="52" t="inlineStr">
@@ -10565,7 +11608,7 @@
       </c>
       <c r="C185" s="52" t="inlineStr">
         <is>
-          <t>4年4班</t>
+          <t>3年7班</t>
         </is>
       </c>
       <c r="D185" s="44" t="n">
@@ -10586,7 +11629,7 @@
     <row r="186" ht="15" customHeight="1" s="36">
       <c r="A186" s="44" t="inlineStr">
         <is>
-          <t>音樂丙</t>
+          <t>音樂丁</t>
         </is>
       </c>
       <c r="B186" s="52" t="inlineStr">
@@ -10596,7 +11639,7 @@
       </c>
       <c r="C186" s="52" t="inlineStr">
         <is>
-          <t>4年5班</t>
+          <t>4年7班</t>
         </is>
       </c>
       <c r="D186" s="44" t="n">
@@ -10617,7 +11660,7 @@
     <row r="187" ht="15" customHeight="1" s="36">
       <c r="A187" s="44" t="inlineStr">
         <is>
-          <t>音樂丙</t>
+          <t>音樂丁</t>
         </is>
       </c>
       <c r="B187" s="52" t="inlineStr">
@@ -10627,7 +11670,7 @@
       </c>
       <c r="C187" s="52" t="inlineStr">
         <is>
-          <t>4年6班</t>
+          <t>5年7班</t>
         </is>
       </c>
       <c r="D187" s="44" t="n">
@@ -10658,7 +11701,7 @@
       </c>
       <c r="C188" s="52" t="inlineStr">
         <is>
-          <t>4年7班</t>
+          <t>6年7班</t>
         </is>
       </c>
       <c r="D188" s="44" t="n">
@@ -10689,11 +11732,11 @@
       </c>
       <c r="C189" s="52" t="inlineStr">
         <is>
-          <t>4年8班</t>
+          <t>1年8班</t>
         </is>
       </c>
       <c r="D189" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E189" s="52" t="inlineStr">
         <is>
@@ -10720,11 +11763,11 @@
       </c>
       <c r="C190" s="52" t="inlineStr">
         <is>
-          <t>4年9班</t>
+          <t>2年8班</t>
         </is>
       </c>
       <c r="D190" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E190" s="52" t="inlineStr">
         <is>
@@ -10751,7 +11794,7 @@
       </c>
       <c r="C191" s="52" t="inlineStr">
         <is>
-          <t>4年10班</t>
+          <t>3年8班</t>
         </is>
       </c>
       <c r="D191" s="44" t="n">
@@ -10782,7 +11825,7 @@
       </c>
       <c r="C192" s="52" t="inlineStr">
         <is>
-          <t>4年11班</t>
+          <t>4年8班</t>
         </is>
       </c>
       <c r="D192" s="44" t="n">
@@ -10813,7 +11856,7 @@
       </c>
       <c r="C193" s="52" t="inlineStr">
         <is>
-          <t>4年12班</t>
+          <t>5年8班</t>
         </is>
       </c>
       <c r="D193" s="44" t="n">
@@ -10844,7 +11887,7 @@
       </c>
       <c r="C194" s="52" t="inlineStr">
         <is>
-          <t>5年1班</t>
+          <t>6年8班</t>
         </is>
       </c>
       <c r="D194" s="44" t="n">
@@ -10865,7 +11908,7 @@
     <row r="195" ht="15" customHeight="1" s="36">
       <c r="A195" s="44" t="inlineStr">
         <is>
-          <t>音樂丁</t>
+          <t>音樂戊</t>
         </is>
       </c>
       <c r="B195" s="52" t="inlineStr">
@@ -10875,11 +11918,11 @@
       </c>
       <c r="C195" s="52" t="inlineStr">
         <is>
-          <t>5年2班</t>
+          <t>1年9班</t>
         </is>
       </c>
       <c r="D195" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E195" s="52" t="inlineStr">
         <is>
@@ -10896,7 +11939,7 @@
     <row r="196" ht="15" customHeight="1" s="36">
       <c r="A196" s="44" t="inlineStr">
         <is>
-          <t>音樂丁</t>
+          <t>音樂戊</t>
         </is>
       </c>
       <c r="B196" s="52" t="inlineStr">
@@ -10906,11 +11949,11 @@
       </c>
       <c r="C196" s="52" t="inlineStr">
         <is>
-          <t>5年3班</t>
+          <t>2年9班</t>
         </is>
       </c>
       <c r="D196" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E196" s="52" t="inlineStr">
         <is>
@@ -10927,7 +11970,7 @@
     <row r="197" ht="15" customHeight="1" s="36">
       <c r="A197" s="44" t="inlineStr">
         <is>
-          <t>音樂丁</t>
+          <t>音樂戊</t>
         </is>
       </c>
       <c r="B197" s="52" t="inlineStr">
@@ -10937,7 +11980,7 @@
       </c>
       <c r="C197" s="52" t="inlineStr">
         <is>
-          <t>5年4班</t>
+          <t>3年9班</t>
         </is>
       </c>
       <c r="D197" s="44" t="n">
@@ -10968,7 +12011,7 @@
       </c>
       <c r="C198" s="52" t="inlineStr">
         <is>
-          <t>5年5班</t>
+          <t>4年9班</t>
         </is>
       </c>
       <c r="D198" s="44" t="n">
@@ -10999,7 +12042,7 @@
       </c>
       <c r="C199" s="52" t="inlineStr">
         <is>
-          <t>5年6班</t>
+          <t>5年9班</t>
         </is>
       </c>
       <c r="D199" s="44" t="n">
@@ -11030,7 +12073,7 @@
       </c>
       <c r="C200" s="52" t="inlineStr">
         <is>
-          <t>5年7班</t>
+          <t>6年9班</t>
         </is>
       </c>
       <c r="D200" s="44" t="n">
@@ -11061,11 +12104,11 @@
       </c>
       <c r="C201" s="52" t="inlineStr">
         <is>
-          <t>5年8班</t>
+          <t>1年10班</t>
         </is>
       </c>
       <c r="D201" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E201" s="52" t="inlineStr">
         <is>
@@ -11092,11 +12135,11 @@
       </c>
       <c r="C202" s="52" t="inlineStr">
         <is>
-          <t>5年9班</t>
+          <t>2年10班</t>
         </is>
       </c>
       <c r="D202" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E202" s="52" t="inlineStr">
         <is>
@@ -11123,7 +12166,7 @@
       </c>
       <c r="C203" s="52" t="inlineStr">
         <is>
-          <t>5年10班</t>
+          <t>3年10班</t>
         </is>
       </c>
       <c r="D203" s="44" t="n">
@@ -11154,7 +12197,7 @@
       </c>
       <c r="C204" s="52" t="inlineStr">
         <is>
-          <t>5年11班</t>
+          <t>4年10班</t>
         </is>
       </c>
       <c r="D204" s="44" t="n">
@@ -11185,7 +12228,7 @@
       </c>
       <c r="C205" s="52" t="inlineStr">
         <is>
-          <t>5年12班</t>
+          <t>5年10班</t>
         </is>
       </c>
       <c r="D205" s="44" t="n">
@@ -11216,7 +12259,7 @@
       </c>
       <c r="C206" s="52" t="inlineStr">
         <is>
-          <t>6年1班</t>
+          <t>6年10班</t>
         </is>
       </c>
       <c r="D206" s="44" t="n">
@@ -11237,7 +12280,7 @@
     <row r="207" ht="15" customHeight="1" s="36">
       <c r="A207" s="44" t="inlineStr">
         <is>
-          <t>音樂戊</t>
+          <t>音樂己</t>
         </is>
       </c>
       <c r="B207" s="52" t="inlineStr">
@@ -11247,11 +12290,11 @@
       </c>
       <c r="C207" s="52" t="inlineStr">
         <is>
-          <t>6年2班</t>
+          <t>1年11班</t>
         </is>
       </c>
       <c r="D207" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E207" s="52" t="inlineStr">
         <is>
@@ -11278,11 +12321,11 @@
       </c>
       <c r="C208" s="52" t="inlineStr">
         <is>
-          <t>6年3班</t>
+          <t>2年11班</t>
         </is>
       </c>
       <c r="D208" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E208" s="52" t="inlineStr">
         <is>
@@ -11309,7 +12352,7 @@
       </c>
       <c r="C209" s="52" t="inlineStr">
         <is>
-          <t>6年4班</t>
+          <t>3年11班</t>
         </is>
       </c>
       <c r="D209" s="44" t="n">
@@ -11340,7 +12383,7 @@
       </c>
       <c r="C210" s="52" t="inlineStr">
         <is>
-          <t>6年5班</t>
+          <t>4年11班</t>
         </is>
       </c>
       <c r="D210" s="44" t="n">
@@ -11371,7 +12414,7 @@
       </c>
       <c r="C211" s="52" t="inlineStr">
         <is>
-          <t>6年6班</t>
+          <t>5年11班</t>
         </is>
       </c>
       <c r="D211" s="44" t="n">
@@ -11402,7 +12445,7 @@
       </c>
       <c r="C212" s="52" t="inlineStr">
         <is>
-          <t>6年7班</t>
+          <t>6年11班</t>
         </is>
       </c>
       <c r="D212" s="44" t="n">
@@ -11433,11 +12476,11 @@
       </c>
       <c r="C213" s="52" t="inlineStr">
         <is>
-          <t>6年8班</t>
+          <t>1年12班</t>
         </is>
       </c>
       <c r="D213" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E213" s="52" t="inlineStr">
         <is>
@@ -11464,7 +12507,7 @@
       </c>
       <c r="C214" s="52" t="inlineStr">
         <is>
-          <t>6年9班</t>
+          <t>3年12班</t>
         </is>
       </c>
       <c r="D214" s="44" t="n">
@@ -11495,7 +12538,7 @@
       </c>
       <c r="C215" s="52" t="inlineStr">
         <is>
-          <t>6年10班</t>
+          <t>4年12班</t>
         </is>
       </c>
       <c r="D215" s="44" t="n">
@@ -11526,7 +12569,7 @@
       </c>
       <c r="C216" s="52" t="inlineStr">
         <is>
-          <t>6年11班</t>
+          <t>5年12班</t>
         </is>
       </c>
       <c r="D216" s="44" t="n">
@@ -11625,7 +12668,7 @@
       </c>
       <c r="C219" s="52" t="inlineStr">
         <is>
-          <t>3年2班</t>
+          <t>4年1班</t>
         </is>
       </c>
       <c r="D219" s="44" t="n">
@@ -11662,7 +12705,7 @@
       </c>
       <c r="C220" s="52" t="inlineStr">
         <is>
-          <t>3年3班</t>
+          <t>5年1班</t>
         </is>
       </c>
       <c r="D220" s="44" t="n">
@@ -11699,7 +12742,7 @@
       </c>
       <c r="C221" s="52" t="inlineStr">
         <is>
-          <t>3年4班</t>
+          <t>6年1班</t>
         </is>
       </c>
       <c r="D221" s="44" t="n">
@@ -11736,7 +12779,7 @@
       </c>
       <c r="C222" s="52" t="inlineStr">
         <is>
-          <t>3年5班</t>
+          <t>3年2班</t>
         </is>
       </c>
       <c r="D222" s="44" t="n">
@@ -11773,7 +12816,7 @@
       </c>
       <c r="C223" s="52" t="inlineStr">
         <is>
-          <t>3年6班</t>
+          <t>4年2班</t>
         </is>
       </c>
       <c r="D223" s="44" t="n">
@@ -11810,7 +12853,7 @@
       </c>
       <c r="C224" s="52" t="inlineStr">
         <is>
-          <t>3年7班</t>
+          <t>5年2班</t>
         </is>
       </c>
       <c r="D224" s="44" t="n">
@@ -11847,7 +12890,7 @@
       </c>
       <c r="C225" s="52" t="inlineStr">
         <is>
-          <t>3年8班</t>
+          <t>6年2班</t>
         </is>
       </c>
       <c r="D225" s="44" t="n">
@@ -11884,7 +12927,7 @@
       </c>
       <c r="C226" s="52" t="inlineStr">
         <is>
-          <t>3年9班</t>
+          <t>3年3班</t>
         </is>
       </c>
       <c r="D226" s="44" t="n">
@@ -11921,7 +12964,7 @@
       </c>
       <c r="C227" s="52" t="inlineStr">
         <is>
-          <t>3年10班</t>
+          <t>4年3班</t>
         </is>
       </c>
       <c r="D227" s="44" t="n">
@@ -11958,7 +13001,7 @@
       </c>
       <c r="C228" s="52" t="inlineStr">
         <is>
-          <t>3年11班</t>
+          <t>5年3班</t>
         </is>
       </c>
       <c r="D228" s="44" t="n">
@@ -11995,7 +13038,7 @@
       </c>
       <c r="C229" s="52" t="inlineStr">
         <is>
-          <t>3年12班</t>
+          <t>6年3班</t>
         </is>
       </c>
       <c r="D229" s="44" t="n">
@@ -12032,7 +13075,7 @@
       </c>
       <c r="C230" s="52" t="inlineStr">
         <is>
-          <t>4年1班</t>
+          <t>3年4班</t>
         </is>
       </c>
       <c r="D230" s="44" t="n">
@@ -12069,7 +13112,7 @@
       </c>
       <c r="C231" s="52" t="inlineStr">
         <is>
-          <t>4年2班</t>
+          <t>4年4班</t>
         </is>
       </c>
       <c r="D231" s="44" t="n">
@@ -12106,7 +13149,7 @@
       </c>
       <c r="C232" s="52" t="inlineStr">
         <is>
-          <t>4年3班</t>
+          <t>5年4班</t>
         </is>
       </c>
       <c r="D232" s="44" t="n">
@@ -12143,7 +13186,7 @@
       </c>
       <c r="C233" s="52" t="inlineStr">
         <is>
-          <t>4年4班</t>
+          <t>6年4班</t>
         </is>
       </c>
       <c r="D233" s="44" t="n">
@@ -12180,7 +13223,7 @@
       </c>
       <c r="C234" s="52" t="inlineStr">
         <is>
-          <t>4年5班</t>
+          <t>3年5班</t>
         </is>
       </c>
       <c r="D234" s="44" t="n">
@@ -12217,7 +13260,7 @@
       </c>
       <c r="C235" s="52" t="inlineStr">
         <is>
-          <t>4年6班</t>
+          <t>4年5班</t>
         </is>
       </c>
       <c r="D235" s="44" t="n">
@@ -12254,7 +13297,7 @@
       </c>
       <c r="C236" s="52" t="inlineStr">
         <is>
-          <t>4年7班</t>
+          <t>5年5班</t>
         </is>
       </c>
       <c r="D236" s="44" t="n">
@@ -12291,7 +13334,7 @@
       </c>
       <c r="C237" s="52" t="inlineStr">
         <is>
-          <t>4年8班</t>
+          <t>6年5班</t>
         </is>
       </c>
       <c r="D237" s="44" t="n">
@@ -12328,7 +13371,7 @@
       </c>
       <c r="C238" s="52" t="inlineStr">
         <is>
-          <t>4年9班</t>
+          <t>3年6班</t>
         </is>
       </c>
       <c r="D238" s="44" t="n">
@@ -12365,7 +13408,7 @@
       </c>
       <c r="C239" s="52" t="inlineStr">
         <is>
-          <t>4年10班</t>
+          <t>4年6班</t>
         </is>
       </c>
       <c r="D239" s="44" t="n">
@@ -12402,7 +13445,7 @@
       </c>
       <c r="C240" s="52" t="inlineStr">
         <is>
-          <t>4年11班</t>
+          <t>5年6班</t>
         </is>
       </c>
       <c r="D240" s="44" t="n">
@@ -12439,7 +13482,7 @@
       </c>
       <c r="C241" s="52" t="inlineStr">
         <is>
-          <t>4年12班</t>
+          <t>6年6班</t>
         </is>
       </c>
       <c r="D241" s="44" t="n">
@@ -12476,7 +13519,7 @@
       </c>
       <c r="C242" s="52" t="inlineStr">
         <is>
-          <t>5年1班</t>
+          <t>3年7班</t>
         </is>
       </c>
       <c r="D242" s="44" t="n">
@@ -12513,7 +13556,7 @@
       </c>
       <c r="C243" s="52" t="inlineStr">
         <is>
-          <t>5年2班</t>
+          <t>4年7班</t>
         </is>
       </c>
       <c r="D243" s="44" t="n">
@@ -12550,7 +13593,7 @@
       </c>
       <c r="C244" s="52" t="inlineStr">
         <is>
-          <t>5年3班</t>
+          <t>5年7班</t>
         </is>
       </c>
       <c r="D244" s="44" t="n">
@@ -12587,7 +13630,7 @@
       </c>
       <c r="C245" s="52" t="inlineStr">
         <is>
-          <t>5年4班</t>
+          <t>6年7班</t>
         </is>
       </c>
       <c r="D245" s="44" t="n">
@@ -12624,7 +13667,7 @@
       </c>
       <c r="C246" s="52" t="inlineStr">
         <is>
-          <t>5年5班</t>
+          <t>3年8班</t>
         </is>
       </c>
       <c r="D246" s="44" t="n">
@@ -12661,7 +13704,7 @@
       </c>
       <c r="C247" s="52" t="inlineStr">
         <is>
-          <t>5年6班</t>
+          <t>4年8班</t>
         </is>
       </c>
       <c r="D247" s="44" t="n">
@@ -12698,7 +13741,7 @@
       </c>
       <c r="C248" s="52" t="inlineStr">
         <is>
-          <t>5年7班</t>
+          <t>5年8班</t>
         </is>
       </c>
       <c r="D248" s="44" t="n">
@@ -12735,7 +13778,7 @@
       </c>
       <c r="C249" s="52" t="inlineStr">
         <is>
-          <t>5年8班</t>
+          <t>6年8班</t>
         </is>
       </c>
       <c r="D249" s="44" t="n">
@@ -12772,7 +13815,7 @@
       </c>
       <c r="C250" s="52" t="inlineStr">
         <is>
-          <t>5年9班</t>
+          <t>3年9班</t>
         </is>
       </c>
       <c r="D250" s="44" t="n">
@@ -12809,7 +13852,7 @@
       </c>
       <c r="C251" s="52" t="inlineStr">
         <is>
-          <t>5年10班</t>
+          <t>4年9班</t>
         </is>
       </c>
       <c r="D251" s="44" t="n">
@@ -12846,7 +13889,7 @@
       </c>
       <c r="C252" s="52" t="inlineStr">
         <is>
-          <t>5年11班</t>
+          <t>5年9班</t>
         </is>
       </c>
       <c r="D252" s="44" t="n">
@@ -12883,7 +13926,7 @@
       </c>
       <c r="C253" s="52" t="inlineStr">
         <is>
-          <t>5年12班</t>
+          <t>6年9班</t>
         </is>
       </c>
       <c r="D253" s="44" t="n">
@@ -12920,7 +13963,7 @@
       </c>
       <c r="C254" s="52" t="inlineStr">
         <is>
-          <t>6年1班</t>
+          <t>3年10班</t>
         </is>
       </c>
       <c r="D254" s="44" t="n">
@@ -12957,7 +14000,7 @@
       </c>
       <c r="C255" s="52" t="inlineStr">
         <is>
-          <t>6年2班</t>
+          <t>4年10班</t>
         </is>
       </c>
       <c r="D255" s="44" t="n">
@@ -12994,7 +14037,7 @@
       </c>
       <c r="C256" s="52" t="inlineStr">
         <is>
-          <t>6年3班</t>
+          <t>5年10班</t>
         </is>
       </c>
       <c r="D256" s="44" t="n">
@@ -13031,7 +14074,7 @@
       </c>
       <c r="C257" s="52" t="inlineStr">
         <is>
-          <t>6年4班</t>
+          <t>6年10班</t>
         </is>
       </c>
       <c r="D257" s="44" t="n">
@@ -13068,7 +14111,7 @@
       </c>
       <c r="C258" s="52" t="inlineStr">
         <is>
-          <t>6年5班</t>
+          <t>3年11班</t>
         </is>
       </c>
       <c r="D258" s="44" t="n">
@@ -13105,7 +14148,7 @@
       </c>
       <c r="C259" s="52" t="inlineStr">
         <is>
-          <t>6年6班</t>
+          <t>4年11班</t>
         </is>
       </c>
       <c r="D259" s="44" t="n">
@@ -13142,7 +14185,7 @@
       </c>
       <c r="C260" s="52" t="inlineStr">
         <is>
-          <t>6年7班</t>
+          <t>5年11班</t>
         </is>
       </c>
       <c r="D260" s="44" t="n">
@@ -13179,7 +14222,7 @@
       </c>
       <c r="C261" s="52" t="inlineStr">
         <is>
-          <t>6年8班</t>
+          <t>6年11班</t>
         </is>
       </c>
       <c r="D261" s="44" t="n">
@@ -13216,7 +14259,7 @@
       </c>
       <c r="C262" s="52" t="inlineStr">
         <is>
-          <t>6年9班</t>
+          <t>3年12班</t>
         </is>
       </c>
       <c r="D262" s="44" t="n">
@@ -13253,7 +14296,7 @@
       </c>
       <c r="C263" s="52" t="inlineStr">
         <is>
-          <t>6年10班</t>
+          <t>4年12班</t>
         </is>
       </c>
       <c r="D263" s="44" t="n">
@@ -13290,7 +14333,7 @@
       </c>
       <c r="C264" s="52" t="inlineStr">
         <is>
-          <t>6年11班</t>
+          <t>5年12班</t>
         </is>
       </c>
       <c r="D264" s="44" t="n">
@@ -13395,7 +14438,7 @@
       </c>
       <c r="C267" s="52" t="inlineStr">
         <is>
-          <t>3年2班</t>
+          <t>4年1班</t>
         </is>
       </c>
       <c r="D267" s="44" t="n">
@@ -13426,7 +14469,7 @@
       </c>
       <c r="C268" s="52" t="inlineStr">
         <is>
-          <t>3年3班</t>
+          <t>5年1班</t>
         </is>
       </c>
       <c r="D268" s="44" t="n">
@@ -13457,7 +14500,7 @@
       </c>
       <c r="C269" s="52" t="inlineStr">
         <is>
-          <t>3年4班</t>
+          <t>6年1班</t>
         </is>
       </c>
       <c r="D269" s="44" t="n">
@@ -13488,7 +14531,7 @@
       </c>
       <c r="C270" s="52" t="inlineStr">
         <is>
-          <t>3年5班</t>
+          <t>3年2班</t>
         </is>
       </c>
       <c r="D270" s="44" t="n">
@@ -13519,7 +14562,7 @@
       </c>
       <c r="C271" s="52" t="inlineStr">
         <is>
-          <t>3年6班</t>
+          <t>4年2班</t>
         </is>
       </c>
       <c r="D271" s="44" t="n">
@@ -13550,7 +14593,7 @@
       </c>
       <c r="C272" s="52" t="inlineStr">
         <is>
-          <t>3年7班</t>
+          <t>5年2班</t>
         </is>
       </c>
       <c r="D272" s="44" t="n">
@@ -13581,7 +14624,7 @@
       </c>
       <c r="C273" s="52" t="inlineStr">
         <is>
-          <t>3年8班</t>
+          <t>6年2班</t>
         </is>
       </c>
       <c r="D273" s="44" t="n">
@@ -13612,7 +14655,7 @@
       </c>
       <c r="C274" s="52" t="inlineStr">
         <is>
-          <t>3年9班</t>
+          <t>3年3班</t>
         </is>
       </c>
       <c r="D274" s="44" t="n">
@@ -13643,7 +14686,7 @@
       </c>
       <c r="C275" s="52" t="inlineStr">
         <is>
-          <t>3年10班</t>
+          <t>4年3班</t>
         </is>
       </c>
       <c r="D275" s="44" t="n">
@@ -13674,7 +14717,7 @@
       </c>
       <c r="C276" s="52" t="inlineStr">
         <is>
-          <t>3年11班</t>
+          <t>5年3班</t>
         </is>
       </c>
       <c r="D276" s="44" t="n">
@@ -13705,7 +14748,7 @@
       </c>
       <c r="C277" s="52" t="inlineStr">
         <is>
-          <t>3年12班</t>
+          <t>6年3班</t>
         </is>
       </c>
       <c r="D277" s="44" t="n">
@@ -13736,7 +14779,7 @@
       </c>
       <c r="C278" s="52" t="inlineStr">
         <is>
-          <t>4年1班</t>
+          <t>3年4班</t>
         </is>
       </c>
       <c r="D278" s="44" t="n">
@@ -13767,7 +14810,7 @@
       </c>
       <c r="C279" s="52" t="inlineStr">
         <is>
-          <t>4年2班</t>
+          <t>4年4班</t>
         </is>
       </c>
       <c r="D279" s="44" t="n">
@@ -13798,7 +14841,7 @@
       </c>
       <c r="C280" s="52" t="inlineStr">
         <is>
-          <t>4年3班</t>
+          <t>5年4班</t>
         </is>
       </c>
       <c r="D280" s="44" t="n">
@@ -13829,7 +14872,7 @@
       </c>
       <c r="C281" s="52" t="inlineStr">
         <is>
-          <t>4年4班</t>
+          <t>6年4班</t>
         </is>
       </c>
       <c r="D281" s="44" t="n">
@@ -13860,7 +14903,7 @@
       </c>
       <c r="C282" s="52" t="inlineStr">
         <is>
-          <t>4年5班</t>
+          <t>3年5班</t>
         </is>
       </c>
       <c r="D282" s="44" t="n">
@@ -13891,7 +14934,7 @@
       </c>
       <c r="C283" s="52" t="inlineStr">
         <is>
-          <t>4年6班</t>
+          <t>4年5班</t>
         </is>
       </c>
       <c r="D283" s="44" t="n">
@@ -13922,7 +14965,7 @@
       </c>
       <c r="C284" s="52" t="inlineStr">
         <is>
-          <t>4年7班</t>
+          <t>5年5班</t>
         </is>
       </c>
       <c r="D284" s="44" t="n">
@@ -13953,7 +14996,7 @@
       </c>
       <c r="C285" s="52" t="inlineStr">
         <is>
-          <t>4年8班</t>
+          <t>6年5班</t>
         </is>
       </c>
       <c r="D285" s="44" t="n">
@@ -13984,7 +15027,7 @@
       </c>
       <c r="C286" s="52" t="inlineStr">
         <is>
-          <t>4年9班</t>
+          <t>3年6班</t>
         </is>
       </c>
       <c r="D286" s="44" t="n">
@@ -14015,7 +15058,7 @@
       </c>
       <c r="C287" s="52" t="inlineStr">
         <is>
-          <t>4年10班</t>
+          <t>4年6班</t>
         </is>
       </c>
       <c r="D287" s="44" t="n">
@@ -14046,7 +15089,7 @@
       </c>
       <c r="C288" s="52" t="inlineStr">
         <is>
-          <t>4年11班</t>
+          <t>5年6班</t>
         </is>
       </c>
       <c r="D288" s="44" t="n">
@@ -14077,7 +15120,7 @@
       </c>
       <c r="C289" s="52" t="inlineStr">
         <is>
-          <t>4年12班</t>
+          <t>6年6班</t>
         </is>
       </c>
       <c r="D289" s="44" t="n">
@@ -14108,7 +15151,7 @@
       </c>
       <c r="C290" s="52" t="inlineStr">
         <is>
-          <t>5年1班</t>
+          <t>3年7班</t>
         </is>
       </c>
       <c r="D290" s="44" t="n">
@@ -14139,7 +15182,7 @@
       </c>
       <c r="C291" s="52" t="inlineStr">
         <is>
-          <t>5年2班</t>
+          <t>4年7班</t>
         </is>
       </c>
       <c r="D291" s="44" t="n">
@@ -14170,7 +15213,7 @@
       </c>
       <c r="C292" s="52" t="inlineStr">
         <is>
-          <t>5年3班</t>
+          <t>5年7班</t>
         </is>
       </c>
       <c r="D292" s="44" t="n">
@@ -14201,7 +15244,7 @@
       </c>
       <c r="C293" s="52" t="inlineStr">
         <is>
-          <t>5年4班</t>
+          <t>6年7班</t>
         </is>
       </c>
       <c r="D293" s="44" t="n">
@@ -14232,7 +15275,7 @@
       </c>
       <c r="C294" s="52" t="inlineStr">
         <is>
-          <t>5年5班</t>
+          <t>3年8班</t>
         </is>
       </c>
       <c r="D294" s="44" t="n">
@@ -14263,7 +15306,7 @@
       </c>
       <c r="C295" s="52" t="inlineStr">
         <is>
-          <t>5年6班</t>
+          <t>4年8班</t>
         </is>
       </c>
       <c r="D295" s="44" t="n">
@@ -14294,7 +15337,7 @@
       </c>
       <c r="C296" s="52" t="inlineStr">
         <is>
-          <t>5年7班</t>
+          <t>5年8班</t>
         </is>
       </c>
       <c r="D296" s="44" t="n">
@@ -14325,7 +15368,7 @@
       </c>
       <c r="C297" s="52" t="inlineStr">
         <is>
-          <t>5年8班</t>
+          <t>6年8班</t>
         </is>
       </c>
       <c r="D297" s="44" t="n">
@@ -14356,7 +15399,7 @@
       </c>
       <c r="C298" s="52" t="inlineStr">
         <is>
-          <t>5年9班</t>
+          <t>3年9班</t>
         </is>
       </c>
       <c r="D298" s="44" t="n">
@@ -14387,7 +15430,7 @@
       </c>
       <c r="C299" s="52" t="inlineStr">
         <is>
-          <t>5年10班</t>
+          <t>4年9班</t>
         </is>
       </c>
       <c r="D299" s="44" t="n">
@@ -14418,7 +15461,7 @@
       </c>
       <c r="C300" s="52" t="inlineStr">
         <is>
-          <t>5年11班</t>
+          <t>5年9班</t>
         </is>
       </c>
       <c r="D300" s="44" t="n">
@@ -14449,7 +15492,7 @@
       </c>
       <c r="C301" s="52" t="inlineStr">
         <is>
-          <t>5年12班</t>
+          <t>6年9班</t>
         </is>
       </c>
       <c r="D301" s="44" t="n">
@@ -14480,7 +15523,7 @@
       </c>
       <c r="C302" s="52" t="inlineStr">
         <is>
-          <t>6年1班</t>
+          <t>3年10班</t>
         </is>
       </c>
       <c r="D302" s="44" t="n">
@@ -14511,7 +15554,7 @@
       </c>
       <c r="C303" s="52" t="inlineStr">
         <is>
-          <t>6年2班</t>
+          <t>4年10班</t>
         </is>
       </c>
       <c r="D303" s="44" t="n">
@@ -14542,7 +15585,7 @@
       </c>
       <c r="C304" s="52" t="inlineStr">
         <is>
-          <t>6年3班</t>
+          <t>5年10班</t>
         </is>
       </c>
       <c r="D304" s="44" t="n">
@@ -14573,7 +15616,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>6年4班</t>
+          <t>6年10班</t>
         </is>
       </c>
       <c r="D305" t="n">
@@ -14598,7 +15641,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>6年5班</t>
+          <t>3年11班</t>
         </is>
       </c>
       <c r="D306" t="n">
@@ -14623,7 +15666,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>6年6班</t>
+          <t>4年11班</t>
         </is>
       </c>
       <c r="D307" t="n">
@@ -14648,7 +15691,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>6年7班</t>
+          <t>5年11班</t>
         </is>
       </c>
       <c r="D308" t="n">
@@ -14673,7 +15716,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>6年8班</t>
+          <t>6年11班</t>
         </is>
       </c>
       <c r="D309" t="n">
@@ -14698,7 +15741,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>6年9班</t>
+          <t>3年12班</t>
         </is>
       </c>
       <c r="D310" t="n">
@@ -14723,7 +15766,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>6年10班</t>
+          <t>4年12班</t>
         </is>
       </c>
       <c r="D311" t="n">
@@ -14748,7 +15791,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>6年11班</t>
+          <t>5年12班</t>
         </is>
       </c>
       <c r="D312" t="n">
@@ -14823,7 +15866,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>3年2班</t>
+          <t>4年1班</t>
         </is>
       </c>
       <c r="D315" t="n">
@@ -14848,7 +15891,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>3年3班</t>
+          <t>5年1班</t>
         </is>
       </c>
       <c r="D316" t="n">
@@ -14873,7 +15916,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>3年4班</t>
+          <t>6年1班</t>
         </is>
       </c>
       <c r="D317" t="n">
@@ -14898,7 +15941,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>3年5班</t>
+          <t>3年2班</t>
         </is>
       </c>
       <c r="D318" t="n">
@@ -14923,7 +15966,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>3年6班</t>
+          <t>4年2班</t>
         </is>
       </c>
       <c r="D319" t="n">
@@ -14948,7 +15991,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>3年7班</t>
+          <t>5年2班</t>
         </is>
       </c>
       <c r="D320" t="n">
@@ -14973,7 +16016,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>3年8班</t>
+          <t>6年2班</t>
         </is>
       </c>
       <c r="D321" t="n">
@@ -14998,7 +16041,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>3年9班</t>
+          <t>3年3班</t>
         </is>
       </c>
       <c r="D322" t="n">
@@ -15023,7 +16066,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>3年10班</t>
+          <t>4年3班</t>
         </is>
       </c>
       <c r="D323" t="n">
@@ -15048,7 +16091,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>3年11班</t>
+          <t>5年3班</t>
         </is>
       </c>
       <c r="D324" t="n">
@@ -15073,7 +16116,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>3年12班</t>
+          <t>6年3班</t>
         </is>
       </c>
       <c r="D325" t="n">
@@ -15098,7 +16141,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>4年1班</t>
+          <t>3年4班</t>
         </is>
       </c>
       <c r="D326" t="n">
@@ -15123,7 +16166,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>4年2班</t>
+          <t>4年4班</t>
         </is>
       </c>
       <c r="D327" t="n">
@@ -15148,7 +16191,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>4年3班</t>
+          <t>5年4班</t>
         </is>
       </c>
       <c r="D328" t="n">
@@ -15173,7 +16216,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>4年4班</t>
+          <t>6年4班</t>
         </is>
       </c>
       <c r="D329" t="n">
@@ -15198,7 +16241,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>4年5班</t>
+          <t>3年5班</t>
         </is>
       </c>
       <c r="D330" t="n">
@@ -15223,7 +16266,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>4年6班</t>
+          <t>4年5班</t>
         </is>
       </c>
       <c r="D331" t="n">
@@ -15248,7 +16291,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>4年7班</t>
+          <t>5年5班</t>
         </is>
       </c>
       <c r="D332" t="n">
@@ -15273,7 +16316,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>4年8班</t>
+          <t>6年5班</t>
         </is>
       </c>
       <c r="D333" t="n">
@@ -15298,7 +16341,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>4年9班</t>
+          <t>3年6班</t>
         </is>
       </c>
       <c r="D334" t="n">
@@ -15323,7 +16366,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>4年10班</t>
+          <t>4年6班</t>
         </is>
       </c>
       <c r="D335" t="n">
@@ -15348,7 +16391,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>4年11班</t>
+          <t>5年6班</t>
         </is>
       </c>
       <c r="D336" t="n">
@@ -15373,7 +16416,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>4年12班</t>
+          <t>6年6班</t>
         </is>
       </c>
       <c r="D337" t="n">
@@ -15398,7 +16441,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>5年1班</t>
+          <t>3年7班</t>
         </is>
       </c>
       <c r="D338" t="n">
@@ -15423,7 +16466,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>5年2班</t>
+          <t>4年7班</t>
         </is>
       </c>
       <c r="D339" t="n">
@@ -15448,7 +16491,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>5年3班</t>
+          <t>5年7班</t>
         </is>
       </c>
       <c r="D340" t="n">
@@ -15473,7 +16516,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>5年4班</t>
+          <t>6年7班</t>
         </is>
       </c>
       <c r="D341" t="n">
@@ -15498,7 +16541,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>5年5班</t>
+          <t>3年8班</t>
         </is>
       </c>
       <c r="D342" t="n">
@@ -15523,7 +16566,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>5年6班</t>
+          <t>4年8班</t>
         </is>
       </c>
       <c r="D343" t="n">
@@ -15548,7 +16591,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>5年7班</t>
+          <t>5年8班</t>
         </is>
       </c>
       <c r="D344" t="n">
@@ -15573,7 +16616,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>5年8班</t>
+          <t>6年8班</t>
         </is>
       </c>
       <c r="D345" t="n">
@@ -15598,7 +16641,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>5年9班</t>
+          <t>3年9班</t>
         </is>
       </c>
       <c r="D346" t="n">
@@ -15623,7 +16666,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>5年10班</t>
+          <t>4年9班</t>
         </is>
       </c>
       <c r="D347" t="n">
@@ -15648,7 +16691,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>5年11班</t>
+          <t>5年9班</t>
         </is>
       </c>
       <c r="D348" t="n">
@@ -15673,7 +16716,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>5年12班</t>
+          <t>6年9班</t>
         </is>
       </c>
       <c r="D349" t="n">
@@ -15698,7 +16741,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>6年1班</t>
+          <t>3年10班</t>
         </is>
       </c>
       <c r="D350" t="n">
@@ -15723,7 +16766,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>6年2班</t>
+          <t>4年10班</t>
         </is>
       </c>
       <c r="D351" t="n">
@@ -15748,7 +16791,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>6年3班</t>
+          <t>5年10班</t>
         </is>
       </c>
       <c r="D352" t="n">
@@ -15773,7 +16816,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>6年4班</t>
+          <t>6年10班</t>
         </is>
       </c>
       <c r="D353" t="n">
@@ -15798,7 +16841,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>6年5班</t>
+          <t>3年11班</t>
         </is>
       </c>
       <c r="D354" t="n">
@@ -15823,7 +16866,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>6年6班</t>
+          <t>4年11班</t>
         </is>
       </c>
       <c r="D355" t="n">
@@ -15848,7 +16891,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>6年7班</t>
+          <t>5年11班</t>
         </is>
       </c>
       <c r="D356" t="n">
@@ -15873,7 +16916,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>6年8班</t>
+          <t>6年11班</t>
         </is>
       </c>
       <c r="D357" t="n">
@@ -15898,7 +16941,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>6年9班</t>
+          <t>3年12班</t>
         </is>
       </c>
       <c r="D358" t="n">
@@ -15923,7 +16966,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>6年10班</t>
+          <t>4年12班</t>
         </is>
       </c>
       <c r="D359" t="n">
@@ -15948,7 +16991,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>6年11班</t>
+          <t>5年12班</t>
         </is>
       </c>
       <c r="D360" t="n">
@@ -16023,7 +17066,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>5年2班</t>
+          <t>6年1班</t>
         </is>
       </c>
       <c r="D363" t="n">
@@ -16048,7 +17091,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>5年3班</t>
+          <t>5年2班</t>
         </is>
       </c>
       <c r="D364" t="n">
@@ -16073,7 +17116,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>5年4班</t>
+          <t>6年2班</t>
         </is>
       </c>
       <c r="D365" t="n">
@@ -16098,7 +17141,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>5年5班</t>
+          <t>5年3班</t>
         </is>
       </c>
       <c r="D366" t="n">
@@ -16123,7 +17166,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>5年6班</t>
+          <t>6年3班</t>
         </is>
       </c>
       <c r="D367" t="n">
@@ -16148,7 +17191,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>5年7班</t>
+          <t>5年4班</t>
         </is>
       </c>
       <c r="D368" t="n">
@@ -16173,7 +17216,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>5年8班</t>
+          <t>6年4班</t>
         </is>
       </c>
       <c r="D369" t="n">
@@ -16198,7 +17241,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>5年9班</t>
+          <t>5年5班</t>
         </is>
       </c>
       <c r="D370" t="n">
@@ -16223,7 +17266,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>5年10班</t>
+          <t>6年5班</t>
         </is>
       </c>
       <c r="D371" t="n">
@@ -16248,7 +17291,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>5年11班</t>
+          <t>5年6班</t>
         </is>
       </c>
       <c r="D372" t="n">
@@ -16273,7 +17316,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>5年12班</t>
+          <t>6年6班</t>
         </is>
       </c>
       <c r="D373" t="n">
@@ -16298,7 +17341,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>6年1班</t>
+          <t>5年7班</t>
         </is>
       </c>
       <c r="D374" t="n">
@@ -16323,7 +17366,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>6年2班</t>
+          <t>6年7班</t>
         </is>
       </c>
       <c r="D375" t="n">
@@ -16348,7 +17391,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>6年3班</t>
+          <t>5年8班</t>
         </is>
       </c>
       <c r="D376" t="n">
@@ -16373,7 +17416,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>6年4班</t>
+          <t>6年8班</t>
         </is>
       </c>
       <c r="D377" t="n">
@@ -16398,7 +17441,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>6年5班</t>
+          <t>5年9班</t>
         </is>
       </c>
       <c r="D378" t="n">
@@ -16423,7 +17466,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>6年6班</t>
+          <t>6年9班</t>
         </is>
       </c>
       <c r="D379" t="n">
@@ -16448,7 +17491,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>6年7班</t>
+          <t>5年10班</t>
         </is>
       </c>
       <c r="D380" t="n">
@@ -16473,7 +17516,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>6年8班</t>
+          <t>6年10班</t>
         </is>
       </c>
       <c r="D381" t="n">
@@ -16498,7 +17541,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>6年9班</t>
+          <t>5年11班</t>
         </is>
       </c>
       <c r="D382" t="n">
@@ -16523,7 +17566,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>6年10班</t>
+          <t>6年11班</t>
         </is>
       </c>
       <c r="D383" t="n">
@@ -16548,7 +17591,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>6年11班</t>
+          <t>5年12班</t>
         </is>
       </c>
       <c r="D384" t="n">
@@ -16714,7 +17757,7 @@
     <row r="5" ht="15" customHeight="1" s="36">
       <c r="A5" s="52" t="inlineStr">
         <is>
-          <t>6年3班</t>
+          <t>1年2班</t>
         </is>
       </c>
       <c r="B5" s="52" t="inlineStr">
@@ -16724,7 +17767,7 @@
       </c>
       <c r="C5" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D5" s="52" t="inlineStr">
@@ -16747,7 +17790,7 @@
     <row r="6" ht="15" customHeight="1" s="36">
       <c r="A6" s="52" t="inlineStr">
         <is>
-          <t>3年7班</t>
+          <t>1年5班</t>
         </is>
       </c>
       <c r="B6" s="52" t="inlineStr">
@@ -16780,7 +17823,7 @@
     <row r="7" ht="15" customHeight="1" s="36">
       <c r="A7" s="52" t="inlineStr">
         <is>
-          <t>4年5班</t>
+          <t>1年6班</t>
         </is>
       </c>
       <c r="B7" s="52" t="inlineStr">
@@ -16813,7 +17856,7 @@
     <row r="8" ht="15" customHeight="1" s="36">
       <c r="A8" s="52" t="inlineStr">
         <is>
-          <t>1年2班</t>
+          <t>1年8班</t>
         </is>
       </c>
       <c r="B8" s="52" t="inlineStr">
@@ -16823,7 +17866,7 @@
       </c>
       <c r="C8" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D8" s="52" t="inlineStr">
@@ -16846,7 +17889,7 @@
     <row r="9" ht="15" customHeight="1" s="36">
       <c r="A9" s="52" t="inlineStr">
         <is>
-          <t>5年9班</t>
+          <t>1年9班</t>
         </is>
       </c>
       <c r="B9" s="52" t="inlineStr">
@@ -16879,7 +17922,7 @@
     <row r="10" ht="15" customHeight="1" s="36">
       <c r="A10" s="52" t="inlineStr">
         <is>
-          <t>6年11班</t>
+          <t>2年8班</t>
         </is>
       </c>
       <c r="B10" s="52" t="inlineStr">
@@ -16889,7 +17932,7 @@
       </c>
       <c r="C10" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="52" t="inlineStr">
@@ -16912,12 +17955,12 @@
     <row r="11" ht="15" customHeight="1" s="36">
       <c r="A11" s="52" t="inlineStr">
         <is>
-          <t>1年8班</t>
+          <t>2年9班</t>
         </is>
       </c>
       <c r="B11" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C11" s="52" t="inlineStr">
@@ -16945,7 +17988,7 @@
     <row r="12" ht="15" customHeight="1" s="36">
       <c r="A12" s="52" t="inlineStr">
         <is>
-          <t>1年5班</t>
+          <t>3年1班</t>
         </is>
       </c>
       <c r="B12" s="52" t="inlineStr">
@@ -16955,7 +17998,7 @@
       </c>
       <c r="C12" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D12" s="52" t="inlineStr">
@@ -16978,17 +18021,17 @@
     <row r="13" ht="15" customHeight="1" s="36">
       <c r="A13" s="52" t="inlineStr">
         <is>
-          <t>6年5班</t>
+          <t>3年2班</t>
         </is>
       </c>
       <c r="B13" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C13" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D13" s="52" t="inlineStr">
@@ -17011,17 +18054,17 @@
     <row r="14" ht="15" customHeight="1" s="36">
       <c r="A14" s="52" t="inlineStr">
         <is>
-          <t>3年2班</t>
+          <t>3年6班</t>
         </is>
       </c>
       <c r="B14" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C14" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="52" t="inlineStr">
@@ -17044,17 +18087,17 @@
     <row r="15" ht="15" customHeight="1" s="36">
       <c r="A15" s="52" t="inlineStr">
         <is>
-          <t>3年10班</t>
+          <t>3年7班</t>
         </is>
       </c>
       <c r="B15" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C15" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D15" s="52" t="inlineStr">
@@ -17077,7 +18120,7 @@
     <row r="16" ht="15" customHeight="1" s="36">
       <c r="A16" s="52" t="inlineStr">
         <is>
-          <t>5年10班</t>
+          <t>3年10班</t>
         </is>
       </c>
       <c r="B16" s="52" t="inlineStr">
@@ -17110,7 +18153,7 @@
     <row r="17" ht="15" customHeight="1" s="36">
       <c r="A17" s="52" t="inlineStr">
         <is>
-          <t>3年1班</t>
+          <t>4年4班</t>
         </is>
       </c>
       <c r="B17" s="52" t="inlineStr">
@@ -17120,7 +18163,7 @@
       </c>
       <c r="C17" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D17" s="52" t="inlineStr">
@@ -17143,7 +18186,7 @@
     <row r="18" ht="15" customHeight="1" s="36">
       <c r="A18" s="52" t="inlineStr">
         <is>
-          <t>1年9班</t>
+          <t>4年5班</t>
         </is>
       </c>
       <c r="B18" s="52" t="inlineStr">
@@ -17153,7 +18196,7 @@
       </c>
       <c r="C18" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D18" s="52" t="inlineStr">
@@ -17176,7 +18219,7 @@
     <row r="19" ht="15" customHeight="1" s="36">
       <c r="A19" s="52" t="inlineStr">
         <is>
-          <t>3年6班</t>
+          <t>5年3班</t>
         </is>
       </c>
       <c r="B19" s="52" t="inlineStr">
@@ -17186,7 +18229,7 @@
       </c>
       <c r="C19" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D19" s="52" t="inlineStr">
@@ -17209,17 +18252,17 @@
     <row r="20" ht="15" customHeight="1" s="36">
       <c r="A20" s="52" t="inlineStr">
         <is>
-          <t>5年7班</t>
+          <t>5年4班</t>
         </is>
       </c>
       <c r="B20" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C20" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D20" s="52" t="inlineStr">
@@ -17242,7 +18285,7 @@
     <row r="21" ht="15" customHeight="1" s="36">
       <c r="A21" s="52" t="inlineStr">
         <is>
-          <t>6年8班</t>
+          <t>5年7班</t>
         </is>
       </c>
       <c r="B21" s="52" t="inlineStr">
@@ -17252,7 +18295,7 @@
       </c>
       <c r="C21" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D21" s="52" t="inlineStr">
@@ -17275,12 +18318,12 @@
     <row r="22" ht="15" customHeight="1" s="36">
       <c r="A22" s="52" t="inlineStr">
         <is>
-          <t>5年3班</t>
+          <t>5年9班</t>
         </is>
       </c>
       <c r="B22" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C22" s="52" t="inlineStr">
@@ -17308,17 +18351,17 @@
     <row r="23" ht="15" customHeight="1" s="36">
       <c r="A23" s="52" t="inlineStr">
         <is>
-          <t>4年4班</t>
+          <t>5年10班</t>
         </is>
       </c>
       <c r="B23" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C23" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D23" s="52" t="inlineStr">
@@ -17341,17 +18384,17 @@
     <row r="24" ht="15" customHeight="1" s="36">
       <c r="A24" s="52" t="inlineStr">
         <is>
-          <t>2年9班</t>
+          <t>6年3班</t>
         </is>
       </c>
       <c r="B24" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C24" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D24" s="52" t="inlineStr">
@@ -17374,17 +18417,17 @@
     <row r="25" ht="15" customHeight="1" s="36">
       <c r="A25" s="52" t="inlineStr">
         <is>
-          <t>2年8班</t>
+          <t>6年5班</t>
         </is>
       </c>
       <c r="B25" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C25" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D25" s="52" t="inlineStr">
@@ -17407,12 +18450,12 @@
     <row r="26" ht="15" customHeight="1" s="36">
       <c r="A26" s="52" t="inlineStr">
         <is>
-          <t>1年6班</t>
+          <t>6年8班</t>
         </is>
       </c>
       <c r="B26" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C26" s="52" t="inlineStr">
@@ -17440,7 +18483,7 @@
     <row r="27" ht="15" customHeight="1" s="36">
       <c r="A27" s="52" t="inlineStr">
         <is>
-          <t>5年4班</t>
+          <t>6年11班</t>
         </is>
       </c>
       <c r="B27" s="52" t="inlineStr">
@@ -17450,7 +18493,7 @@
       </c>
       <c r="C27" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D27" s="52" t="inlineStr">
@@ -17473,7 +18516,7 @@
     <row r="28" ht="15" customHeight="1" s="36">
       <c r="A28" s="52" t="inlineStr">
         <is>
-          <t>2年11班</t>
+          <t>1年1班</t>
         </is>
       </c>
       <c r="B28" s="52" t="inlineStr">
@@ -17483,7 +18526,7 @@
       </c>
       <c r="C28" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D28" s="52" t="inlineStr">
@@ -17506,7 +18549,7 @@
     <row r="29" ht="15" customHeight="1" s="36">
       <c r="A29" s="52" t="inlineStr">
         <is>
-          <t>6年6班</t>
+          <t>1年7班</t>
         </is>
       </c>
       <c r="B29" s="52" t="inlineStr">
@@ -17516,7 +18559,7 @@
       </c>
       <c r="C29" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D29" s="52" t="inlineStr">
@@ -17539,7 +18582,7 @@
     <row r="30" ht="15" customHeight="1" s="36">
       <c r="A30" s="52" t="inlineStr">
         <is>
-          <t>6年1班</t>
+          <t>2年1班</t>
         </is>
       </c>
       <c r="B30" s="52" t="inlineStr">
@@ -17549,7 +18592,7 @@
       </c>
       <c r="C30" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D30" s="52" t="inlineStr">
@@ -17572,7 +18615,7 @@
     <row r="31" ht="15" customHeight="1" s="36">
       <c r="A31" s="52" t="inlineStr">
         <is>
-          <t>1年7班</t>
+          <t>2年2班</t>
         </is>
       </c>
       <c r="B31" s="52" t="inlineStr">
@@ -17582,7 +18625,7 @@
       </c>
       <c r="C31" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D31" s="52" t="inlineStr">
@@ -17605,17 +18648,17 @@
     <row r="32" ht="15" customHeight="1" s="36">
       <c r="A32" s="52" t="inlineStr">
         <is>
-          <t>6年4班</t>
+          <t>2年5班</t>
         </is>
       </c>
       <c r="B32" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C32" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D32" s="52" t="inlineStr">
@@ -17638,17 +18681,17 @@
     <row r="33" ht="15" customHeight="1" s="36">
       <c r="A33" s="52" t="inlineStr">
         <is>
-          <t>3年12班</t>
+          <t>2年6班</t>
         </is>
       </c>
       <c r="B33" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C33" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D33" s="52" t="inlineStr">
@@ -17671,17 +18714,17 @@
     <row r="34" ht="15" customHeight="1" s="36">
       <c r="A34" s="52" t="inlineStr">
         <is>
-          <t>4年12班</t>
+          <t>2年10班</t>
         </is>
       </c>
       <c r="B34" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C34" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D34" s="52" t="inlineStr">
@@ -17704,12 +18747,12 @@
     <row r="35" ht="15" customHeight="1" s="36">
       <c r="A35" s="52" t="inlineStr">
         <is>
-          <t>4年7班</t>
+          <t>2年11班</t>
         </is>
       </c>
       <c r="B35" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C35" s="52" t="inlineStr">
@@ -17742,12 +18785,12 @@
       </c>
       <c r="B36" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C36" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D36" s="52" t="inlineStr">
@@ -17770,7 +18813,7 @@
     <row r="37" ht="15" customHeight="1" s="36">
       <c r="A37" s="52" t="inlineStr">
         <is>
-          <t>2年5班</t>
+          <t>3年5班</t>
         </is>
       </c>
       <c r="B37" s="52" t="inlineStr">
@@ -17780,7 +18823,7 @@
       </c>
       <c r="C37" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D37" s="52" t="inlineStr">
@@ -17803,17 +18846,17 @@
     <row r="38" ht="15" customHeight="1" s="36">
       <c r="A38" s="52" t="inlineStr">
         <is>
-          <t>6年9班</t>
+          <t>3年11班</t>
         </is>
       </c>
       <c r="B38" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C38" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D38" s="52" t="inlineStr">
@@ -17836,12 +18879,12 @@
     <row r="39" ht="15" customHeight="1" s="36">
       <c r="A39" s="52" t="inlineStr">
         <is>
-          <t>2年6班</t>
+          <t>3年12班</t>
         </is>
       </c>
       <c r="B39" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C39" s="52" t="inlineStr">
@@ -17869,17 +18912,17 @@
     <row r="40" ht="15" customHeight="1" s="36">
       <c r="A40" s="52" t="inlineStr">
         <is>
-          <t>5年2班</t>
+          <t>4年6班</t>
         </is>
       </c>
       <c r="B40" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C40" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D40" s="52" t="inlineStr">
@@ -17902,7 +18945,7 @@
     <row r="41" ht="15" customHeight="1" s="36">
       <c r="A41" s="52" t="inlineStr">
         <is>
-          <t>2年10班</t>
+          <t>4年7班</t>
         </is>
       </c>
       <c r="B41" s="52" t="inlineStr">
@@ -17940,12 +18983,12 @@
       </c>
       <c r="B42" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C42" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D42" s="52" t="inlineStr">
@@ -17968,7 +19011,7 @@
     <row r="43" ht="15" customHeight="1" s="36">
       <c r="A43" s="52" t="inlineStr">
         <is>
-          <t>2年1班</t>
+          <t>4年11班</t>
         </is>
       </c>
       <c r="B43" s="52" t="inlineStr">
@@ -17978,7 +19021,7 @@
       </c>
       <c r="C43" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D43" s="52" t="inlineStr">
@@ -18001,17 +19044,17 @@
     <row r="44" ht="15" customHeight="1" s="36">
       <c r="A44" s="52" t="inlineStr">
         <is>
-          <t>1年1班</t>
+          <t>4年12班</t>
         </is>
       </c>
       <c r="B44" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C44" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D44" s="52" t="inlineStr">
@@ -18034,17 +19077,17 @@
     <row r="45" ht="15" customHeight="1" s="36">
       <c r="A45" s="52" t="inlineStr">
         <is>
-          <t>3年5班</t>
+          <t>5年2班</t>
         </is>
       </c>
       <c r="B45" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C45" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D45" s="52" t="inlineStr">
@@ -18067,12 +19110,12 @@
     <row r="46" ht="15" customHeight="1" s="36">
       <c r="A46" s="52" t="inlineStr">
         <is>
-          <t>4年6班</t>
+          <t>6年1班</t>
         </is>
       </c>
       <c r="B46" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C46" s="52" t="inlineStr">
@@ -18100,17 +19143,17 @@
     <row r="47" ht="15" customHeight="1" s="36">
       <c r="A47" s="52" t="inlineStr">
         <is>
-          <t>4年11班</t>
+          <t>6年4班</t>
         </is>
       </c>
       <c r="B47" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C47" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D47" s="52" t="inlineStr">
@@ -18133,7 +19176,7 @@
     <row r="48" ht="15" customHeight="1" s="36">
       <c r="A48" s="52" t="inlineStr">
         <is>
-          <t>2年2班</t>
+          <t>6年6班</t>
         </is>
       </c>
       <c r="B48" s="52" t="inlineStr">
@@ -18143,7 +19186,7 @@
       </c>
       <c r="C48" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D48" s="52" t="inlineStr">
@@ -18166,7 +19209,7 @@
     <row r="49" ht="15" customHeight="1" s="36">
       <c r="A49" s="52" t="inlineStr">
         <is>
-          <t>3年11班</t>
+          <t>6年9班</t>
         </is>
       </c>
       <c r="B49" s="52" t="inlineStr">
@@ -18176,7 +19219,7 @@
       </c>
       <c r="C49" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D49" s="52" t="inlineStr">
@@ -18199,7 +19242,7 @@
     <row r="50" ht="15" customHeight="1" s="36">
       <c r="A50" s="52" t="inlineStr">
         <is>
-          <t>5年11班</t>
+          <t>1年3班</t>
         </is>
       </c>
       <c r="B50" s="52" t="inlineStr">
@@ -18209,7 +19252,7 @@
       </c>
       <c r="C50" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D50" s="52" t="inlineStr">
@@ -18232,17 +19275,17 @@
     <row r="51" ht="15" customHeight="1" s="36">
       <c r="A51" s="52" t="inlineStr">
         <is>
-          <t>5年8班</t>
+          <t>1年4班</t>
         </is>
       </c>
       <c r="B51" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C51" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D51" s="52" t="inlineStr">
@@ -18265,17 +19308,17 @@
     <row r="52" ht="15" customHeight="1" s="36">
       <c r="A52" s="52" t="inlineStr">
         <is>
-          <t>1年11班</t>
+          <t>1年10班</t>
         </is>
       </c>
       <c r="B52" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C52" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D52" s="52" t="inlineStr">
@@ -18298,17 +19341,17 @@
     <row r="53" ht="15" customHeight="1" s="36">
       <c r="A53" s="52" t="inlineStr">
         <is>
-          <t>2年4班</t>
+          <t>1年11班</t>
         </is>
       </c>
       <c r="B53" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C53" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D53" s="52" t="inlineStr">
@@ -18331,17 +19374,17 @@
     <row r="54" ht="15" customHeight="1" s="36">
       <c r="A54" s="52" t="inlineStr">
         <is>
-          <t>6年7班</t>
+          <t>1年12班</t>
         </is>
       </c>
       <c r="B54" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C54" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D54" s="52" t="inlineStr">
@@ -18364,17 +19407,17 @@
     <row r="55" ht="15" customHeight="1" s="36">
       <c r="A55" s="52" t="inlineStr">
         <is>
-          <t>5年1班</t>
+          <t>2年4班</t>
         </is>
       </c>
       <c r="B55" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C55" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D55" s="52" t="inlineStr">
@@ -18397,12 +19440,12 @@
     <row r="56" ht="15" customHeight="1" s="36">
       <c r="A56" s="52" t="inlineStr">
         <is>
-          <t>3年9班</t>
+          <t>2年7班</t>
         </is>
       </c>
       <c r="B56" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C56" s="52" t="inlineStr">
@@ -18430,17 +19473,17 @@
     <row r="57" ht="15" customHeight="1" s="36">
       <c r="A57" s="52" t="inlineStr">
         <is>
-          <t>1年12班</t>
+          <t>3年8班</t>
         </is>
       </c>
       <c r="B57" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C57" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D57" s="52" t="inlineStr">
@@ -18463,17 +19506,17 @@
     <row r="58" ht="15" customHeight="1" s="36">
       <c r="A58" s="52" t="inlineStr">
         <is>
-          <t>5年5班</t>
+          <t>3年9班</t>
         </is>
       </c>
       <c r="B58" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C58" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D58" s="52" t="inlineStr">
@@ -18496,17 +19539,17 @@
     <row r="59" ht="15" customHeight="1" s="36">
       <c r="A59" s="52" t="inlineStr">
         <is>
-          <t>5年6班</t>
+          <t>4年1班</t>
         </is>
       </c>
       <c r="B59" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C59" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D59" s="52" t="inlineStr">
@@ -18529,17 +19572,17 @@
     <row r="60" ht="15" customHeight="1" s="36">
       <c r="A60" s="52" t="inlineStr">
         <is>
-          <t>2年7班</t>
+          <t>4年3班</t>
         </is>
       </c>
       <c r="B60" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C60" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D60" s="52" t="inlineStr">
@@ -18562,17 +19605,17 @@
     <row r="61" ht="15" customHeight="1" s="36">
       <c r="A61" s="52" t="inlineStr">
         <is>
-          <t>1年3班</t>
+          <t>4年9班</t>
         </is>
       </c>
       <c r="B61" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C61" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D61" s="52" t="inlineStr">
@@ -18595,17 +19638,17 @@
     <row r="62" ht="15" customHeight="1" s="36">
       <c r="A62" s="52" t="inlineStr">
         <is>
-          <t>5年12班</t>
+          <t>5年1班</t>
         </is>
       </c>
       <c r="B62" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C62" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D62" s="52" t="inlineStr">
@@ -18628,17 +19671,17 @@
     <row r="63" ht="15" customHeight="1" s="36">
       <c r="A63" s="52" t="inlineStr">
         <is>
-          <t>1年10班</t>
+          <t>5年5班</t>
         </is>
       </c>
       <c r="B63" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C63" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D63" s="52" t="inlineStr">
@@ -18661,17 +19704,17 @@
     <row r="64" ht="15" customHeight="1" s="36">
       <c r="A64" s="52" t="inlineStr">
         <is>
-          <t>6年2班</t>
+          <t>5年6班</t>
         </is>
       </c>
       <c r="B64" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C64" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D64" s="52" t="inlineStr">
@@ -18694,17 +19737,17 @@
     <row r="65" ht="15" customHeight="1" s="36">
       <c r="A65" s="52" t="inlineStr">
         <is>
-          <t>4年1班</t>
+          <t>5年8班</t>
         </is>
       </c>
       <c r="B65" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C65" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D65" s="52" t="inlineStr">
@@ -18727,17 +19770,17 @@
     <row r="66" ht="15" customHeight="1" s="36">
       <c r="A66" s="52" t="inlineStr">
         <is>
-          <t>1年4班</t>
+          <t>5年11班</t>
         </is>
       </c>
       <c r="B66" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C66" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D66" s="52" t="inlineStr">
@@ -18760,17 +19803,17 @@
     <row r="67" ht="15" customHeight="1" s="36">
       <c r="A67" s="52" t="inlineStr">
         <is>
-          <t>3年8班</t>
+          <t>5年12班</t>
         </is>
       </c>
       <c r="B67" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C67" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D67" s="52" t="inlineStr">
@@ -18793,17 +19836,17 @@
     <row r="68" ht="15" customHeight="1" s="36">
       <c r="A68" s="52" t="inlineStr">
         <is>
-          <t>4年9班</t>
+          <t>6年2班</t>
         </is>
       </c>
       <c r="B68" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C68" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D68" s="52" t="inlineStr">
@@ -18826,17 +19869,17 @@
     <row r="69" ht="15" customHeight="1" s="36">
       <c r="A69" s="52" t="inlineStr">
         <is>
-          <t>6年12班</t>
+          <t>6年7班</t>
         </is>
       </c>
       <c r="B69" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C69" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D69" s="52" t="inlineStr">
@@ -18859,12 +19902,12 @@
     <row r="70" ht="15" customHeight="1" s="36">
       <c r="A70" s="52" t="inlineStr">
         <is>
-          <t>4年3班</t>
+          <t>6年12班</t>
         </is>
       </c>
       <c r="B70" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C70" s="52" t="inlineStr">
@@ -18892,17 +19935,17 @@
     <row r="71" ht="15" customHeight="1" s="36">
       <c r="A71" s="52" t="inlineStr">
         <is>
-          <t>4年8班</t>
+          <t>2年3班</t>
         </is>
       </c>
       <c r="B71" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C71" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D71" s="52" t="inlineStr">
@@ -18925,7 +19968,7 @@
     <row r="72" ht="15" customHeight="1" s="36">
       <c r="A72" s="52" t="inlineStr">
         <is>
-          <t>6年10班</t>
+          <t>4年8班</t>
         </is>
       </c>
       <c r="B72" s="52" t="inlineStr">
@@ -18958,17 +20001,17 @@
     <row r="73" ht="15" customHeight="1" s="36">
       <c r="A73" s="52" t="inlineStr">
         <is>
-          <t>2年3班</t>
+          <t>6年10班</t>
         </is>
       </c>
       <c r="B73" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C73" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D73" s="52" t="inlineStr">
@@ -18996,12 +20039,12 @@
       </c>
       <c r="B74" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C74" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D74" s="52" t="inlineStr">
@@ -19033,12 +20076,12 @@
       </c>
       <c r="B75" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C75" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D75" s="52" t="inlineStr">
@@ -19065,17 +20108,17 @@
     <row r="76" ht="15" customHeight="1" s="36">
       <c r="A76" s="52" t="inlineStr">
         <is>
-          <t>3年10班</t>
+          <t>6年1班</t>
         </is>
       </c>
       <c r="B76" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C76" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D76" s="52" t="inlineStr">
@@ -19102,7 +20145,7 @@
     <row r="77" ht="15" customHeight="1" s="36">
       <c r="A77" s="52" t="inlineStr">
         <is>
-          <t>1年1班</t>
+          <t>1年5班</t>
         </is>
       </c>
       <c r="B77" s="52" t="inlineStr">
@@ -19112,17 +20155,17 @@
       </c>
       <c r="C77" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D77" s="52" t="inlineStr">
         <is>
-          <t>客語</t>
+          <t>族語</t>
         </is>
       </c>
       <c r="E77" s="44" t="inlineStr">
         <is>
-          <t>客語甲</t>
+          <t>族語甲</t>
         </is>
       </c>
       <c r="F77" s="44" t="inlineStr">
@@ -19139,17 +20182,17 @@
     <row r="78" ht="15" customHeight="1" s="36">
       <c r="A78" s="52" t="inlineStr">
         <is>
-          <t>5年4班</t>
+          <t>1年12班</t>
         </is>
       </c>
       <c r="B78" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C78" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D78" s="52" t="inlineStr">
@@ -19176,27 +20219,27 @@
     <row r="79" ht="15" customHeight="1" s="36">
       <c r="A79" s="52" t="inlineStr">
         <is>
-          <t>5年7班</t>
+          <t>3年10班</t>
         </is>
       </c>
       <c r="B79" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C79" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D79" s="52" t="inlineStr">
         <is>
-          <t>族語</t>
+          <t>客語</t>
         </is>
       </c>
       <c r="E79" s="44" t="inlineStr">
         <is>
-          <t>族語甲</t>
+          <t>客語甲</t>
         </is>
       </c>
       <c r="F79" s="44" t="inlineStr">
@@ -19213,17 +20256,17 @@
     <row r="80" ht="15" customHeight="1" s="36">
       <c r="A80" s="52" t="inlineStr">
         <is>
-          <t>1年2班</t>
+          <t>2年10班</t>
         </is>
       </c>
       <c r="B80" s="52" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C80" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D80" s="52" t="inlineStr">
@@ -19250,7 +20293,7 @@
     <row r="81" ht="15" customHeight="1" s="36">
       <c r="A81" s="52" t="inlineStr">
         <is>
-          <t>4年6班</t>
+          <t>5年3班</t>
         </is>
       </c>
       <c r="B81" s="52" t="inlineStr">
@@ -19260,17 +20303,17 @@
       </c>
       <c r="C81" s="52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D81" s="52" t="inlineStr">
         <is>
-          <t>客語</t>
+          <t>族語</t>
         </is>
       </c>
       <c r="E81" s="44" t="inlineStr">
         <is>
-          <t>客語甲</t>
+          <t>族語甲</t>
         </is>
       </c>
       <c r="F81" s="44" t="inlineStr">
@@ -19287,7 +20330,7 @@
     <row r="82" ht="15" customHeight="1" s="36">
       <c r="A82" s="52" t="inlineStr">
         <is>
-          <t>3年7班</t>
+          <t>2年11班</t>
         </is>
       </c>
       <c r="B82" s="52" t="inlineStr">
@@ -19297,17 +20340,17 @@
       </c>
       <c r="C82" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D82" s="52" t="inlineStr">
         <is>
-          <t>族語</t>
+          <t>新住民語</t>
         </is>
       </c>
       <c r="E82" s="44" t="inlineStr">
         <is>
-          <t>族語甲</t>
+          <t>新住民語甲</t>
         </is>
       </c>
       <c r="F82" s="44" t="inlineStr">
@@ -19324,27 +20367,27 @@
     <row r="83" ht="15" customHeight="1" s="36">
       <c r="A83" s="52" t="inlineStr">
         <is>
-          <t>6年7班</t>
+          <t>6年9班</t>
         </is>
       </c>
       <c r="B83" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C83" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D83" s="52" t="inlineStr">
         <is>
-          <t>客語</t>
+          <t>族語</t>
         </is>
       </c>
       <c r="E83" s="44" t="inlineStr">
         <is>
-          <t>客語甲</t>
+          <t>族語甲</t>
         </is>
       </c>
       <c r="F83" s="44" t="inlineStr">
@@ -19361,12 +20404,12 @@
     <row r="84" ht="15" customHeight="1" s="36">
       <c r="A84" s="52" t="inlineStr">
         <is>
-          <t>1年11班</t>
+          <t>5年5班</t>
         </is>
       </c>
       <c r="B84" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C84" s="52" t="inlineStr">
@@ -19376,12 +20419,12 @@
       </c>
       <c r="D84" s="52" t="inlineStr">
         <is>
-          <t>客語</t>
+          <t>新住民語</t>
         </is>
       </c>
       <c r="E84" s="44" t="inlineStr">
         <is>
-          <t>客語甲</t>
+          <t>新住民語甲</t>
         </is>
       </c>
       <c r="F84" s="44" t="inlineStr">
@@ -19398,27 +20441,27 @@
     <row r="85" ht="15" customHeight="1" s="36">
       <c r="A85" s="52" t="inlineStr">
         <is>
-          <t>6年11班</t>
+          <t>6年8班</t>
         </is>
       </c>
       <c r="B85" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C85" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D85" s="52" t="inlineStr">
         <is>
-          <t>族語</t>
+          <t>客語</t>
         </is>
       </c>
       <c r="E85" s="44" t="inlineStr">
         <is>
-          <t>族語甲</t>
+          <t>客語甲</t>
         </is>
       </c>
       <c r="F85" s="44" t="inlineStr">
@@ -20203,7 +21246,7 @@
       </c>
       <c r="B5" s="52" t="inlineStr">
         <is>
-          <t>5年4班</t>
+          <t>6年12班</t>
         </is>
       </c>
       <c r="C5" s="44" t="inlineStr">
@@ -20218,7 +21261,7 @@
       </c>
       <c r="E5" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F5" s="44" t="inlineStr">
@@ -20227,7 +21270,7 @@
         </is>
       </c>
       <c r="G5" s="44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" s="44" t="n"/>
     </row>
@@ -20239,22 +21282,22 @@
       </c>
       <c r="B6" s="52" t="inlineStr">
         <is>
-          <t>4年1班</t>
+          <t>2年1班</t>
         </is>
       </c>
       <c r="C6" s="44" t="inlineStr">
         <is>
-          <t>數學</t>
+          <t>國語</t>
         </is>
       </c>
       <c r="D6" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>三</t>
         </is>
       </c>
       <c r="E6" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F6" s="44" t="inlineStr">
@@ -20275,7 +21318,7 @@
       </c>
       <c r="B7" s="52" t="inlineStr">
         <is>
-          <t>4年8班</t>
+          <t>3年1班</t>
         </is>
       </c>
       <c r="C7" s="44" t="inlineStr">
@@ -20290,7 +21333,7 @@
       </c>
       <c r="E7" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F7" s="44" t="inlineStr">
@@ -20311,22 +21354,22 @@
       </c>
       <c r="B8" s="52" t="inlineStr">
         <is>
-          <t>6年11班</t>
+          <t>5年6班</t>
         </is>
       </c>
       <c r="C8" s="44" t="inlineStr">
         <is>
-          <t>國語</t>
+          <t>數學</t>
         </is>
       </c>
       <c r="D8" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>四</t>
         </is>
       </c>
       <c r="E8" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F8" s="44" t="inlineStr">
@@ -20335,7 +21378,7 @@
         </is>
       </c>
       <c r="G8" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="44" t="n"/>
     </row>
@@ -20347,22 +21390,22 @@
       </c>
       <c r="B9" s="52" t="inlineStr">
         <is>
-          <t>4年5班</t>
+          <t>4年8班</t>
         </is>
       </c>
       <c r="C9" s="44" t="inlineStr">
         <is>
-          <t>數學</t>
+          <t>國語</t>
         </is>
       </c>
       <c r="D9" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>三</t>
         </is>
       </c>
       <c r="E9" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F9" s="44" t="inlineStr">
@@ -20371,7 +21414,7 @@
         </is>
       </c>
       <c r="G9" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="44" t="n"/>
     </row>
@@ -20383,22 +21426,22 @@
       </c>
       <c r="B10" s="52" t="inlineStr">
         <is>
-          <t>2年1班</t>
+          <t>3年2班</t>
         </is>
       </c>
       <c r="C10" s="44" t="inlineStr">
         <is>
-          <t>國語</t>
+          <t>數學</t>
         </is>
       </c>
       <c r="D10" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>二</t>
         </is>
       </c>
       <c r="E10" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F10" s="44" t="inlineStr">
@@ -20407,7 +21450,7 @@
         </is>
       </c>
       <c r="G10" s="44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" s="44" t="n"/>
     </row>
@@ -20419,7 +21462,7 @@
       </c>
       <c r="B11" s="52" t="inlineStr">
         <is>
-          <t>6年7班</t>
+          <t>6年3班</t>
         </is>
       </c>
       <c r="C11" s="44" t="inlineStr">
@@ -20429,12 +21472,12 @@
       </c>
       <c r="D11" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>四</t>
         </is>
       </c>
       <c r="E11" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F11" s="44" t="inlineStr">
@@ -20443,7 +21486,7 @@
         </is>
       </c>
       <c r="G11" s="44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" s="44" t="n"/>
     </row>
@@ -20455,7 +21498,7 @@
       </c>
       <c r="B12" s="52" t="inlineStr">
         <is>
-          <t>3年1班</t>
+          <t>5年8班</t>
         </is>
       </c>
       <c r="C12" s="44" t="inlineStr">
@@ -20465,12 +21508,12 @@
       </c>
       <c r="D12" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="E12" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F12" s="44" t="inlineStr">
@@ -20479,7 +21522,7 @@
         </is>
       </c>
       <c r="G12" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="44" t="n"/>
     </row>
@@ -20491,7 +21534,7 @@
       </c>
       <c r="B13" s="52" t="inlineStr">
         <is>
-          <t>5年6班</t>
+          <t>4年11班</t>
         </is>
       </c>
       <c r="C13" s="44" t="inlineStr">
@@ -20506,7 +21549,7 @@
       </c>
       <c r="E13" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F13" s="44" t="inlineStr">
@@ -20515,7 +21558,7 @@
         </is>
       </c>
       <c r="G13" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="44" t="n"/>
     </row>
@@ -20527,22 +21570,22 @@
       </c>
       <c r="B14" s="52" t="inlineStr">
         <is>
-          <t>6年10班</t>
+          <t>4年7班</t>
         </is>
       </c>
       <c r="C14" s="44" t="inlineStr">
         <is>
-          <t>數學</t>
+          <t>國語</t>
         </is>
       </c>
       <c r="D14" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>五</t>
         </is>
       </c>
       <c r="E14" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F14" s="44" t="inlineStr">
@@ -24453,7 +25496,7 @@
     <row r="5" ht="15" customHeight="1" s="36">
       <c r="A5" s="44" t="inlineStr">
         <is>
-          <t>體育己</t>
+          <t>音樂己</t>
         </is>
       </c>
       <c r="B5" s="52" t="inlineStr">
@@ -24463,7 +25506,7 @@
       </c>
       <c r="C5" s="52" t="inlineStr">
         <is>
-          <t>下午</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D5" s="52" t="inlineStr">
@@ -24471,11 +25514,7 @@
           <t>希望</t>
         </is>
       </c>
-      <c r="E5" s="44" t="inlineStr">
-        <is>
-          <t>接送小孩</t>
-        </is>
-      </c>
+      <c r="E5" s="44" t="n"/>
       <c r="F5" s="56">
         <f>IF(A5="","",COUNTIFS($A$5:$A$304,A5,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24484,25 +25523,29 @@
     <row r="6" ht="15" customHeight="1" s="36">
       <c r="A6" s="44" t="inlineStr">
         <is>
-          <t>體育甲</t>
+          <t>體育丁</t>
         </is>
       </c>
       <c r="B6" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C6" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D6" s="52" t="inlineStr">
         <is>
-          <t>希望</t>
-        </is>
-      </c>
-      <c r="E6" s="44" t="n"/>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E6" s="44" t="inlineStr">
+        <is>
+          <t>身體因素</t>
+        </is>
+      </c>
       <c r="F6" s="56">
         <f>IF(A6="","",COUNTIFS($A$5:$A$304,A6,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24511,22 +25554,22 @@
     <row r="7" ht="15" customHeight="1" s="36">
       <c r="A7" s="44" t="inlineStr">
         <is>
-          <t>英語甲</t>
+          <t>體育丁</t>
         </is>
       </c>
       <c r="B7" s="52" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C7" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D7" s="52" t="inlineStr">
         <is>
-          <t>希望</t>
+          <t>必須</t>
         </is>
       </c>
       <c r="E7" s="44" t="n"/>
@@ -24538,17 +25581,17 @@
     <row r="8" ht="15" customHeight="1" s="36">
       <c r="A8" s="44" t="inlineStr">
         <is>
-          <t>音樂甲</t>
+          <t>體育丁</t>
         </is>
       </c>
       <c r="B8" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C8" s="52" t="inlineStr">
         <is>
-          <t>下午</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" s="52" t="inlineStr">
@@ -24556,11 +25599,7 @@
           <t>希望</t>
         </is>
       </c>
-      <c r="E8" s="44" t="inlineStr">
-        <is>
-          <t>接送小孩</t>
-        </is>
-      </c>
+      <c r="E8" s="44" t="n"/>
       <c r="F8" s="56">
         <f>IF(A8="","",COUNTIFS($A$5:$A$304,A8,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24569,7 +25608,7 @@
     <row r="9" ht="15" customHeight="1" s="36">
       <c r="A9" s="44" t="inlineStr">
         <is>
-          <t>音樂戊</t>
+          <t>健康丙</t>
         </is>
       </c>
       <c r="B9" s="52" t="inlineStr">
@@ -24579,12 +25618,12 @@
       </c>
       <c r="C9" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="D9" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>希望</t>
         </is>
       </c>
       <c r="E9" s="44" t="inlineStr">
@@ -24600,12 +25639,12 @@
     <row r="10" ht="15" customHeight="1" s="36">
       <c r="A10" s="44" t="inlineStr">
         <is>
-          <t>音樂戊</t>
+          <t>社會丙</t>
         </is>
       </c>
       <c r="B10" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C10" s="52" t="inlineStr">
@@ -24620,7 +25659,7 @@
       </c>
       <c r="E10" s="44" t="inlineStr">
         <is>
-          <t>兼任行政會議</t>
+          <t>身體因素</t>
         </is>
       </c>
       <c r="F10" s="56">
@@ -24631,7 +25670,7 @@
     <row r="11" ht="15" customHeight="1" s="36">
       <c r="A11" s="44" t="inlineStr">
         <is>
-          <t>音樂戊</t>
+          <t>社會丙</t>
         </is>
       </c>
       <c r="B11" s="52" t="inlineStr">
@@ -24641,17 +25680,17 @@
       </c>
       <c r="C11" s="52" t="inlineStr">
         <is>
-          <t>下午</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D11" s="52" t="inlineStr">
         <is>
-          <t>希望</t>
+          <t>必須</t>
         </is>
       </c>
       <c r="E11" s="44" t="inlineStr">
         <is>
-          <t>接送小孩</t>
+          <t>身體因素</t>
         </is>
       </c>
       <c r="F11" s="56">
@@ -24662,17 +25701,17 @@
     <row r="12" ht="15" customHeight="1" s="36">
       <c r="A12" s="44" t="inlineStr">
         <is>
-          <t>體育戊</t>
+          <t>社會丙</t>
         </is>
       </c>
       <c r="B12" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C12" s="52" t="inlineStr">
         <is>
-          <t>下午</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" s="52" t="inlineStr">
@@ -24680,11 +25719,7 @@
           <t>希望</t>
         </is>
       </c>
-      <c r="E12" s="44" t="inlineStr">
-        <is>
-          <t>接送小孩</t>
-        </is>
-      </c>
+      <c r="E12" s="44" t="n"/>
       <c r="F12" s="56">
         <f>IF(A12="","",COUNTIFS($A$5:$A$304,A12,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24693,22 +25728,22 @@
     <row r="13" ht="15" customHeight="1" s="36">
       <c r="A13" s="44" t="inlineStr">
         <is>
-          <t>資訊乙</t>
+          <t>資訊甲</t>
         </is>
       </c>
       <c r="B13" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C13" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="D13" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>希望</t>
         </is>
       </c>
       <c r="E13" s="44" t="inlineStr">
@@ -24724,7 +25759,7 @@
     <row r="14" ht="15" customHeight="1" s="36">
       <c r="A14" s="44" t="inlineStr">
         <is>
-          <t>資訊乙</t>
+          <t>健康甲</t>
         </is>
       </c>
       <c r="B14" s="52" t="inlineStr">
@@ -24734,7 +25769,7 @@
       </c>
       <c r="C14" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" s="52" t="inlineStr">
@@ -24742,11 +25777,7 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="E14" s="44" t="inlineStr">
-        <is>
-          <t>進修</t>
-        </is>
-      </c>
+      <c r="E14" s="44" t="n"/>
       <c r="F14" s="56">
         <f>IF(A14="","",COUNTIFS($A$5:$A$304,A14,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24755,25 +25786,29 @@
     <row r="15" ht="15" customHeight="1" s="36">
       <c r="A15" s="44" t="inlineStr">
         <is>
-          <t>資訊乙</t>
+          <t>健康甲</t>
         </is>
       </c>
       <c r="B15" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C15" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D15" s="52" t="inlineStr">
         <is>
-          <t>希望</t>
-        </is>
-      </c>
-      <c r="E15" s="44" t="n"/>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E15" s="44" t="inlineStr">
+        <is>
+          <t>身體因素</t>
+        </is>
+      </c>
       <c r="F15" s="56">
         <f>IF(A15="","",COUNTIFS($A$5:$A$304,A15,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24782,7 +25817,7 @@
     <row r="16" ht="15" customHeight="1" s="36">
       <c r="A16" s="44" t="inlineStr">
         <is>
-          <t>健康丙</t>
+          <t>健康甲</t>
         </is>
       </c>
       <c r="B16" s="52" t="inlineStr">
@@ -24792,15 +25827,19 @@
       </c>
       <c r="C16" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="D16" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E16" s="44" t="n"/>
+          <t>希望</t>
+        </is>
+      </c>
+      <c r="E16" s="44" t="inlineStr">
+        <is>
+          <t>接送小孩</t>
+        </is>
+      </c>
       <c r="F16" s="56">
         <f>IF(A16="","",COUNTIFS($A$5:$A$304,A16,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24809,7 +25848,7 @@
     <row r="17" ht="15" customHeight="1" s="36">
       <c r="A17" s="44" t="inlineStr">
         <is>
-          <t>健康丙</t>
+          <t>英語丁</t>
         </is>
       </c>
       <c r="B17" s="52" t="inlineStr">
@@ -24819,7 +25858,7 @@
       </c>
       <c r="C17" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D17" s="52" t="inlineStr">
@@ -24827,7 +25866,11 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="E17" s="44" t="n"/>
+      <c r="E17" s="44" t="inlineStr">
+        <is>
+          <t>進修</t>
+        </is>
+      </c>
       <c r="F17" s="56">
         <f>IF(A17="","",COUNTIFS($A$5:$A$304,A17,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24836,27 +25879,27 @@
     <row r="18" ht="15" customHeight="1" s="36">
       <c r="A18" s="44" t="inlineStr">
         <is>
-          <t>健康丙</t>
+          <t>英語丁</t>
         </is>
       </c>
       <c r="B18" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C18" s="52" t="inlineStr">
         <is>
-          <t>下午</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D18" s="52" t="inlineStr">
         <is>
-          <t>希望</t>
+          <t>必須</t>
         </is>
       </c>
       <c r="E18" s="44" t="inlineStr">
         <is>
-          <t>接送小孩</t>
+          <t>兼任行政會議</t>
         </is>
       </c>
       <c r="F18" s="56">
@@ -24867,25 +25910,29 @@
     <row r="19" ht="15" customHeight="1" s="36">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>健康丙</t>
+          <t>英語丁</t>
         </is>
       </c>
       <c r="B19" s="52" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C19" s="52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D19" s="52" t="inlineStr">
         <is>
-          <t>希望</t>
-        </is>
-      </c>
-      <c r="E19" s="44" t="n"/>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E19" s="44" t="inlineStr">
+        <is>
+          <t>身體因素</t>
+        </is>
+      </c>
       <c r="F19" s="56">
         <f>IF(A19="","",COUNTIFS($A$5:$A$304,A19,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24894,27 +25941,27 @@
     <row r="20" ht="15" customHeight="1" s="36">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>社會丙</t>
+          <t>英語丁</t>
         </is>
       </c>
       <c r="B20" s="52" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C20" s="52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="D20" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>希望</t>
         </is>
       </c>
       <c r="E20" s="44" t="inlineStr">
         <is>
-          <t>身體因素</t>
+          <t>接送小孩</t>
         </is>
       </c>
       <c r="F20" s="56">
@@ -24925,7 +25972,7 @@
     <row r="21" ht="15" customHeight="1" s="36">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>社會丙</t>
+          <t>自然丙</t>
         </is>
       </c>
       <c r="B21" s="52" t="inlineStr">
@@ -24935,7 +25982,7 @@
       </c>
       <c r="C21" s="52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D21" s="52" t="inlineStr">
@@ -24943,11 +25990,7 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="E21" s="44" t="inlineStr">
-        <is>
-          <t>進修</t>
-        </is>
-      </c>
+      <c r="E21" s="44" t="n"/>
       <c r="F21" s="56">
         <f>IF(A21="","",COUNTIFS($A$5:$A$304,A21,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24956,7 +25999,7 @@
     <row r="22" ht="15" customHeight="1" s="36">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>社會丙</t>
+          <t>自然丙</t>
         </is>
       </c>
       <c r="B22" s="52" t="inlineStr">
@@ -24966,15 +26009,19 @@
       </c>
       <c r="C22" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>下午</t>
         </is>
       </c>
       <c r="D22" s="52" t="inlineStr">
         <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E22" s="44" t="n"/>
+          <t>希望</t>
+        </is>
+      </c>
+      <c r="E22" s="44" t="inlineStr">
+        <is>
+          <t>接送小孩</t>
+        </is>
+      </c>
       <c r="F22" s="56">
         <f>IF(A22="","",COUNTIFS($A$5:$A$304,A22,$D$5:$D$304,"必須"))</f>
         <v/>
@@ -24983,22 +26030,22 @@
     <row r="23" ht="15" customHeight="1" s="36">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>社會丙</t>
+          <t>音樂丁</t>
         </is>
       </c>
       <c r="B23" s="52" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C23" s="52" t="inlineStr">
         <is>
-          <t>下午</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D23" s="52" t="inlineStr">
         <is>
-          <t>希望</t>
+          <t>必須</t>
         </is>
       </c>
       <c r="E23" s="44" t="inlineStr">
@@ -25012,65 +26059,181 @@
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="36">
-      <c r="A24" s="44" t="n"/>
-      <c r="B24" s="52" t="n"/>
-      <c r="C24" s="52" t="n"/>
-      <c r="D24" s="52" t="n"/>
-      <c r="E24" s="44" t="n"/>
+      <c r="A24" s="44" t="inlineStr">
+        <is>
+          <t>音樂丁</t>
+        </is>
+      </c>
+      <c r="B24" s="52" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="C24" s="52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D24" s="52" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E24" s="44" t="inlineStr">
+        <is>
+          <t>接送小孩</t>
+        </is>
+      </c>
       <c r="F24" s="56">
         <f>IF(A24="","",COUNTIFS($A$5:$A$304,A24,$D$5:$D$304,"必須"))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="36">
-      <c r="A25" s="44" t="n"/>
-      <c r="B25" s="52" t="n"/>
-      <c r="C25" s="52" t="n"/>
-      <c r="D25" s="52" t="n"/>
-      <c r="E25" s="44" t="n"/>
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>音樂丁</t>
+        </is>
+      </c>
+      <c r="B25" s="52" t="inlineStr">
+        <is>
+          <t>二</t>
+        </is>
+      </c>
+      <c r="C25" s="52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="52" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E25" s="44" t="inlineStr">
+        <is>
+          <t>接送小孩</t>
+        </is>
+      </c>
       <c r="F25" s="56">
         <f>IF(A25="","",COUNTIFS($A$5:$A$304,A25,$D$5:$D$304,"必須"))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="36">
-      <c r="A26" s="44" t="n"/>
-      <c r="B26" s="52" t="n"/>
-      <c r="C26" s="52" t="n"/>
-      <c r="D26" s="52" t="n"/>
-      <c r="E26" s="44" t="n"/>
+      <c r="A26" s="44" t="inlineStr">
+        <is>
+          <t>音樂丁</t>
+        </is>
+      </c>
+      <c r="B26" s="52" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C26" s="52" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D26" s="52" t="inlineStr">
+        <is>
+          <t>希望</t>
+        </is>
+      </c>
+      <c r="E26" s="44" t="inlineStr">
+        <is>
+          <t>接送小孩</t>
+        </is>
+      </c>
       <c r="F26" s="56">
         <f>IF(A26="","",COUNTIFS($A$5:$A$304,A26,$D$5:$D$304,"必須"))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="36">
-      <c r="A27" s="44" t="n"/>
-      <c r="B27" s="52" t="n"/>
-      <c r="C27" s="52" t="n"/>
-      <c r="D27" s="52" t="n"/>
-      <c r="E27" s="44" t="n"/>
+      <c r="A27" s="44" t="inlineStr">
+        <is>
+          <t>社會丁</t>
+        </is>
+      </c>
+      <c r="B27" s="52" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C27" s="52" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D27" s="52" t="inlineStr">
+        <is>
+          <t>希望</t>
+        </is>
+      </c>
+      <c r="E27" s="44" t="inlineStr">
+        <is>
+          <t>接送小孩</t>
+        </is>
+      </c>
       <c r="F27" s="56">
         <f>IF(A27="","",COUNTIFS($A$5:$A$304,A27,$D$5:$D$304,"必須"))</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="36">
-      <c r="A28" s="44" t="n"/>
-      <c r="B28" s="52" t="n"/>
-      <c r="C28" s="52" t="n"/>
-      <c r="D28" s="52" t="n"/>
-      <c r="E28" s="44" t="n"/>
+      <c r="A28" s="44" t="inlineStr">
+        <is>
+          <t>自然乙</t>
+        </is>
+      </c>
+      <c r="B28" s="52" t="inlineStr">
+        <is>
+          <t>四</t>
+        </is>
+      </c>
+      <c r="C28" s="52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="52" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E28" s="44" t="inlineStr">
+        <is>
+          <t>接送小孩</t>
+        </is>
+      </c>
       <c r="F28" s="56">
         <f>IF(A28="","",COUNTIFS($A$5:$A$304,A28,$D$5:$D$304,"必須"))</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="36">
-      <c r="A29" s="44" t="n"/>
-      <c r="B29" s="52" t="n"/>
-      <c r="C29" s="52" t="n"/>
-      <c r="D29" s="52" t="n"/>
+      <c r="A29" s="44" t="inlineStr">
+        <is>
+          <t>自然乙</t>
+        </is>
+      </c>
+      <c r="B29" s="52" t="inlineStr">
+        <is>
+          <t>四</t>
+        </is>
+      </c>
+      <c r="C29" s="52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" s="52" t="inlineStr">
+        <is>
+          <t>希望</t>
+        </is>
+      </c>
       <c r="E29" s="44" t="n"/>
       <c r="F29" s="56">
         <f>IF(A29="","",COUNTIFS($A$5:$A$304,A29,$D$5:$D$304,"必須"))</f>
